--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845438</v>
+        <v>129845425</v>
       </c>
       <c r="B4" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406361</v>
+        <v>406832</v>
       </c>
       <c r="R4" t="n">
-        <v>6832815</v>
+        <v>6832816</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845425</v>
+        <v>129845419</v>
       </c>
       <c r="B5" t="n">
         <v>79700</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406832</v>
+        <v>406387</v>
       </c>
       <c r="R5" t="n">
-        <v>6832816</v>
+        <v>6832850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845441</v>
+        <v>129845438</v>
       </c>
       <c r="B6" t="n">
         <v>79671</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406638</v>
+        <v>406361</v>
       </c>
       <c r="R6" t="n">
-        <v>6832869</v>
+        <v>6832815</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845419</v>
+        <v>129845441</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406387</v>
+        <v>406638</v>
       </c>
       <c r="R7" t="n">
-        <v>6832850</v>
+        <v>6832869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845661</v>
+        <v>129845630</v>
       </c>
       <c r="B8" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406352</v>
+        <v>406631</v>
       </c>
       <c r="R8" t="n">
-        <v>6832709</v>
+        <v>6832822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845427</v>
+        <v>129845443</v>
       </c>
       <c r="B9" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1373,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406794</v>
+        <v>406333</v>
       </c>
       <c r="R9" t="n">
-        <v>6832934</v>
+        <v>6832733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845417</v>
+        <v>129845661</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406346</v>
+        <v>406352</v>
       </c>
       <c r="R10" t="n">
-        <v>6832798</v>
+        <v>6832709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1552,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845443</v>
+        <v>129845427</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,42 +1575,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406333</v>
+        <v>406794</v>
       </c>
       <c r="R11" t="n">
-        <v>6832733</v>
+        <v>6832934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845630</v>
+        <v>129845417</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,42 +1672,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406631</v>
+        <v>406346</v>
       </c>
       <c r="R12" t="n">
-        <v>6832822</v>
+        <v>6832798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,57 +1746,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845610</v>
+        <v>129845462</v>
       </c>
       <c r="B13" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406262</v>
+        <v>406713</v>
       </c>
       <c r="R13" t="n">
-        <v>6832854</v>
+        <v>6832904</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,28 +1846,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845604</v>
+        <v>129845610</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,21 +1876,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406424</v>
+        <v>406262</v>
       </c>
       <c r="R14" t="n">
-        <v>6832657</v>
+        <v>6832854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2243,10 +2253,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845655</v>
+        <v>129845613</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2254,21 +2264,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2288,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406473</v>
+        <v>406388</v>
       </c>
       <c r="R18" t="n">
-        <v>6832798</v>
+        <v>6832683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,54 +2350,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845462</v>
+        <v>129845617</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406713</v>
+        <v>406626</v>
       </c>
       <c r="R19" t="n">
-        <v>6832904</v>
+        <v>6832781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2428,29 +2429,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845613</v>
+        <v>129845604</v>
       </c>
       <c r="B20" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2458,21 +2458,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406388</v>
+        <v>406424</v>
       </c>
       <c r="R20" t="n">
-        <v>6832683</v>
+        <v>6832657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845617</v>
+        <v>129845655</v>
       </c>
       <c r="B22" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406626</v>
+        <v>406473</v>
       </c>
       <c r="R22" t="n">
-        <v>6832781</v>
+        <v>6832798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,54 +2742,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129845460</v>
+        <v>129845619</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406431</v>
+        <v>406776</v>
       </c>
       <c r="R23" t="n">
-        <v>6832825</v>
+        <v>6832860</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,26 +2821,25 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129845652</v>
+        <v>129845488</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2884,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406408</v>
+        <v>406528</v>
       </c>
       <c r="R24" t="n">
-        <v>6832778</v>
+        <v>6832873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2934,19 +2924,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129845659</v>
+        <v>129845652</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -2981,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406556</v>
+        <v>406408</v>
       </c>
       <c r="R25" t="n">
-        <v>6832846</v>
+        <v>6832778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3043,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845619</v>
+        <v>129845659</v>
       </c>
       <c r="B26" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406776</v>
+        <v>406556</v>
       </c>
       <c r="R26" t="n">
-        <v>6832860</v>
+        <v>6832846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,45 +3324,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129845488</v>
+        <v>129845460</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406528</v>
+        <v>406431</v>
       </c>
       <c r="R29" t="n">
-        <v>6832873</v>
+        <v>6832825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3413,6 +3412,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3431,41 +3431,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845463</v>
+        <v>129845636</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3475,10 +3474,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406746</v>
+        <v>406595</v>
       </c>
       <c r="R30" t="n">
-        <v>6832985</v>
+        <v>6833001</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,29 +3518,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845639</v>
+        <v>129845449</v>
       </c>
       <c r="B31" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3549,34 +3547,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406276</v>
+        <v>406498</v>
       </c>
       <c r="R31" t="n">
-        <v>6832761</v>
+        <v>6832913</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,22 +3629,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845636</v>
+        <v>129845412</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3646,42 +3652,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406595</v>
+        <v>406426</v>
       </c>
       <c r="R32" t="n">
-        <v>6833001</v>
+        <v>6832990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,57 +3726,66 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845412</v>
+        <v>129845463</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406426</v>
+        <v>406746</v>
       </c>
       <c r="R33" t="n">
-        <v>6832990</v>
+        <v>6832985</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3819,6 +3826,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3837,10 +3845,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845449</v>
+        <v>129845639</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3848,42 +3856,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406498</v>
+        <v>406276</v>
       </c>
       <c r="R34" t="n">
-        <v>6832913</v>
+        <v>6832761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3930,12 +3930,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845592</v>
+        <v>129845483</v>
       </c>
       <c r="B36" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406370</v>
+        <v>406344</v>
       </c>
       <c r="R36" t="n">
-        <v>6832711</v>
+        <v>6832706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4124,19 +4124,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845483</v>
+        <v>129845657</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406344</v>
+        <v>406495</v>
       </c>
       <c r="R37" t="n">
-        <v>6832706</v>
+        <v>6832766</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,22 +4221,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845455</v>
+        <v>129845592</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406486</v>
+        <v>406370</v>
       </c>
       <c r="R38" t="n">
-        <v>6833057</v>
+        <v>6832711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,22 +4318,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129845657</v>
+        <v>129845455</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406495</v>
+        <v>406486</v>
       </c>
       <c r="R39" t="n">
-        <v>6832766</v>
+        <v>6833057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,22 +4415,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845446</v>
+        <v>129845490</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4438,21 +4438,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406393</v>
+        <v>406560</v>
       </c>
       <c r="R40" t="n">
-        <v>6833110</v>
+        <v>6832885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4498,11 +4498,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>16.21 färska spår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4529,7 +4524,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845490</v>
+        <v>129845491</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4564,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406560</v>
+        <v>406588</v>
       </c>
       <c r="R41" t="n">
-        <v>6832885</v>
+        <v>6832866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4626,7 +4621,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845491</v>
+        <v>129845492</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -4655,16 +4650,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406588</v>
+        <v>406591</v>
       </c>
       <c r="R42" t="n">
-        <v>6832866</v>
+        <v>6832966</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4705,6 +4703,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4723,10 +4722,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845611</v>
+        <v>129845660</v>
       </c>
       <c r="B43" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4734,21 +4733,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406276</v>
+        <v>406728</v>
       </c>
       <c r="R43" t="n">
-        <v>6832761</v>
+        <v>6832848</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4820,10 +4819,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845601</v>
+        <v>129845611</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4831,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406583</v>
+        <v>406276</v>
       </c>
       <c r="R44" t="n">
-        <v>6832841</v>
+        <v>6832761</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4917,10 +4916,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845492</v>
+        <v>129845431</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4928,37 +4927,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406591</v>
+        <v>406368</v>
       </c>
       <c r="R45" t="n">
-        <v>6832966</v>
+        <v>6833201</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4999,7 +4995,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5018,10 +5013,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845431</v>
+        <v>129845601</v>
       </c>
       <c r="B46" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5029,21 +5024,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5053,10 +5048,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406368</v>
+        <v>406583</v>
       </c>
       <c r="R46" t="n">
-        <v>6833201</v>
+        <v>6832841</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5103,22 +5098,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845631</v>
+        <v>129845456</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5126,42 +5121,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406698</v>
+        <v>406442</v>
       </c>
       <c r="R47" t="n">
-        <v>6832875</v>
+        <v>6833041</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5208,22 +5195,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845456</v>
+        <v>129845631</v>
       </c>
       <c r="B48" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5231,34 +5218,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406442</v>
+        <v>406698</v>
       </c>
       <c r="R48" t="n">
-        <v>6833041</v>
+        <v>6832875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5305,57 +5300,66 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845660</v>
+        <v>129845461</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406728</v>
+        <v>406589</v>
       </c>
       <c r="R49" t="n">
-        <v>6832848</v>
+        <v>6832990</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5396,28 +5400,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845638</v>
+        <v>129845624</v>
       </c>
       <c r="B50" t="n">
-        <v>78839</v>
+        <v>57896</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5425,34 +5430,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406290</v>
+        <v>406494</v>
       </c>
       <c r="R50" t="n">
-        <v>6832900</v>
+        <v>6832766</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5511,54 +5524,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845461</v>
+        <v>129845638</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406589</v>
+        <v>406290</v>
       </c>
       <c r="R51" t="n">
-        <v>6832990</v>
+        <v>6832900</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,19 +5603,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5718,7 +5721,7 @@
         <v>129845626</v>
       </c>
       <c r="B53" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5917,10 +5920,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845624</v>
+        <v>129845589</v>
       </c>
       <c r="B55" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5928,42 +5931,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406494</v>
+        <v>406406</v>
       </c>
       <c r="R55" t="n">
-        <v>6832766</v>
+        <v>6833199</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6022,10 +6017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845589</v>
+        <v>129845632</v>
       </c>
       <c r="B56" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,34 +6028,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406406</v>
+        <v>406667</v>
       </c>
       <c r="R56" t="n">
-        <v>6833199</v>
+        <v>6832849</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6119,10 +6122,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845602</v>
+        <v>129845633</v>
       </c>
       <c r="B57" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6130,34 +6133,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406791</v>
+        <v>406674</v>
       </c>
       <c r="R57" t="n">
-        <v>6832844</v>
+        <v>6832801</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6216,10 +6227,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845487</v>
+        <v>129845627</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6227,34 +6238,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406409</v>
+        <v>406539</v>
       </c>
       <c r="R58" t="n">
-        <v>6832824</v>
+        <v>6832767</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6301,57 +6320,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845435</v>
+        <v>129845459</v>
       </c>
       <c r="B59" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406455</v>
+        <v>406331</v>
       </c>
       <c r="R59" t="n">
-        <v>6833027</v>
+        <v>6832715</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6392,6 +6420,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6410,10 +6439,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845625</v>
+        <v>129845435</v>
       </c>
       <c r="B60" t="n">
-        <v>91614</v>
+        <v>79671</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6421,41 +6450,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406472</v>
+        <v>406455</v>
       </c>
       <c r="R60" t="n">
-        <v>6832767</v>
+        <v>6833027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6496,19 +6518,18 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6612,10 +6633,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845632</v>
+        <v>129845602</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6623,42 +6644,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406667</v>
+        <v>406791</v>
       </c>
       <c r="R62" t="n">
-        <v>6832849</v>
+        <v>6832844</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6717,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845633</v>
+        <v>129845466</v>
       </c>
       <c r="B63" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6728,42 +6741,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406674</v>
+        <v>406266</v>
       </c>
       <c r="R63" t="n">
-        <v>6832801</v>
+        <v>6832810</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6810,22 +6815,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845466</v>
+        <v>129845625</v>
       </c>
       <c r="B64" t="n">
-        <v>78838</v>
+        <v>91618</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6833,34 +6838,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406266</v>
+        <v>406472</v>
       </c>
       <c r="R64" t="n">
-        <v>6832810</v>
+        <v>6832767</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6901,72 +6913,64 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845459</v>
+        <v>129845487</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406331</v>
+        <v>406409</v>
       </c>
       <c r="R65" t="n">
-        <v>6832715</v>
+        <v>6832824</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7007,7 +7011,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7026,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845627</v>
+        <v>129845654</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7037,42 +7040,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406539</v>
+        <v>406460</v>
       </c>
       <c r="R66" t="n">
-        <v>6832767</v>
+        <v>6832823</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,10 +7126,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845590</v>
+        <v>129845493</v>
       </c>
       <c r="B67" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7142,21 +7137,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406421</v>
+        <v>406785</v>
       </c>
       <c r="R67" t="n">
-        <v>6833142</v>
+        <v>6832912</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7216,22 +7211,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845593</v>
+        <v>129845452</v>
       </c>
       <c r="B68" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7239,34 +7234,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406451</v>
+        <v>406630</v>
       </c>
       <c r="R68" t="n">
-        <v>6832712</v>
+        <v>6832941</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7313,57 +7316,66 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845605</v>
+        <v>129845642</v>
       </c>
       <c r="B69" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406440</v>
+        <v>406547</v>
       </c>
       <c r="R69" t="n">
-        <v>6833100</v>
+        <v>6832775</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7404,6 +7416,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7422,10 +7435,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845493</v>
+        <v>129845434</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7433,21 +7446,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7457,10 +7470,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406785</v>
+        <v>406499</v>
       </c>
       <c r="R70" t="n">
-        <v>6832912</v>
+        <v>6833054</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7519,7 +7532,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845607</v>
+        <v>129845440</v>
       </c>
       <c r="B71" t="n">
         <v>79671</v>
@@ -7554,10 +7567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406407</v>
+        <v>406445</v>
       </c>
       <c r="R71" t="n">
-        <v>6833199</v>
+        <v>6832921</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7604,22 +7617,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845654</v>
+        <v>129845605</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7627,21 +7640,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7651,10 +7664,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406460</v>
+        <v>406440</v>
       </c>
       <c r="R72" t="n">
-        <v>6832823</v>
+        <v>6833100</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7713,7 +7726,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845434</v>
+        <v>129845607</v>
       </c>
       <c r="B73" t="n">
         <v>79671</v>
@@ -7748,10 +7761,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406499</v>
+        <v>406407</v>
       </c>
       <c r="R73" t="n">
-        <v>6833054</v>
+        <v>6833199</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7798,22 +7811,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845440</v>
+        <v>129845590</v>
       </c>
       <c r="B74" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7821,21 +7834,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7845,10 +7858,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406445</v>
+        <v>406421</v>
       </c>
       <c r="R74" t="n">
-        <v>6832921</v>
+        <v>6833142</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7895,66 +7908,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845642</v>
+        <v>129845593</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406547</v>
+        <v>406451</v>
       </c>
       <c r="R75" t="n">
-        <v>6832775</v>
+        <v>6832712</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7995,7 +7999,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8014,10 +8017,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129845452</v>
+        <v>129845420</v>
       </c>
       <c r="B76" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8025,42 +8028,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406630</v>
+        <v>406424</v>
       </c>
       <c r="R76" t="n">
-        <v>6832941</v>
+        <v>6832865</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8119,10 +8114,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845486</v>
+        <v>129845415</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8130,21 +8125,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8154,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406350</v>
+        <v>406317</v>
       </c>
       <c r="R77" t="n">
-        <v>6832772</v>
+        <v>6832733</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8216,10 +8211,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845606</v>
+        <v>129845600</v>
       </c>
       <c r="B78" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8227,21 +8222,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8251,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406394</v>
+        <v>406582</v>
       </c>
       <c r="R78" t="n">
-        <v>6833197</v>
+        <v>6832826</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8313,10 +8308,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845600</v>
+        <v>129845486</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8324,21 +8319,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8348,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406582</v>
+        <v>406350</v>
       </c>
       <c r="R79" t="n">
-        <v>6832826</v>
+        <v>6832772</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8398,22 +8393,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129845420</v>
+        <v>129845606</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8421,21 +8416,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8445,10 +8440,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406424</v>
+        <v>406394</v>
       </c>
       <c r="R80" t="n">
-        <v>6832865</v>
+        <v>6833197</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8495,57 +8490,65 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845415</v>
+        <v>129845465</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>58106</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406317</v>
+        <v>406542</v>
       </c>
       <c r="R81" t="n">
-        <v>6832733</v>
+        <v>6832915</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8604,37 +8607,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845478</v>
+        <v>129845454</v>
       </c>
       <c r="B82" t="n">
-        <v>90975</v>
+        <v>57733</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8642,10 +8650,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406607</v>
+        <v>406675</v>
       </c>
       <c r="R82" t="n">
-        <v>6832929</v>
+        <v>6832988</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8686,7 +8694,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8705,10 +8712,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845454</v>
+        <v>129845621</v>
       </c>
       <c r="B83" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8716,16 +8723,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8738,7 +8745,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8748,10 +8755,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406675</v>
+        <v>406672</v>
       </c>
       <c r="R83" t="n">
-        <v>6832988</v>
+        <v>6832840</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8798,22 +8805,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845621</v>
+        <v>129845647</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8821,42 +8828,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406672</v>
+        <v>406274</v>
       </c>
       <c r="R84" t="n">
-        <v>6832840</v>
+        <v>6832759</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8915,42 +8914,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845465</v>
+        <v>129845444</v>
       </c>
       <c r="B85" t="n">
-        <v>58106</v>
+        <v>91618</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -8958,10 +8952,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406542</v>
+        <v>406601</v>
       </c>
       <c r="R85" t="n">
-        <v>6832915</v>
+        <v>6832858</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9002,6 +8996,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9020,10 +9015,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845444</v>
+        <v>129845423</v>
       </c>
       <c r="B86" t="n">
-        <v>91614</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9031,37 +9026,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406601</v>
+        <v>406531</v>
       </c>
       <c r="R86" t="n">
-        <v>6832858</v>
+        <v>6832868</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9102,7 +9094,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9121,10 +9112,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845647</v>
+        <v>129845656</v>
       </c>
       <c r="B87" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9132,21 +9123,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9156,10 +9147,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406274</v>
+        <v>406480</v>
       </c>
       <c r="R87" t="n">
-        <v>6832759</v>
+        <v>6832777</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9218,54 +9209,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845641</v>
+        <v>129845653</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406618</v>
+        <v>406430</v>
       </c>
       <c r="R88" t="n">
-        <v>6832813</v>
+        <v>6832777</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9306,7 +9288,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9325,10 +9306,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845656</v>
+        <v>129845437</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9336,34 +9317,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406480</v>
+        <v>406331</v>
       </c>
       <c r="R89" t="n">
-        <v>6832777</v>
+        <v>6832676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9404,55 +9388,62 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845437</v>
+        <v>129845641</v>
       </c>
       <c r="B90" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9460,10 +9451,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406331</v>
+        <v>406618</v>
       </c>
       <c r="R90" t="n">
-        <v>6832676</v>
+        <v>6832813</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9511,57 +9502,65 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845423</v>
+        <v>129845464</v>
       </c>
       <c r="B91" t="n">
-        <v>79700</v>
+        <v>58106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406531</v>
+        <v>406416</v>
       </c>
       <c r="R91" t="n">
-        <v>6832868</v>
+        <v>6832880</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9620,10 +9619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845653</v>
+        <v>129845608</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9631,21 +9630,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9655,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406430</v>
+        <v>406399</v>
       </c>
       <c r="R92" t="n">
-        <v>6832777</v>
+        <v>6833177</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9814,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845608</v>
+        <v>129845418</v>
       </c>
       <c r="B94" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9825,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9849,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406399</v>
+        <v>406377</v>
       </c>
       <c r="R94" t="n">
-        <v>6833177</v>
+        <v>6832837</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9899,22 +9898,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845479</v>
+        <v>129845408</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9946,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406408</v>
+        <v>406368</v>
       </c>
       <c r="R95" t="n">
-        <v>6832975</v>
+        <v>6833202</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10008,7 +10007,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845480</v>
+        <v>129845479</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -10043,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406277</v>
+        <v>406408</v>
       </c>
       <c r="R96" t="n">
-        <v>6832823</v>
+        <v>6832975</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10105,10 +10104,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845634</v>
+        <v>129845480</v>
       </c>
       <c r="B97" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10116,42 +10115,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406781</v>
+        <v>406277</v>
       </c>
       <c r="R97" t="n">
-        <v>6832843</v>
+        <v>6832823</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10198,22 +10189,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845457</v>
+        <v>129845634</v>
       </c>
       <c r="B98" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,34 +10212,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406265</v>
+        <v>406781</v>
       </c>
       <c r="R98" t="n">
-        <v>6832808</v>
+        <v>6832843</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10295,65 +10294,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845464</v>
+        <v>129845457</v>
       </c>
       <c r="B99" t="n">
-        <v>58106</v>
+        <v>78839</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406416</v>
+        <v>406265</v>
       </c>
       <c r="R99" t="n">
-        <v>6832880</v>
+        <v>6832808</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10412,7 +10403,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845418</v>
+        <v>129845426</v>
       </c>
       <c r="B100" t="n">
         <v>79700</v>
@@ -10447,10 +10438,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406377</v>
+        <v>406796</v>
       </c>
       <c r="R100" t="n">
-        <v>6832837</v>
+        <v>6832917</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10509,7 +10500,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845408</v>
+        <v>129845407</v>
       </c>
       <c r="B101" t="n">
         <v>79700</v>
@@ -10544,10 +10535,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406368</v>
+        <v>406416</v>
       </c>
       <c r="R101" t="n">
-        <v>6833202</v>
+        <v>6833166</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10606,10 +10597,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845615</v>
+        <v>129845629</v>
       </c>
       <c r="B102" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10617,34 +10608,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406583</v>
+        <v>406618</v>
       </c>
       <c r="R102" t="n">
-        <v>6832911</v>
+        <v>6832773</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10703,10 +10702,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845629</v>
+        <v>129845615</v>
       </c>
       <c r="B103" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10714,42 +10713,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406618</v>
+        <v>406583</v>
       </c>
       <c r="R103" t="n">
-        <v>6832773</v>
+        <v>6832911</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10905,7 +10896,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845426</v>
+        <v>129845597</v>
       </c>
       <c r="B105" t="n">
         <v>79700</v>
@@ -10940,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406796</v>
+        <v>406615</v>
       </c>
       <c r="R105" t="n">
-        <v>6832917</v>
+        <v>6832770</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10990,19 +10981,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845407</v>
+        <v>129845595</v>
       </c>
       <c r="B106" t="n">
         <v>79700</v>
@@ -11037,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406416</v>
+        <v>406455</v>
       </c>
       <c r="R106" t="n">
-        <v>6833166</v>
+        <v>6832823</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11087,22 +11078,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845597</v>
+        <v>129845485</v>
       </c>
       <c r="B107" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11110,21 +11101,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11134,10 +11125,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406615</v>
+        <v>406320</v>
       </c>
       <c r="R107" t="n">
-        <v>6832770</v>
+        <v>6832742</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11184,22 +11175,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845485</v>
+        <v>129845450</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11207,34 +11198,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406320</v>
+        <v>406508</v>
       </c>
       <c r="R108" t="n">
-        <v>6832742</v>
+        <v>6832877</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11293,10 +11292,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845595</v>
+        <v>129845448</v>
       </c>
       <c r="B109" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11304,34 +11303,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406455</v>
+        <v>406396</v>
       </c>
       <c r="R109" t="n">
-        <v>6832823</v>
+        <v>6832853</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11378,12 +11385,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11487,27 +11494,27 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845448</v>
+        <v>129845644</v>
       </c>
       <c r="B111" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11520,7 +11527,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11530,10 +11537,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406396</v>
+        <v>406457</v>
       </c>
       <c r="R111" t="n">
-        <v>6832853</v>
+        <v>6832809</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11580,52 +11587,53 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845450</v>
+        <v>129845640</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11635,10 +11643,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406508</v>
+        <v>406404</v>
       </c>
       <c r="R112" t="n">
-        <v>6832877</v>
+        <v>6832729</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11679,71 +11687,64 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845644</v>
+        <v>129845433</v>
       </c>
       <c r="B113" t="n">
-        <v>58106</v>
+        <v>79671</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406457</v>
+        <v>406438</v>
       </c>
       <c r="R113" t="n">
-        <v>6832809</v>
+        <v>6833114</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11790,19 +11791,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845433</v>
+        <v>129845430</v>
       </c>
       <c r="B114" t="n">
         <v>79671</v>
@@ -11837,10 +11838,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406438</v>
+        <v>406465</v>
       </c>
       <c r="R114" t="n">
-        <v>6833114</v>
+        <v>6833093</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11899,10 +11900,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845430</v>
+        <v>129845421</v>
       </c>
       <c r="B115" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11910,21 +11911,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11934,10 +11935,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406465</v>
+        <v>406500</v>
       </c>
       <c r="R115" t="n">
-        <v>6833093</v>
+        <v>6832933</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11996,54 +11997,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845640</v>
+        <v>129845596</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406404</v>
+        <v>406536</v>
       </c>
       <c r="R116" t="n">
-        <v>6832729</v>
+        <v>6832770</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12084,7 +12076,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12103,10 +12094,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845421</v>
+        <v>129845628</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12114,34 +12105,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406500</v>
+        <v>406541</v>
       </c>
       <c r="R117" t="n">
-        <v>6832933</v>
+        <v>6832823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12188,22 +12187,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845458</v>
+        <v>129845635</v>
       </c>
       <c r="B118" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12211,34 +12210,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406531</v>
+        <v>406677</v>
       </c>
       <c r="R118" t="n">
-        <v>6832927</v>
+        <v>6832986</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12285,22 +12292,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845596</v>
+        <v>129845436</v>
       </c>
       <c r="B119" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12308,21 +12315,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12332,10 +12339,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406536</v>
+        <v>406315</v>
       </c>
       <c r="R119" t="n">
-        <v>6832770</v>
+        <v>6832667</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12382,22 +12389,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845628</v>
+        <v>129845458</v>
       </c>
       <c r="B120" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12405,42 +12412,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406541</v>
+        <v>406531</v>
       </c>
       <c r="R120" t="n">
-        <v>6832823</v>
+        <v>6832927</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12487,22 +12486,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845635</v>
+        <v>129845588</v>
       </c>
       <c r="B121" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12510,42 +12509,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406677</v>
+        <v>406440</v>
       </c>
       <c r="R121" t="n">
-        <v>6832986</v>
+        <v>6833101</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12604,10 +12595,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129845436</v>
+        <v>129845591</v>
       </c>
       <c r="B122" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12615,21 +12606,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12639,10 +12630,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406315</v>
+        <v>406439</v>
       </c>
       <c r="R122" t="n">
-        <v>6832667</v>
+        <v>6833139</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12689,22 +12680,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845494</v>
+        <v>129845432</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12712,21 +12703,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12736,10 +12727,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406710</v>
+        <v>406373</v>
       </c>
       <c r="R123" t="n">
-        <v>6832990</v>
+        <v>6833176</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12798,7 +12789,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845495</v>
+        <v>129845494</v>
       </c>
       <c r="B124" t="n">
         <v>79081</v>
@@ -12833,10 +12824,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406668</v>
+        <v>406710</v>
       </c>
       <c r="R124" t="n">
-        <v>6833007</v>
+        <v>6832990</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12895,10 +12886,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845588</v>
+        <v>129845495</v>
       </c>
       <c r="B125" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12906,21 +12897,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12930,10 +12921,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406440</v>
+        <v>406668</v>
       </c>
       <c r="R125" t="n">
-        <v>6833101</v>
+        <v>6833007</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12980,22 +12971,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845591</v>
+        <v>129845484</v>
       </c>
       <c r="B126" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13003,34 +12994,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406439</v>
+        <v>406310</v>
       </c>
       <c r="R126" t="n">
-        <v>6833139</v>
+        <v>6832729</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13071,28 +13065,29 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845484</v>
+        <v>129845451</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13100,26 +13095,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406310</v>
+        <v>406595</v>
       </c>
       <c r="R127" t="n">
-        <v>6832729</v>
+        <v>6832931</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13171,7 +13171,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13190,45 +13189,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845432</v>
+        <v>129845623</v>
       </c>
       <c r="B128" t="n">
-        <v>79671</v>
+        <v>56926</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406373</v>
+        <v>406310</v>
       </c>
       <c r="R128" t="n">
-        <v>6833176</v>
+        <v>6832901</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13275,60 +13282,57 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845497</v>
+        <v>129845414</v>
       </c>
       <c r="B129" t="n">
-        <v>92016</v>
+        <v>79700</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4217</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406271</v>
+        <v>406313</v>
       </c>
       <c r="R129" t="n">
-        <v>6832633</v>
+        <v>6832656</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13369,7 +13373,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13388,10 +13391,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129845451</v>
+        <v>129845411</v>
       </c>
       <c r="B130" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13399,42 +13402,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406595</v>
+        <v>406442</v>
       </c>
       <c r="R130" t="n">
-        <v>6832931</v>
+        <v>6833040</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13493,10 +13488,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845489</v>
+        <v>129845603</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13504,21 +13499,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13528,10 +13523,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406542</v>
+        <v>406764</v>
       </c>
       <c r="R131" t="n">
-        <v>6832915</v>
+        <v>6832925</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13578,22 +13573,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845482</v>
+        <v>129845424</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13601,21 +13596,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13625,10 +13620,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406282</v>
+        <v>406533</v>
       </c>
       <c r="R132" t="n">
-        <v>6832624</v>
+        <v>6832861</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13687,10 +13682,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845603</v>
+        <v>129845489</v>
       </c>
       <c r="B133" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13698,21 +13693,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13722,10 +13717,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406764</v>
+        <v>406542</v>
       </c>
       <c r="R133" t="n">
-        <v>6832925</v>
+        <v>6832915</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13772,22 +13767,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845414</v>
+        <v>129845658</v>
       </c>
       <c r="B134" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13795,21 +13790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13819,10 +13814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406313</v>
+        <v>406563</v>
       </c>
       <c r="R134" t="n">
-        <v>6832656</v>
+        <v>6832887</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13869,22 +13864,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845411</v>
+        <v>129845482</v>
       </c>
       <c r="B135" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13892,21 +13887,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13916,10 +13911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406442</v>
+        <v>406282</v>
       </c>
       <c r="R135" t="n">
-        <v>6833040</v>
+        <v>6832624</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13978,10 +13973,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845658</v>
+        <v>129845453</v>
       </c>
       <c r="B136" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13989,34 +13984,42 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406563</v>
+        <v>406716</v>
       </c>
       <c r="R136" t="n">
-        <v>6832887</v>
+        <v>6832970</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14063,44 +14066,44 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129845623</v>
+        <v>129845446</v>
       </c>
       <c r="B137" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14108,7 +14111,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -14118,10 +14121,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>406310</v>
+        <v>406393</v>
       </c>
       <c r="R137" t="n">
-        <v>6832901</v>
+        <v>6833110</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14168,57 +14171,60 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129845424</v>
+        <v>129845478</v>
       </c>
       <c r="B138" t="n">
-        <v>79700</v>
+        <v>90979</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>406533</v>
+        <v>406607</v>
       </c>
       <c r="R138" t="n">
-        <v>6832861</v>
+        <v>6832929</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14253,14 +14259,30 @@
           <t>2025-11-25</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Substrat: Tallåga</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Tallåga</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -14277,42 +14299,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129845453</v>
+        <v>129845497</v>
       </c>
       <c r="B139" t="n">
-        <v>57733</v>
+        <v>92020</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14320,10 +14337,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>406716</v>
+        <v>406271</v>
       </c>
       <c r="R139" t="n">
-        <v>6832970</v>
+        <v>6832633</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14358,14 +14375,25 @@
           <t>2025-11-25</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Substrat: Tallåga</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845599</v>
+        <v>129845438</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406635</v>
+        <v>406361</v>
       </c>
       <c r="R2" t="n">
-        <v>6832779</v>
+        <v>6832815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845598</v>
+        <v>129845441</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406626</v>
+        <v>406638</v>
       </c>
       <c r="R3" t="n">
-        <v>6832781</v>
+        <v>6832869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845425</v>
+        <v>129845598</v>
       </c>
       <c r="B4" t="n">
         <v>79700</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406832</v>
+        <v>406626</v>
       </c>
       <c r="R4" t="n">
-        <v>6832816</v>
+        <v>6832781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845419</v>
+        <v>129845599</v>
       </c>
       <c r="B5" t="n">
         <v>79700</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406387</v>
+        <v>406635</v>
       </c>
       <c r="R5" t="n">
-        <v>6832850</v>
+        <v>6832779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845438</v>
+        <v>129845425</v>
       </c>
       <c r="B6" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406361</v>
+        <v>406832</v>
       </c>
       <c r="R6" t="n">
-        <v>6832815</v>
+        <v>6832816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845441</v>
+        <v>129845419</v>
       </c>
       <c r="B7" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406638</v>
+        <v>406387</v>
       </c>
       <c r="R7" t="n">
-        <v>6832869</v>
+        <v>6832850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845630</v>
+        <v>129845427</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406631</v>
+        <v>406794</v>
       </c>
       <c r="R8" t="n">
-        <v>6832822</v>
+        <v>6832934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845443</v>
+        <v>129845417</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406333</v>
+        <v>406346</v>
       </c>
       <c r="R9" t="n">
-        <v>6832733</v>
+        <v>6832798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845427</v>
+        <v>129845630</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,34 +1559,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406794</v>
+        <v>406631</v>
       </c>
       <c r="R11" t="n">
-        <v>6832934</v>
+        <v>6832822</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,22 +1641,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845417</v>
+        <v>129845443</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,34 +1664,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406346</v>
+        <v>406333</v>
       </c>
       <c r="R12" t="n">
-        <v>6832798</v>
+        <v>6832733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,54 +1758,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845462</v>
+        <v>129845655</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406713</v>
+        <v>406473</v>
       </c>
       <c r="R13" t="n">
-        <v>6832904</v>
+        <v>6832798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,29 +1837,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845610</v>
+        <v>129845604</v>
       </c>
       <c r="B14" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1876,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1900,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406262</v>
+        <v>406424</v>
       </c>
       <c r="R14" t="n">
-        <v>6832854</v>
+        <v>6832657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845614</v>
+        <v>129845467</v>
       </c>
       <c r="B15" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,34 +1963,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406492</v>
+        <v>406359</v>
       </c>
       <c r="R15" t="n">
-        <v>6832753</v>
+        <v>6832764</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,63 +2034,73 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845618</v>
+        <v>129845462</v>
       </c>
       <c r="B16" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406791</v>
+        <v>406713</v>
       </c>
       <c r="R16" t="n">
-        <v>6832845</v>
+        <v>6832904</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,25 +2141,26 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845429</v>
+        <v>129845610</v>
       </c>
       <c r="B17" t="n">
         <v>79671</v>
@@ -2191,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406472</v>
+        <v>406262</v>
       </c>
       <c r="R17" t="n">
-        <v>6833103</v>
+        <v>6832854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,19 +2245,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845613</v>
+        <v>129845614</v>
       </c>
       <c r="B18" t="n">
         <v>79671</v>
@@ -2288,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406388</v>
+        <v>406492</v>
       </c>
       <c r="R18" t="n">
-        <v>6832683</v>
+        <v>6832753</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2350,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845617</v>
+        <v>129845618</v>
       </c>
       <c r="B19" t="n">
         <v>79671</v>
@@ -2385,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406626</v>
+        <v>406791</v>
       </c>
       <c r="R19" t="n">
-        <v>6832781</v>
+        <v>6832845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845604</v>
+        <v>129845429</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2458,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406424</v>
+        <v>406472</v>
       </c>
       <c r="R20" t="n">
-        <v>6832657</v>
+        <v>6833103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,22 +2536,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845467</v>
+        <v>129845613</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,37 +2559,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406359</v>
+        <v>406388</v>
       </c>
       <c r="R21" t="n">
-        <v>6832764</v>
+        <v>6832683</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2626,29 +2627,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845655</v>
+        <v>129845617</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406473</v>
+        <v>406626</v>
       </c>
       <c r="R22" t="n">
-        <v>6832798</v>
+        <v>6832781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129845619</v>
+        <v>129845488</v>
       </c>
       <c r="B23" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2753,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406776</v>
+        <v>406528</v>
       </c>
       <c r="R23" t="n">
-        <v>6832860</v>
+        <v>6832873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,19 +2827,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129845488</v>
+        <v>129845652</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406528</v>
+        <v>406408</v>
       </c>
       <c r="R24" t="n">
-        <v>6832873</v>
+        <v>6832778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,19 +2924,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129845652</v>
+        <v>129845659</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406408</v>
+        <v>406556</v>
       </c>
       <c r="R25" t="n">
-        <v>6832778</v>
+        <v>6832846</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845659</v>
+        <v>129845422</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406556</v>
+        <v>406513</v>
       </c>
       <c r="R26" t="n">
-        <v>6832846</v>
+        <v>6832869</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3118,57 +3118,66 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845422</v>
+        <v>129845460</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406513</v>
+        <v>406431</v>
       </c>
       <c r="R27" t="n">
-        <v>6832869</v>
+        <v>6832825</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3209,6 +3218,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3227,10 +3237,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129845413</v>
+        <v>129845619</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3248,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3272,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406266</v>
+        <v>406776</v>
       </c>
       <c r="R28" t="n">
-        <v>6832827</v>
+        <v>6832860</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3312,66 +3322,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129845460</v>
+        <v>129845413</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406431</v>
+        <v>406266</v>
       </c>
       <c r="R29" t="n">
-        <v>6832825</v>
+        <v>6832827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,7 +3413,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845636</v>
+        <v>129845412</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,42 +3442,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406595</v>
+        <v>406426</v>
       </c>
       <c r="R30" t="n">
-        <v>6833001</v>
+        <v>6832990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3524,12 +3516,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3641,10 +3633,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845412</v>
+        <v>129845636</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3652,34 +3644,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406426</v>
+        <v>406595</v>
       </c>
       <c r="R32" t="n">
-        <v>6832990</v>
+        <v>6833001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,12 +3726,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845481</v>
+        <v>129845455</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406278</v>
+        <v>406486</v>
       </c>
       <c r="R35" t="n">
-        <v>6832795</v>
+        <v>6833057</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845483</v>
+        <v>129845481</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406344</v>
+        <v>406278</v>
       </c>
       <c r="R36" t="n">
-        <v>6832706</v>
+        <v>6832795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845657</v>
+        <v>129845483</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406495</v>
+        <v>406344</v>
       </c>
       <c r="R37" t="n">
-        <v>6832766</v>
+        <v>6832706</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,22 +4221,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845592</v>
+        <v>129845657</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406370</v>
+        <v>406495</v>
       </c>
       <c r="R38" t="n">
-        <v>6832711</v>
+        <v>6832766</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129845455</v>
+        <v>129845592</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406486</v>
+        <v>406370</v>
       </c>
       <c r="R39" t="n">
-        <v>6833057</v>
+        <v>6832711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,19 +4415,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845490</v>
+        <v>129845491</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406560</v>
+        <v>406588</v>
       </c>
       <c r="R40" t="n">
-        <v>6832885</v>
+        <v>6832866</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4524,7 +4524,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845491</v>
+        <v>129845490</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406588</v>
+        <v>406560</v>
       </c>
       <c r="R41" t="n">
-        <v>6832866</v>
+        <v>6832885</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845611</v>
+        <v>129845601</v>
       </c>
       <c r="B44" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406276</v>
+        <v>406583</v>
       </c>
       <c r="R44" t="n">
-        <v>6832761</v>
+        <v>6832841</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845431</v>
+        <v>129845631</v>
       </c>
       <c r="B45" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,34 +4927,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406368</v>
+        <v>406698</v>
       </c>
       <c r="R45" t="n">
-        <v>6833201</v>
+        <v>6832875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,22 +5009,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845601</v>
+        <v>129845611</v>
       </c>
       <c r="B46" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5024,21 +5032,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5048,10 +5056,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406583</v>
+        <v>406276</v>
       </c>
       <c r="R46" t="n">
-        <v>6832841</v>
+        <v>6832761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5110,10 +5118,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845456</v>
+        <v>129845431</v>
       </c>
       <c r="B47" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5121,21 +5129,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5145,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406442</v>
+        <v>406368</v>
       </c>
       <c r="R47" t="n">
-        <v>6833041</v>
+        <v>6833201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5207,10 +5215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845631</v>
+        <v>129845456</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5218,42 +5226,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406698</v>
+        <v>406442</v>
       </c>
       <c r="R48" t="n">
-        <v>6832875</v>
+        <v>6833041</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5300,66 +5300,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845461</v>
+        <v>129845589</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406589</v>
+        <v>406406</v>
       </c>
       <c r="R49" t="n">
-        <v>6832990</v>
+        <v>6833199</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5400,29 +5391,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845624</v>
+        <v>129845416</v>
       </c>
       <c r="B50" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5430,39 +5420,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406494</v>
+        <v>406362</v>
       </c>
       <c r="R50" t="n">
         <v>6832766</v>
@@ -5512,22 +5494,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845638</v>
+        <v>129845626</v>
       </c>
       <c r="B51" t="n">
-        <v>78839</v>
+        <v>91620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5535,34 +5517,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406290</v>
+        <v>406533</v>
       </c>
       <c r="R51" t="n">
-        <v>6832900</v>
+        <v>6832761</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5603,6 +5592,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5621,10 +5611,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845612</v>
+        <v>129845624</v>
       </c>
       <c r="B52" t="n">
-        <v>79671</v>
+        <v>57896</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,34 +5622,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406379</v>
+        <v>406494</v>
       </c>
       <c r="R52" t="n">
-        <v>6832756</v>
+        <v>6832766</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5718,41 +5716,43 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845626</v>
+        <v>129845461</v>
       </c>
       <c r="B53" t="n">
-        <v>91618</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406533</v>
+        <v>406589</v>
       </c>
       <c r="R53" t="n">
-        <v>6832761</v>
+        <v>6832990</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5811,22 +5811,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845416</v>
+        <v>129845612</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406362</v>
+        <v>406379</v>
       </c>
       <c r="R54" t="n">
-        <v>6832766</v>
+        <v>6832756</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5908,22 +5908,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845589</v>
+        <v>129845638</v>
       </c>
       <c r="B55" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406406</v>
+        <v>406290</v>
       </c>
       <c r="R55" t="n">
-        <v>6833199</v>
+        <v>6832900</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845632</v>
+        <v>129845627</v>
       </c>
       <c r="B56" t="n">
         <v>57733</v>
@@ -6050,7 +6050,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406667</v>
+        <v>406539</v>
       </c>
       <c r="R56" t="n">
-        <v>6832849</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6227,7 +6227,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845627</v>
+        <v>129845632</v>
       </c>
       <c r="B58" t="n">
         <v>57733</v>
@@ -6260,7 +6260,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406539</v>
+        <v>406667</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832849</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6332,43 +6332,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845459</v>
+        <v>129845625</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>91620</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6376,10 +6374,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406331</v>
+        <v>406472</v>
       </c>
       <c r="R59" t="n">
-        <v>6832715</v>
+        <v>6832767</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6427,22 +6425,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845435</v>
+        <v>129845487</v>
       </c>
       <c r="B60" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6450,21 +6448,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6474,10 +6472,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406455</v>
+        <v>406409</v>
       </c>
       <c r="R60" t="n">
-        <v>6833027</v>
+        <v>6832824</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6827,41 +6825,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845625</v>
+        <v>129845459</v>
       </c>
       <c r="B64" t="n">
-        <v>91618</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406472</v>
+        <v>406331</v>
       </c>
       <c r="R64" t="n">
-        <v>6832767</v>
+        <v>6832715</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6920,22 +6920,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845487</v>
+        <v>129845435</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,21 +6943,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406409</v>
+        <v>406455</v>
       </c>
       <c r="R65" t="n">
-        <v>6832824</v>
+        <v>6833027</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,45 +7029,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845654</v>
+        <v>129845642</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406460</v>
+        <v>406547</v>
       </c>
       <c r="R66" t="n">
-        <v>6832823</v>
+        <v>6832775</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7108,6 +7117,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7126,10 +7136,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845493</v>
+        <v>129845452</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7137,34 +7147,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406785</v>
+        <v>406630</v>
       </c>
       <c r="R67" t="n">
-        <v>6832912</v>
+        <v>6832941</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7223,10 +7241,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845452</v>
+        <v>129845434</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7234,42 +7252,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406630</v>
+        <v>406499</v>
       </c>
       <c r="R68" t="n">
-        <v>6832941</v>
+        <v>6833054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7328,54 +7338,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845642</v>
+        <v>129845654</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406547</v>
+        <v>406460</v>
       </c>
       <c r="R69" t="n">
-        <v>6832775</v>
+        <v>6832823</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7416,7 +7417,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845434</v>
+        <v>129845493</v>
       </c>
       <c r="B70" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7446,21 +7446,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406499</v>
+        <v>406785</v>
       </c>
       <c r="R70" t="n">
-        <v>6833054</v>
+        <v>6832912</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7532,10 +7532,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845440</v>
+        <v>129845593</v>
       </c>
       <c r="B71" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,21 +7543,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406445</v>
+        <v>406451</v>
       </c>
       <c r="R71" t="n">
-        <v>6832921</v>
+        <v>6832712</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7617,22 +7617,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845605</v>
+        <v>129845590</v>
       </c>
       <c r="B72" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,21 +7640,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406440</v>
+        <v>406421</v>
       </c>
       <c r="R72" t="n">
-        <v>6833100</v>
+        <v>6833142</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7726,7 +7726,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845607</v>
+        <v>129845440</v>
       </c>
       <c r="B73" t="n">
         <v>79671</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406407</v>
+        <v>406445</v>
       </c>
       <c r="R73" t="n">
-        <v>6833199</v>
+        <v>6832921</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7811,22 +7811,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845590</v>
+        <v>129845605</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,21 +7834,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406421</v>
+        <v>406440</v>
       </c>
       <c r="R74" t="n">
-        <v>6833142</v>
+        <v>6833100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7920,10 +7920,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845593</v>
+        <v>129845607</v>
       </c>
       <c r="B75" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,21 +7931,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406451</v>
+        <v>406407</v>
       </c>
       <c r="R75" t="n">
-        <v>6832712</v>
+        <v>6833199</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8017,10 +8017,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129845420</v>
+        <v>129845486</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,21 +8028,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406424</v>
+        <v>406350</v>
       </c>
       <c r="R76" t="n">
-        <v>6832865</v>
+        <v>6832772</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845415</v>
+        <v>129845606</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406317</v>
+        <v>406394</v>
       </c>
       <c r="R77" t="n">
-        <v>6832733</v>
+        <v>6833197</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8199,19 +8199,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845600</v>
+        <v>129845415</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406582</v>
+        <v>406317</v>
       </c>
       <c r="R78" t="n">
-        <v>6832826</v>
+        <v>6832733</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8296,22 +8296,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845486</v>
+        <v>129845600</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406350</v>
+        <v>406582</v>
       </c>
       <c r="R79" t="n">
-        <v>6832772</v>
+        <v>6832826</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8393,22 +8393,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129845606</v>
+        <v>129845420</v>
       </c>
       <c r="B80" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406394</v>
+        <v>406424</v>
       </c>
       <c r="R80" t="n">
-        <v>6833197</v>
+        <v>6832865</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8490,39 +8490,39 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845465</v>
+        <v>129845454</v>
       </c>
       <c r="B81" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8535,7 +8535,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406542</v>
+        <v>406675</v>
       </c>
       <c r="R81" t="n">
-        <v>6832915</v>
+        <v>6832988</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845454</v>
+        <v>129845621</v>
       </c>
       <c r="B82" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8618,16 +8618,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8640,7 +8640,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406675</v>
+        <v>406672</v>
       </c>
       <c r="R82" t="n">
-        <v>6832988</v>
+        <v>6832840</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8700,39 +8700,39 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845621</v>
+        <v>129845465</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>58106</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8745,7 +8745,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406672</v>
+        <v>406542</v>
       </c>
       <c r="R83" t="n">
-        <v>6832840</v>
+        <v>6832915</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8805,22 +8805,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845647</v>
+        <v>129845444</v>
       </c>
       <c r="B84" t="n">
-        <v>78838</v>
+        <v>91620</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8828,34 +8828,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406274</v>
+        <v>406601</v>
       </c>
       <c r="R84" t="n">
-        <v>6832759</v>
+        <v>6832858</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8896,28 +8899,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845444</v>
+        <v>129845647</v>
       </c>
       <c r="B85" t="n">
-        <v>91618</v>
+        <v>78838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8925,37 +8929,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406601</v>
+        <v>406274</v>
       </c>
       <c r="R85" t="n">
-        <v>6832858</v>
+        <v>6832759</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8996,19 +8997,18 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9514,53 +9514,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845464</v>
+        <v>129845479</v>
       </c>
       <c r="B91" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406416</v>
+        <v>406408</v>
       </c>
       <c r="R91" t="n">
-        <v>6832880</v>
+        <v>6832975</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,10 +9611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845608</v>
+        <v>129845480</v>
       </c>
       <c r="B92" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9630,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9654,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406399</v>
+        <v>406277</v>
       </c>
       <c r="R92" t="n">
-        <v>6833177</v>
+        <v>6832823</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9704,19 +9696,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845594</v>
+        <v>129845418</v>
       </c>
       <c r="B93" t="n">
         <v>79700</v>
@@ -9751,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406506</v>
+        <v>406377</v>
       </c>
       <c r="R93" t="n">
-        <v>6832725</v>
+        <v>6832837</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9801,19 +9793,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845418</v>
+        <v>129845594</v>
       </c>
       <c r="B94" t="n">
         <v>79700</v>
@@ -9848,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406377</v>
+        <v>406506</v>
       </c>
       <c r="R94" t="n">
-        <v>6832837</v>
+        <v>6832725</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9898,12 +9890,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10007,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845479</v>
+        <v>129845634</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,34 +10010,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406408</v>
+        <v>406781</v>
       </c>
       <c r="R96" t="n">
-        <v>6832975</v>
+        <v>6832843</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10092,57 +10092,65 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845480</v>
+        <v>129845464</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>58106</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406277</v>
+        <v>406416</v>
       </c>
       <c r="R97" t="n">
-        <v>6832823</v>
+        <v>6832880</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,10 +10209,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845634</v>
+        <v>129845608</v>
       </c>
       <c r="B98" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10212,42 +10220,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406781</v>
+        <v>406399</v>
       </c>
       <c r="R98" t="n">
-        <v>6832843</v>
+        <v>6833177</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10597,10 +10597,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845629</v>
+        <v>129845646</v>
       </c>
       <c r="B102" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,42 +10608,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406618</v>
+        <v>406290</v>
       </c>
       <c r="R102" t="n">
-        <v>6832773</v>
+        <v>6832901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10702,10 +10694,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845615</v>
+        <v>129845629</v>
       </c>
       <c r="B103" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10713,34 +10705,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406583</v>
+        <v>406618</v>
       </c>
       <c r="R103" t="n">
-        <v>6832911</v>
+        <v>6832773</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10799,10 +10799,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845646</v>
+        <v>129845615</v>
       </c>
       <c r="B104" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406290</v>
+        <v>406583</v>
       </c>
       <c r="R104" t="n">
-        <v>6832901</v>
+        <v>6832911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845485</v>
+        <v>129845448</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,34 +11101,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406320</v>
+        <v>406396</v>
       </c>
       <c r="R107" t="n">
-        <v>6832742</v>
+        <v>6832853</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11292,10 +11300,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845448</v>
+        <v>129845439</v>
       </c>
       <c r="B109" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11303,42 +11311,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406396</v>
+        <v>406377</v>
       </c>
       <c r="R109" t="n">
-        <v>6832853</v>
+        <v>6832840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11397,10 +11397,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845439</v>
+        <v>129845485</v>
       </c>
       <c r="B110" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11408,21 +11408,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406377</v>
+        <v>406320</v>
       </c>
       <c r="R110" t="n">
-        <v>6832840</v>
+        <v>6832742</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11494,53 +11494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845644</v>
+        <v>129845421</v>
       </c>
       <c r="B111" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406457</v>
+        <v>406500</v>
       </c>
       <c r="R111" t="n">
-        <v>6832809</v>
+        <v>6832933</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11587,66 +11579,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845640</v>
+        <v>129845433</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406404</v>
+        <v>406438</v>
       </c>
       <c r="R112" t="n">
-        <v>6832729</v>
+        <v>6833114</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11687,64 +11670,71 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845433</v>
+        <v>129845644</v>
       </c>
       <c r="B113" t="n">
-        <v>79671</v>
+        <v>58106</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406438</v>
+        <v>406457</v>
       </c>
       <c r="R113" t="n">
-        <v>6833114</v>
+        <v>6832809</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11791,57 +11781,66 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845430</v>
+        <v>129845640</v>
       </c>
       <c r="B114" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406465</v>
+        <v>406404</v>
       </c>
       <c r="R114" t="n">
-        <v>6833093</v>
+        <v>6832729</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11882,28 +11881,29 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845421</v>
+        <v>129845430</v>
       </c>
       <c r="B115" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11911,21 +11911,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406500</v>
+        <v>406465</v>
       </c>
       <c r="R115" t="n">
-        <v>6832933</v>
+        <v>6833093</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845628</v>
+        <v>129845458</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12105,42 +12105,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406541</v>
+        <v>406531</v>
       </c>
       <c r="R117" t="n">
-        <v>6832823</v>
+        <v>6832927</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12187,12 +12179,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12304,10 +12296,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845436</v>
+        <v>129845628</v>
       </c>
       <c r="B119" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12315,34 +12307,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406315</v>
+        <v>406541</v>
       </c>
       <c r="R119" t="n">
-        <v>6832667</v>
+        <v>6832823</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12389,22 +12389,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845458</v>
+        <v>129845436</v>
       </c>
       <c r="B120" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406531</v>
+        <v>406315</v>
       </c>
       <c r="R120" t="n">
-        <v>6832927</v>
+        <v>6832667</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12498,10 +12498,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845588</v>
+        <v>129845494</v>
       </c>
       <c r="B121" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12509,21 +12509,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12533,10 +12533,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406440</v>
+        <v>406710</v>
       </c>
       <c r="R121" t="n">
-        <v>6833101</v>
+        <v>6832990</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12583,22 +12583,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129845591</v>
+        <v>129845495</v>
       </c>
       <c r="B122" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12606,21 +12606,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406439</v>
+        <v>406668</v>
       </c>
       <c r="R122" t="n">
-        <v>6833139</v>
+        <v>6833007</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12680,22 +12680,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845432</v>
+        <v>129845484</v>
       </c>
       <c r="B123" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12703,34 +12703,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406373</v>
+        <v>406310</v>
       </c>
       <c r="R123" t="n">
-        <v>6833176</v>
+        <v>6832729</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12771,6 +12774,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12789,10 +12793,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845494</v>
+        <v>129845591</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12800,21 +12804,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12824,10 +12828,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406710</v>
+        <v>406439</v>
       </c>
       <c r="R124" t="n">
-        <v>6832990</v>
+        <v>6833139</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12874,22 +12878,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845495</v>
+        <v>129845588</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12897,21 +12901,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12921,10 +12925,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406668</v>
+        <v>406440</v>
       </c>
       <c r="R125" t="n">
-        <v>6833007</v>
+        <v>6833101</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12971,22 +12975,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845484</v>
+        <v>129845432</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12994,37 +12998,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406310</v>
+        <v>406373</v>
       </c>
       <c r="R126" t="n">
-        <v>6832729</v>
+        <v>6833176</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13065,7 +13066,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13189,53 +13189,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845623</v>
+        <v>129845489</v>
       </c>
       <c r="B128" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406310</v>
+        <v>406542</v>
       </c>
       <c r="R128" t="n">
-        <v>6832901</v>
+        <v>6832915</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13282,22 +13274,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845414</v>
+        <v>129845658</v>
       </c>
       <c r="B129" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13305,21 +13297,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13329,10 +13321,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406313</v>
+        <v>406563</v>
       </c>
       <c r="R129" t="n">
-        <v>6832656</v>
+        <v>6832887</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13379,22 +13371,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129845411</v>
+        <v>129845482</v>
       </c>
       <c r="B130" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13402,21 +13394,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13426,10 +13418,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406442</v>
+        <v>406282</v>
       </c>
       <c r="R130" t="n">
-        <v>6833040</v>
+        <v>6832624</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13488,7 +13480,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845603</v>
+        <v>129845411</v>
       </c>
       <c r="B131" t="n">
         <v>79700</v>
@@ -13523,10 +13515,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406764</v>
+        <v>406442</v>
       </c>
       <c r="R131" t="n">
-        <v>6832925</v>
+        <v>6833040</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13573,19 +13565,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845424</v>
+        <v>129845414</v>
       </c>
       <c r="B132" t="n">
         <v>79700</v>
@@ -13620,10 +13612,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406533</v>
+        <v>406313</v>
       </c>
       <c r="R132" t="n">
-        <v>6832861</v>
+        <v>6832656</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13682,10 +13674,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845489</v>
+        <v>129845603</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13693,21 +13685,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13717,10 +13709,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406542</v>
+        <v>406764</v>
       </c>
       <c r="R133" t="n">
-        <v>6832915</v>
+        <v>6832925</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13767,22 +13759,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845658</v>
+        <v>129845424</v>
       </c>
       <c r="B134" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13790,21 +13782,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13814,10 +13806,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406563</v>
+        <v>406533</v>
       </c>
       <c r="R134" t="n">
-        <v>6832887</v>
+        <v>6832861</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13864,22 +13856,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845482</v>
+        <v>129845453</v>
       </c>
       <c r="B135" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13887,34 +13879,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406282</v>
+        <v>406716</v>
       </c>
       <c r="R135" t="n">
-        <v>6832624</v>
+        <v>6832970</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13973,32 +13973,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845453</v>
+        <v>129845623</v>
       </c>
       <c r="B136" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -14016,10 +14016,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406716</v>
+        <v>406310</v>
       </c>
       <c r="R136" t="n">
-        <v>6832970</v>
+        <v>6832901</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14186,7 +14186,7 @@
         <v>129845478</v>
       </c>
       <c r="B138" t="n">
-        <v>90979</v>
+        <v>90981</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>129845497</v>
       </c>
       <c r="B139" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845438</v>
+        <v>129845598</v>
       </c>
       <c r="B2" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406361</v>
+        <v>406626</v>
       </c>
       <c r="R2" t="n">
-        <v>6832815</v>
+        <v>6832781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845441</v>
+        <v>129845599</v>
       </c>
       <c r="B3" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406638</v>
+        <v>406635</v>
       </c>
       <c r="R3" t="n">
-        <v>6832869</v>
+        <v>6832779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845598</v>
+        <v>129845425</v>
       </c>
       <c r="B4" t="n">
         <v>79700</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406626</v>
+        <v>406832</v>
       </c>
       <c r="R4" t="n">
-        <v>6832781</v>
+        <v>6832816</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845599</v>
+        <v>129845419</v>
       </c>
       <c r="B5" t="n">
         <v>79700</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406635</v>
+        <v>406387</v>
       </c>
       <c r="R5" t="n">
-        <v>6832779</v>
+        <v>6832850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845425</v>
+        <v>129845438</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406832</v>
+        <v>406361</v>
       </c>
       <c r="R6" t="n">
-        <v>6832816</v>
+        <v>6832815</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845419</v>
+        <v>129845441</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406387</v>
+        <v>406638</v>
       </c>
       <c r="R7" t="n">
-        <v>6832850</v>
+        <v>6832869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845661</v>
+        <v>129845630</v>
       </c>
       <c r="B10" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406352</v>
+        <v>406631</v>
       </c>
       <c r="R10" t="n">
-        <v>6832709</v>
+        <v>6832822</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845630</v>
+        <v>129845443</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1581,7 +1589,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1591,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406631</v>
+        <v>406333</v>
       </c>
       <c r="R11" t="n">
-        <v>6832822</v>
+        <v>6832733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,22 +1649,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845443</v>
+        <v>129845661</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>78747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,42 +1672,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406333</v>
+        <v>406352</v>
       </c>
       <c r="R12" t="n">
-        <v>6832733</v>
+        <v>6832709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,22 +1746,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845655</v>
+        <v>129845429</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406473</v>
+        <v>406472</v>
       </c>
       <c r="R13" t="n">
-        <v>6832798</v>
+        <v>6833103</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,22 +1843,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845604</v>
+        <v>129845467</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,34 +1866,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406424</v>
+        <v>406359</v>
       </c>
       <c r="R14" t="n">
-        <v>6832657</v>
+        <v>6832764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,28 +1937,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845467</v>
+        <v>129845610</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,37 +1967,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406359</v>
+        <v>406262</v>
       </c>
       <c r="R15" t="n">
-        <v>6832764</v>
+        <v>6832854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2034,73 +2035,63 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845462</v>
+        <v>129845618</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406713</v>
+        <v>406791</v>
       </c>
       <c r="R16" t="n">
-        <v>6832904</v>
+        <v>6832845</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,26 +2132,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845610</v>
+        <v>129845617</v>
       </c>
       <c r="B17" t="n">
         <v>79671</v>
@@ -2195,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406262</v>
+        <v>406626</v>
       </c>
       <c r="R17" t="n">
-        <v>6832854</v>
+        <v>6832781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845614</v>
+        <v>129845655</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2292,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406492</v>
+        <v>406473</v>
       </c>
       <c r="R18" t="n">
-        <v>6832753</v>
+        <v>6832798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845618</v>
+        <v>129845604</v>
       </c>
       <c r="B19" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406791</v>
+        <v>406424</v>
       </c>
       <c r="R19" t="n">
-        <v>6832845</v>
+        <v>6832657</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2441,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845429</v>
+        <v>129845614</v>
       </c>
       <c r="B20" t="n">
         <v>79671</v>
@@ -2486,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406472</v>
+        <v>406492</v>
       </c>
       <c r="R20" t="n">
-        <v>6833103</v>
+        <v>6832753</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,12 +2526,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,45 +2635,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845617</v>
+        <v>129845462</v>
       </c>
       <c r="B22" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406626</v>
+        <v>406713</v>
       </c>
       <c r="R22" t="n">
-        <v>6832781</v>
+        <v>6832904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2724,18 +2723,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845412</v>
+        <v>129845639</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406426</v>
+        <v>406276</v>
       </c>
       <c r="R30" t="n">
-        <v>6832990</v>
+        <v>6832761</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3516,22 +3516,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845449</v>
+        <v>129845412</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,42 +3539,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406498</v>
+        <v>406426</v>
       </c>
       <c r="R31" t="n">
-        <v>6832913</v>
+        <v>6832990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3633,7 +3625,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845636</v>
+        <v>129845449</v>
       </c>
       <c r="B32" t="n">
         <v>57733</v>
@@ -3666,7 +3658,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3676,10 +3668,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406595</v>
+        <v>406498</v>
       </c>
       <c r="R32" t="n">
-        <v>6833001</v>
+        <v>6832913</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,53 +3718,52 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845463</v>
+        <v>129845636</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3782,10 +3773,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406746</v>
+        <v>406595</v>
       </c>
       <c r="R33" t="n">
-        <v>6832985</v>
+        <v>6833001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3826,64 +3817,72 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845639</v>
+        <v>129845463</v>
       </c>
       <c r="B34" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406276</v>
+        <v>406746</v>
       </c>
       <c r="R34" t="n">
-        <v>6832761</v>
+        <v>6832985</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3924,28 +3923,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845455</v>
+        <v>129845481</v>
       </c>
       <c r="B35" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406486</v>
+        <v>406278</v>
       </c>
       <c r="R35" t="n">
-        <v>6833057</v>
+        <v>6832795</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845481</v>
+        <v>129845483</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406278</v>
+        <v>406344</v>
       </c>
       <c r="R36" t="n">
-        <v>6832795</v>
+        <v>6832706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845483</v>
+        <v>129845657</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406344</v>
+        <v>406495</v>
       </c>
       <c r="R37" t="n">
-        <v>6832706</v>
+        <v>6832766</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,22 +4221,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845657</v>
+        <v>129845592</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406495</v>
+        <v>406370</v>
       </c>
       <c r="R38" t="n">
-        <v>6832766</v>
+        <v>6832711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129845592</v>
+        <v>129845455</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406370</v>
+        <v>406486</v>
       </c>
       <c r="R39" t="n">
-        <v>6832711</v>
+        <v>6833057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,12 +4415,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5506,10 +5506,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845626</v>
+        <v>129845624</v>
       </c>
       <c r="B51" t="n">
-        <v>91620</v>
+        <v>57896</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5517,30 +5517,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5548,10 +5549,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406533</v>
+        <v>406494</v>
       </c>
       <c r="R51" t="n">
-        <v>6832761</v>
+        <v>6832766</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5592,7 +5593,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5611,10 +5611,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845624</v>
+        <v>129845612</v>
       </c>
       <c r="B52" t="n">
-        <v>57896</v>
+        <v>79671</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5622,42 +5622,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406494</v>
+        <v>406379</v>
       </c>
       <c r="R52" t="n">
-        <v>6832766</v>
+        <v>6832756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5716,54 +5708,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845461</v>
+        <v>129845638</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406589</v>
+        <v>406290</v>
       </c>
       <c r="R53" t="n">
-        <v>6832990</v>
+        <v>6832900</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5804,29 +5787,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845612</v>
+        <v>129845626</v>
       </c>
       <c r="B54" t="n">
-        <v>79671</v>
+        <v>91620</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5834,34 +5816,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406379</v>
+        <v>406533</v>
       </c>
       <c r="R54" t="n">
-        <v>6832756</v>
+        <v>6832761</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5902,6 +5891,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5920,45 +5910,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845638</v>
+        <v>129845461</v>
       </c>
       <c r="B55" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406290</v>
+        <v>406589</v>
       </c>
       <c r="R55" t="n">
-        <v>6832900</v>
+        <v>6832990</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5999,28 +5998,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845627</v>
+        <v>129845410</v>
       </c>
       <c r="B56" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,42 +6028,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406539</v>
+        <v>406487</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6833064</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6110,22 +6102,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845633</v>
+        <v>129845602</v>
       </c>
       <c r="B57" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6133,42 +6125,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406674</v>
+        <v>406791</v>
       </c>
       <c r="R57" t="n">
-        <v>6832801</v>
+        <v>6832844</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6227,10 +6211,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845632</v>
+        <v>129845435</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6238,42 +6222,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406667</v>
+        <v>406455</v>
       </c>
       <c r="R58" t="n">
-        <v>6832849</v>
+        <v>6833027</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6320,12 +6296,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6534,10 +6510,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845410</v>
+        <v>129845466</v>
       </c>
       <c r="B61" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6545,21 +6521,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6569,10 +6545,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406487</v>
+        <v>406266</v>
       </c>
       <c r="R61" t="n">
-        <v>6833064</v>
+        <v>6832810</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6631,10 +6607,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845602</v>
+        <v>129845627</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6642,34 +6618,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406791</v>
+        <v>406539</v>
       </c>
       <c r="R62" t="n">
-        <v>6832844</v>
+        <v>6832767</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845466</v>
+        <v>129845633</v>
       </c>
       <c r="B63" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6739,34 +6723,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406266</v>
+        <v>406674</v>
       </c>
       <c r="R63" t="n">
-        <v>6832810</v>
+        <v>6832801</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6813,53 +6805,52 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845459</v>
+        <v>129845632</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6869,10 +6860,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406331</v>
+        <v>406667</v>
       </c>
       <c r="R64" t="n">
-        <v>6832715</v>
+        <v>6832849</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6913,64 +6904,72 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845435</v>
+        <v>129845459</v>
       </c>
       <c r="B65" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406455</v>
+        <v>406331</v>
       </c>
       <c r="R65" t="n">
-        <v>6833027</v>
+        <v>6832715</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,6 +7010,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845452</v>
+        <v>129845654</v>
       </c>
       <c r="B67" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7147,42 +7147,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406630</v>
+        <v>406460</v>
       </c>
       <c r="R67" t="n">
-        <v>6832941</v>
+        <v>6832823</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7229,22 +7221,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845434</v>
+        <v>129845493</v>
       </c>
       <c r="B68" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7252,21 +7244,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7276,10 +7268,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406499</v>
+        <v>406785</v>
       </c>
       <c r="R68" t="n">
-        <v>6833054</v>
+        <v>6832912</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7338,10 +7330,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845654</v>
+        <v>129845593</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7349,21 +7341,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7373,10 +7365,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406460</v>
+        <v>406451</v>
       </c>
       <c r="R69" t="n">
-        <v>6832823</v>
+        <v>6832712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7435,10 +7427,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845493</v>
+        <v>129845590</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7446,21 +7438,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7470,10 +7462,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406785</v>
+        <v>406421</v>
       </c>
       <c r="R70" t="n">
-        <v>6832912</v>
+        <v>6833142</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7520,22 +7512,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845593</v>
+        <v>129845452</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,34 +7535,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406451</v>
+        <v>406630</v>
       </c>
       <c r="R71" t="n">
-        <v>6832712</v>
+        <v>6832941</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7617,22 +7617,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845590</v>
+        <v>129845434</v>
       </c>
       <c r="B72" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,21 +7640,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406421</v>
+        <v>406499</v>
       </c>
       <c r="R72" t="n">
-        <v>6833142</v>
+        <v>6833054</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7714,12 +7714,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845454</v>
+        <v>129845444</v>
       </c>
       <c r="B81" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,31 +8513,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406675</v>
+        <v>406601</v>
       </c>
       <c r="R81" t="n">
-        <v>6832988</v>
+        <v>6832858</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8589,6 +8584,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8607,10 +8603,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845621</v>
+        <v>129845647</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8618,42 +8614,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406672</v>
+        <v>406274</v>
       </c>
       <c r="R82" t="n">
-        <v>6832840</v>
+        <v>6832759</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8712,27 +8700,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845465</v>
+        <v>129845621</v>
       </c>
       <c r="B83" t="n">
-        <v>58106</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8745,7 +8733,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8755,10 +8743,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406542</v>
+        <v>406672</v>
       </c>
       <c r="R83" t="n">
-        <v>6832915</v>
+        <v>6832840</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8805,22 +8793,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845444</v>
+        <v>129845454</v>
       </c>
       <c r="B84" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8828,26 +8816,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -8855,10 +8848,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406601</v>
+        <v>406675</v>
       </c>
       <c r="R84" t="n">
-        <v>6832858</v>
+        <v>6832988</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8899,7 +8892,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8918,45 +8910,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845647</v>
+        <v>129845465</v>
       </c>
       <c r="B85" t="n">
-        <v>78838</v>
+        <v>58106</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406274</v>
+        <v>406542</v>
       </c>
       <c r="R85" t="n">
-        <v>6832759</v>
+        <v>6832915</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9003,22 +9003,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845423</v>
+        <v>129845656</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9026,21 +9026,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406531</v>
+        <v>406480</v>
       </c>
       <c r="R86" t="n">
-        <v>6832868</v>
+        <v>6832777</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,19 +9100,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845656</v>
+        <v>129845653</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406480</v>
+        <v>406430</v>
       </c>
       <c r="R87" t="n">
         <v>6832777</v>
@@ -9209,10 +9209,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845653</v>
+        <v>129845423</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9220,21 +9220,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406430</v>
+        <v>406531</v>
       </c>
       <c r="R88" t="n">
-        <v>6832777</v>
+        <v>6832868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9294,49 +9294,55 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845437</v>
+        <v>129845641</v>
       </c>
       <c r="B89" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9344,10 +9350,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406331</v>
+        <v>406618</v>
       </c>
       <c r="R89" t="n">
-        <v>6832676</v>
+        <v>6832813</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9395,55 +9401,49 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845641</v>
+        <v>129845437</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406618</v>
+        <v>406331</v>
       </c>
       <c r="R90" t="n">
-        <v>6832813</v>
+        <v>6832676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9502,12 +9502,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845418</v>
+        <v>129845608</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406377</v>
+        <v>406399</v>
       </c>
       <c r="R93" t="n">
-        <v>6832837</v>
+        <v>6833177</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9793,22 +9793,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845594</v>
+        <v>129845457</v>
       </c>
       <c r="B94" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406506</v>
+        <v>406265</v>
       </c>
       <c r="R94" t="n">
-        <v>6832725</v>
+        <v>6832808</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9890,19 +9890,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845408</v>
+        <v>129845418</v>
       </c>
       <c r="B95" t="n">
         <v>79700</v>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406368</v>
+        <v>406377</v>
       </c>
       <c r="R95" t="n">
-        <v>6833202</v>
+        <v>6832837</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845634</v>
+        <v>129845594</v>
       </c>
       <c r="B96" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,42 +10010,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406781</v>
+        <v>406506</v>
       </c>
       <c r="R96" t="n">
-        <v>6832843</v>
+        <v>6832725</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,53 +10096,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845464</v>
+        <v>129845408</v>
       </c>
       <c r="B97" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406416</v>
+        <v>406368</v>
       </c>
       <c r="R97" t="n">
-        <v>6832880</v>
+        <v>6833202</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10209,10 +10193,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845608</v>
+        <v>129845634</v>
       </c>
       <c r="B98" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10220,34 +10204,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406399</v>
+        <v>406781</v>
       </c>
       <c r="R98" t="n">
-        <v>6833177</v>
+        <v>6832843</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10306,45 +10298,53 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845457</v>
+        <v>129845464</v>
       </c>
       <c r="B99" t="n">
-        <v>78839</v>
+        <v>58106</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406265</v>
+        <v>406416</v>
       </c>
       <c r="R99" t="n">
-        <v>6832808</v>
+        <v>6832880</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10403,10 +10403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845426</v>
+        <v>129845629</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,34 +10414,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406796</v>
+        <v>406618</v>
       </c>
       <c r="R100" t="n">
-        <v>6832917</v>
+        <v>6832773</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10488,22 +10496,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B101" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10511,21 +10519,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10535,10 +10543,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R101" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10585,22 +10593,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845646</v>
+        <v>129845426</v>
       </c>
       <c r="B102" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,21 +10616,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10632,10 +10640,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406290</v>
+        <v>406796</v>
       </c>
       <c r="R102" t="n">
-        <v>6832901</v>
+        <v>6832917</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10682,22 +10690,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845629</v>
+        <v>129845407</v>
       </c>
       <c r="B103" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,42 +10713,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406618</v>
+        <v>406416</v>
       </c>
       <c r="R103" t="n">
-        <v>6832773</v>
+        <v>6833166</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10787,22 +10787,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845615</v>
+        <v>129845646</v>
       </c>
       <c r="B104" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406583</v>
+        <v>406290</v>
       </c>
       <c r="R104" t="n">
-        <v>6832911</v>
+        <v>6832901</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10896,10 +10896,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845597</v>
+        <v>129845485</v>
       </c>
       <c r="B105" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406615</v>
+        <v>406320</v>
       </c>
       <c r="R105" t="n">
-        <v>6832770</v>
+        <v>6832742</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10981,19 +10981,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845595</v>
+        <v>129845597</v>
       </c>
       <c r="B106" t="n">
         <v>79700</v>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406455</v>
+        <v>406615</v>
       </c>
       <c r="R106" t="n">
-        <v>6832823</v>
+        <v>6832770</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845448</v>
+        <v>129845595</v>
       </c>
       <c r="B107" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,42 +11101,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406396</v>
+        <v>406455</v>
       </c>
       <c r="R107" t="n">
-        <v>6832853</v>
+        <v>6832823</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11183,19 +11175,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845450</v>
+        <v>129845448</v>
       </c>
       <c r="B108" t="n">
         <v>57733</v>
@@ -11238,10 +11230,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406508</v>
+        <v>406396</v>
       </c>
       <c r="R108" t="n">
-        <v>6832877</v>
+        <v>6832853</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11300,10 +11292,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845439</v>
+        <v>129845450</v>
       </c>
       <c r="B109" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11311,34 +11303,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406377</v>
+        <v>406508</v>
       </c>
       <c r="R109" t="n">
-        <v>6832840</v>
+        <v>6832877</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11397,10 +11397,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845485</v>
+        <v>129845439</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11408,21 +11408,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406320</v>
+        <v>406377</v>
       </c>
       <c r="R110" t="n">
-        <v>6832742</v>
+        <v>6832840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11997,10 +11997,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845596</v>
+        <v>129845635</v>
       </c>
       <c r="B116" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,34 +12008,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406536</v>
+        <v>406677</v>
       </c>
       <c r="R116" t="n">
-        <v>6832770</v>
+        <v>6832986</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12094,10 +12102,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845458</v>
+        <v>129845628</v>
       </c>
       <c r="B117" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12105,34 +12113,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406531</v>
+        <v>406541</v>
       </c>
       <c r="R117" t="n">
-        <v>6832927</v>
+        <v>6832823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12179,22 +12195,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845635</v>
+        <v>129845436</v>
       </c>
       <c r="B118" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12202,42 +12218,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406677</v>
+        <v>406315</v>
       </c>
       <c r="R118" t="n">
-        <v>6832986</v>
+        <v>6832667</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12284,22 +12292,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845628</v>
+        <v>129845458</v>
       </c>
       <c r="B119" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12307,42 +12315,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406541</v>
+        <v>406531</v>
       </c>
       <c r="R119" t="n">
-        <v>6832823</v>
+        <v>6832927</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12389,22 +12389,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845436</v>
+        <v>129845596</v>
       </c>
       <c r="B120" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406315</v>
+        <v>406536</v>
       </c>
       <c r="R120" t="n">
-        <v>6832667</v>
+        <v>6832770</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,12 +12486,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -3431,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845639</v>
+        <v>129845412</v>
       </c>
       <c r="B30" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406276</v>
+        <v>406426</v>
       </c>
       <c r="R30" t="n">
-        <v>6832761</v>
+        <v>6832990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3516,22 +3516,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845412</v>
+        <v>129845449</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,34 +3539,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406426</v>
+        <v>406498</v>
       </c>
       <c r="R31" t="n">
-        <v>6832990</v>
+        <v>6832913</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3625,7 +3633,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845449</v>
+        <v>129845636</v>
       </c>
       <c r="B32" t="n">
         <v>57733</v>
@@ -3658,7 +3666,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3668,10 +3676,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406498</v>
+        <v>406595</v>
       </c>
       <c r="R32" t="n">
-        <v>6832913</v>
+        <v>6833001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3718,52 +3726,53 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845636</v>
+        <v>129845463</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3773,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406595</v>
+        <v>406746</v>
       </c>
       <c r="R33" t="n">
-        <v>6833001</v>
+        <v>6832985</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3817,72 +3826,64 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845463</v>
+        <v>129845639</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406746</v>
+        <v>406276</v>
       </c>
       <c r="R34" t="n">
-        <v>6832985</v>
+        <v>6832761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3923,19 +3924,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845491</v>
+        <v>129845490</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406588</v>
+        <v>406560</v>
       </c>
       <c r="R40" t="n">
-        <v>6832866</v>
+        <v>6832885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4524,7 +4524,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845490</v>
+        <v>129845491</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406560</v>
+        <v>406588</v>
       </c>
       <c r="R41" t="n">
-        <v>6832885</v>
+        <v>6832866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,10 +5312,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845589</v>
+        <v>129845624</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5323,34 +5323,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406406</v>
+        <v>406494</v>
       </c>
       <c r="R49" t="n">
-        <v>6833199</v>
+        <v>6832766</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5409,45 +5417,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845416</v>
+        <v>129845461</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406362</v>
+        <v>406589</v>
       </c>
       <c r="R50" t="n">
-        <v>6832766</v>
+        <v>6832990</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5488,6 +5505,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5506,10 +5524,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845624</v>
+        <v>129845612</v>
       </c>
       <c r="B51" t="n">
-        <v>57896</v>
+        <v>79671</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5517,42 +5535,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406494</v>
+        <v>406379</v>
       </c>
       <c r="R51" t="n">
-        <v>6832766</v>
+        <v>6832756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5611,10 +5621,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845612</v>
+        <v>129845638</v>
       </c>
       <c r="B52" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5622,21 +5632,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5646,10 +5656,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406379</v>
+        <v>406290</v>
       </c>
       <c r="R52" t="n">
-        <v>6832756</v>
+        <v>6832900</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5708,10 +5718,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845638</v>
+        <v>129845589</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5719,21 +5729,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5743,10 +5753,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406290</v>
+        <v>406406</v>
       </c>
       <c r="R53" t="n">
-        <v>6832900</v>
+        <v>6833199</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5805,10 +5815,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845626</v>
+        <v>129845416</v>
       </c>
       <c r="B54" t="n">
-        <v>91620</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5816,41 +5826,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406533</v>
+        <v>406362</v>
       </c>
       <c r="R54" t="n">
-        <v>6832761</v>
+        <v>6832766</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5891,62 +5894,59 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845461</v>
+        <v>129845626</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>91620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406589</v>
+        <v>406533</v>
       </c>
       <c r="R55" t="n">
-        <v>6832990</v>
+        <v>6832761</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6005,22 +6005,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845410</v>
+        <v>129845625</v>
       </c>
       <c r="B56" t="n">
-        <v>79700</v>
+        <v>91620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,34 +6028,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406487</v>
+        <v>406472</v>
       </c>
       <c r="R56" t="n">
-        <v>6833064</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,28 +6103,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845602</v>
+        <v>129845487</v>
       </c>
       <c r="B57" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6125,21 +6133,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6149,10 +6157,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406791</v>
+        <v>406409</v>
       </c>
       <c r="R57" t="n">
-        <v>6832844</v>
+        <v>6832824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6199,22 +6207,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845435</v>
+        <v>129845410</v>
       </c>
       <c r="B58" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6222,21 +6230,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6246,10 +6254,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406455</v>
+        <v>406487</v>
       </c>
       <c r="R58" t="n">
-        <v>6833027</v>
+        <v>6833064</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6308,10 +6316,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845625</v>
+        <v>129845602</v>
       </c>
       <c r="B59" t="n">
-        <v>91620</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6319,41 +6327,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406472</v>
+        <v>406791</v>
       </c>
       <c r="R59" t="n">
-        <v>6832767</v>
+        <v>6832844</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6394,7 +6395,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6413,10 +6413,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845487</v>
+        <v>129845466</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6424,21 +6424,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406409</v>
+        <v>406266</v>
       </c>
       <c r="R60" t="n">
-        <v>6832824</v>
+        <v>6832810</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6510,45 +6510,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845466</v>
+        <v>129845459</v>
       </c>
       <c r="B61" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406266</v>
+        <v>406331</v>
       </c>
       <c r="R61" t="n">
-        <v>6832810</v>
+        <v>6832715</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6589,6 +6598,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6607,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845627</v>
+        <v>129845435</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6618,42 +6628,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406539</v>
+        <v>406455</v>
       </c>
       <c r="R62" t="n">
-        <v>6832767</v>
+        <v>6833027</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6700,19 +6702,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845633</v>
+        <v>129845627</v>
       </c>
       <c r="B63" t="n">
         <v>57733</v>
@@ -6745,7 +6747,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6755,10 +6757,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406674</v>
+        <v>406539</v>
       </c>
       <c r="R63" t="n">
-        <v>6832801</v>
+        <v>6832767</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6817,7 +6819,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845632</v>
+        <v>129845633</v>
       </c>
       <c r="B64" t="n">
         <v>57733</v>
@@ -6860,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406667</v>
+        <v>406674</v>
       </c>
       <c r="R64" t="n">
-        <v>6832849</v>
+        <v>6832801</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6922,41 +6924,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845459</v>
+        <v>129845632</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -6966,10 +6967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406331</v>
+        <v>406667</v>
       </c>
       <c r="R65" t="n">
-        <v>6832715</v>
+        <v>6832849</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7010,19 +7011,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845629</v>
+        <v>129845426</v>
       </c>
       <c r="B100" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,42 +10414,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406618</v>
+        <v>406796</v>
       </c>
       <c r="R100" t="n">
-        <v>6832773</v>
+        <v>6832917</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10496,22 +10488,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845615</v>
+        <v>129845407</v>
       </c>
       <c r="B101" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10519,21 +10511,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10543,10 +10535,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406583</v>
+        <v>406416</v>
       </c>
       <c r="R101" t="n">
-        <v>6832911</v>
+        <v>6833166</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10593,22 +10585,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845426</v>
+        <v>129845646</v>
       </c>
       <c r="B102" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10616,21 +10608,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10640,10 +10632,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406796</v>
+        <v>406290</v>
       </c>
       <c r="R102" t="n">
-        <v>6832917</v>
+        <v>6832901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10690,22 +10682,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845407</v>
+        <v>129845629</v>
       </c>
       <c r="B103" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10713,34 +10705,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406416</v>
+        <v>406618</v>
       </c>
       <c r="R103" t="n">
-        <v>6833166</v>
+        <v>6832773</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10787,22 +10787,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845646</v>
+        <v>129845615</v>
       </c>
       <c r="B104" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406290</v>
+        <v>406583</v>
       </c>
       <c r="R104" t="n">
-        <v>6832901</v>
+        <v>6832911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11494,45 +11494,53 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845421</v>
+        <v>129845644</v>
       </c>
       <c r="B111" t="n">
-        <v>79700</v>
+        <v>58106</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406500</v>
+        <v>406457</v>
       </c>
       <c r="R111" t="n">
-        <v>6832933</v>
+        <v>6832809</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11579,57 +11587,66 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845433</v>
+        <v>129845640</v>
       </c>
       <c r="B112" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406438</v>
+        <v>406404</v>
       </c>
       <c r="R112" t="n">
-        <v>6833114</v>
+        <v>6832729</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11670,71 +11687,64 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845644</v>
+        <v>129845430</v>
       </c>
       <c r="B113" t="n">
-        <v>58106</v>
+        <v>79671</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406457</v>
+        <v>406465</v>
       </c>
       <c r="R113" t="n">
-        <v>6832809</v>
+        <v>6833093</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11781,66 +11791,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845640</v>
+        <v>129845421</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406404</v>
+        <v>406500</v>
       </c>
       <c r="R114" t="n">
-        <v>6832729</v>
+        <v>6832933</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11881,26 +11882,25 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845430</v>
+        <v>129845433</v>
       </c>
       <c r="B115" t="n">
         <v>79671</v>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406465</v>
+        <v>406438</v>
       </c>
       <c r="R115" t="n">
-        <v>6833093</v>
+        <v>6833114</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11997,10 +11997,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845635</v>
+        <v>129845596</v>
       </c>
       <c r="B116" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,42 +12008,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406677</v>
+        <v>406536</v>
       </c>
       <c r="R116" t="n">
-        <v>6832986</v>
+        <v>6832770</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12102,7 +12094,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845628</v>
+        <v>129845635</v>
       </c>
       <c r="B117" t="n">
         <v>57733</v>
@@ -12135,7 +12127,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12145,10 +12137,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406541</v>
+        <v>406677</v>
       </c>
       <c r="R117" t="n">
-        <v>6832823</v>
+        <v>6832986</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12207,10 +12199,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845436</v>
+        <v>129845628</v>
       </c>
       <c r="B118" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12218,34 +12210,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406315</v>
+        <v>406541</v>
       </c>
       <c r="R118" t="n">
-        <v>6832667</v>
+        <v>6832823</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12292,22 +12292,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845458</v>
+        <v>129845436</v>
       </c>
       <c r="B119" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12315,21 +12315,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406531</v>
+        <v>406315</v>
       </c>
       <c r="R119" t="n">
-        <v>6832927</v>
+        <v>6832667</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12401,10 +12401,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845596</v>
+        <v>129845458</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406536</v>
+        <v>406531</v>
       </c>
       <c r="R120" t="n">
-        <v>6832770</v>
+        <v>6832927</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,12 +12486,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -10403,10 +10403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845426</v>
+        <v>129845629</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,34 +10414,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406796</v>
+        <v>406618</v>
       </c>
       <c r="R100" t="n">
-        <v>6832917</v>
+        <v>6832773</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10488,22 +10496,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B101" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10511,21 +10519,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10535,10 +10543,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R101" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10585,22 +10593,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845646</v>
+        <v>129845426</v>
       </c>
       <c r="B102" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,21 +10616,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10632,10 +10640,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406290</v>
+        <v>406796</v>
       </c>
       <c r="R102" t="n">
-        <v>6832901</v>
+        <v>6832917</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10682,22 +10690,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845629</v>
+        <v>129845407</v>
       </c>
       <c r="B103" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,42 +10713,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406618</v>
+        <v>406416</v>
       </c>
       <c r="R103" t="n">
-        <v>6832773</v>
+        <v>6833166</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10787,22 +10787,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845615</v>
+        <v>129845646</v>
       </c>
       <c r="B104" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406583</v>
+        <v>406290</v>
       </c>
       <c r="R104" t="n">
-        <v>6832911</v>
+        <v>6832901</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845427</v>
+        <v>129845443</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406794</v>
+        <v>406333</v>
       </c>
       <c r="R8" t="n">
-        <v>6832934</v>
+        <v>6832733</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845417</v>
+        <v>129845661</v>
       </c>
       <c r="B9" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406346</v>
+        <v>406352</v>
       </c>
       <c r="R9" t="n">
-        <v>6832798</v>
+        <v>6832709</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,22 +1447,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845630</v>
+        <v>129845427</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406631</v>
+        <v>406794</v>
       </c>
       <c r="R10" t="n">
-        <v>6832822</v>
+        <v>6832934</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,22 +1544,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845443</v>
+        <v>129845417</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,42 +1567,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406333</v>
+        <v>406346</v>
       </c>
       <c r="R11" t="n">
-        <v>6832733</v>
+        <v>6832798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845661</v>
+        <v>129845630</v>
       </c>
       <c r="B12" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,34 +1664,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406352</v>
+        <v>406631</v>
       </c>
       <c r="R12" t="n">
-        <v>6832709</v>
+        <v>6832822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845429</v>
+        <v>129845467</v>
       </c>
       <c r="B13" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,34 +1769,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406472</v>
+        <v>406359</v>
       </c>
       <c r="R13" t="n">
-        <v>6833103</v>
+        <v>6832764</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,6 +1840,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1855,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845467</v>
+        <v>129845610</v>
       </c>
       <c r="B14" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,37 +1870,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406359</v>
+        <v>406262</v>
       </c>
       <c r="R14" t="n">
-        <v>6832764</v>
+        <v>6832854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1937,26 +1938,25 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845610</v>
+        <v>129845614</v>
       </c>
       <c r="B15" t="n">
         <v>79671</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406262</v>
+        <v>406492</v>
       </c>
       <c r="R15" t="n">
-        <v>6832854</v>
+        <v>6832753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845617</v>
+        <v>129845429</v>
       </c>
       <c r="B17" t="n">
         <v>79671</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406626</v>
+        <v>406472</v>
       </c>
       <c r="R17" t="n">
-        <v>6832781</v>
+        <v>6833103</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,22 +2235,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845655</v>
+        <v>129845613</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406473</v>
+        <v>406388</v>
       </c>
       <c r="R18" t="n">
-        <v>6832798</v>
+        <v>6832683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845604</v>
+        <v>129845617</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406424</v>
+        <v>406626</v>
       </c>
       <c r="R19" t="n">
-        <v>6832657</v>
+        <v>6832781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845614</v>
+        <v>129845655</v>
       </c>
       <c r="B20" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406492</v>
+        <v>406473</v>
       </c>
       <c r="R20" t="n">
-        <v>6832753</v>
+        <v>6832798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845613</v>
+        <v>129845604</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406388</v>
+        <v>406424</v>
       </c>
       <c r="R21" t="n">
-        <v>6832683</v>
+        <v>6832657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3130,54 +3130,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845460</v>
+        <v>129845413</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406431</v>
+        <v>406266</v>
       </c>
       <c r="R27" t="n">
-        <v>6832825</v>
+        <v>6832827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,7 +3209,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3237,45 +3227,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129845619</v>
+        <v>129845460</v>
       </c>
       <c r="B28" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406776</v>
+        <v>406431</v>
       </c>
       <c r="R28" t="n">
-        <v>6832860</v>
+        <v>6832825</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3316,28 +3315,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129845413</v>
+        <v>129845619</v>
       </c>
       <c r="B29" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406266</v>
+        <v>406776</v>
       </c>
       <c r="R29" t="n">
-        <v>6832827</v>
+        <v>6832860</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,22 +3419,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845412</v>
+        <v>129845639</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406426</v>
+        <v>406276</v>
       </c>
       <c r="R30" t="n">
-        <v>6832990</v>
+        <v>6832761</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3516,22 +3516,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845449</v>
+        <v>129845412</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,42 +3539,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406498</v>
+        <v>406426</v>
       </c>
       <c r="R31" t="n">
-        <v>6832913</v>
+        <v>6832990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,41 +3730,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845463</v>
+        <v>129845449</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3782,10 +3773,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406746</v>
+        <v>406498</v>
       </c>
       <c r="R33" t="n">
-        <v>6832985</v>
+        <v>6832913</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3826,7 +3817,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3845,45 +3835,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845639</v>
+        <v>129845463</v>
       </c>
       <c r="B34" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406276</v>
+        <v>406746</v>
       </c>
       <c r="R34" t="n">
-        <v>6832761</v>
+        <v>6832985</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3924,18 +3923,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845592</v>
+        <v>129845455</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406370</v>
+        <v>406486</v>
       </c>
       <c r="R38" t="n">
-        <v>6832711</v>
+        <v>6833057</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,22 +4318,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129845455</v>
+        <v>129845592</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406486</v>
+        <v>406370</v>
       </c>
       <c r="R39" t="n">
-        <v>6833057</v>
+        <v>6832711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,12 +4415,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845601</v>
+        <v>129845611</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406583</v>
+        <v>406276</v>
       </c>
       <c r="R44" t="n">
-        <v>6832841</v>
+        <v>6832761</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845631</v>
+        <v>129845431</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,42 +4927,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406698</v>
+        <v>406368</v>
       </c>
       <c r="R45" t="n">
-        <v>6832875</v>
+        <v>6833201</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,22 +5001,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845611</v>
+        <v>129845456</v>
       </c>
       <c r="B46" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5032,21 +5024,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5056,10 +5048,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406276</v>
+        <v>406442</v>
       </c>
       <c r="R46" t="n">
-        <v>6832761</v>
+        <v>6833041</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5106,22 +5098,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845431</v>
+        <v>129845601</v>
       </c>
       <c r="B47" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5129,21 +5121,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5153,10 +5145,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406368</v>
+        <v>406583</v>
       </c>
       <c r="R47" t="n">
-        <v>6833201</v>
+        <v>6832841</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5203,22 +5195,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845456</v>
+        <v>129845631</v>
       </c>
       <c r="B48" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5226,34 +5218,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406442</v>
+        <v>406698</v>
       </c>
       <c r="R48" t="n">
-        <v>6833041</v>
+        <v>6832875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5300,22 +5300,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845624</v>
+        <v>129845626</v>
       </c>
       <c r="B49" t="n">
-        <v>57896</v>
+        <v>91620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5323,31 +5323,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5355,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406494</v>
+        <v>406533</v>
       </c>
       <c r="R49" t="n">
-        <v>6832766</v>
+        <v>6832761</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,6 +5398,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5417,41 +5417,40 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845461</v>
+        <v>129845624</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5461,10 +5460,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406589</v>
+        <v>406494</v>
       </c>
       <c r="R50" t="n">
-        <v>6832990</v>
+        <v>6832766</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5505,29 +5504,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845612</v>
+        <v>129845638</v>
       </c>
       <c r="B51" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5535,21 +5533,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5559,10 +5557,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406379</v>
+        <v>406290</v>
       </c>
       <c r="R51" t="n">
-        <v>6832756</v>
+        <v>6832900</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,10 +5619,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845638</v>
+        <v>129845612</v>
       </c>
       <c r="B52" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,21 +5630,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5656,10 +5654,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406290</v>
+        <v>406379</v>
       </c>
       <c r="R52" t="n">
-        <v>6832900</v>
+        <v>6832756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5718,45 +5716,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845589</v>
+        <v>129845461</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406406</v>
+        <v>406589</v>
       </c>
       <c r="R53" t="n">
-        <v>6833199</v>
+        <v>6832990</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5797,25 +5804,26 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845416</v>
+        <v>129845589</v>
       </c>
       <c r="B54" t="n">
         <v>79700</v>
@@ -5850,10 +5858,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406362</v>
+        <v>406406</v>
       </c>
       <c r="R54" t="n">
-        <v>6832766</v>
+        <v>6833199</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5900,22 +5908,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845626</v>
+        <v>129845416</v>
       </c>
       <c r="B55" t="n">
-        <v>91620</v>
+        <v>79700</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5923,41 +5931,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406533</v>
+        <v>406362</v>
       </c>
       <c r="R55" t="n">
-        <v>6832761</v>
+        <v>6832766</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5998,19 +5999,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845410</v>
+        <v>129845466</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6230,21 +6230,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406487</v>
+        <v>406266</v>
       </c>
       <c r="R58" t="n">
-        <v>6833064</v>
+        <v>6832810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845602</v>
+        <v>129845410</v>
       </c>
       <c r="B59" t="n">
         <v>79700</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406791</v>
+        <v>406487</v>
       </c>
       <c r="R59" t="n">
-        <v>6832844</v>
+        <v>6833064</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6401,22 +6401,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845466</v>
+        <v>129845602</v>
       </c>
       <c r="B60" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6424,21 +6424,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406266</v>
+        <v>406791</v>
       </c>
       <c r="R60" t="n">
-        <v>6832810</v>
+        <v>6832844</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6498,53 +6498,52 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845459</v>
+        <v>129845632</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6554,10 +6553,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406331</v>
+        <v>406667</v>
       </c>
       <c r="R61" t="n">
-        <v>6832715</v>
+        <v>6832849</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6598,29 +6597,28 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845435</v>
+        <v>129845633</v>
       </c>
       <c r="B62" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,34 +6626,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406455</v>
+        <v>406674</v>
       </c>
       <c r="R62" t="n">
-        <v>6833027</v>
+        <v>6832801</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6702,12 +6708,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6819,40 +6825,41 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845633</v>
+        <v>129845459</v>
       </c>
       <c r="B64" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6862,10 +6869,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406674</v>
+        <v>406331</v>
       </c>
       <c r="R64" t="n">
-        <v>6832801</v>
+        <v>6832715</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,28 +6913,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845632</v>
+        <v>129845435</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6935,42 +6943,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406667</v>
+        <v>406455</v>
       </c>
       <c r="R65" t="n">
-        <v>6832849</v>
+        <v>6833027</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7017,66 +7017,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845642</v>
+        <v>129845654</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406547</v>
+        <v>406460</v>
       </c>
       <c r="R66" t="n">
-        <v>6832775</v>
+        <v>6832823</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7117,7 +7108,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7136,7 +7126,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845654</v>
+        <v>129845493</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7171,10 +7161,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406460</v>
+        <v>406785</v>
       </c>
       <c r="R67" t="n">
-        <v>6832823</v>
+        <v>6832912</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7221,22 +7211,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845493</v>
+        <v>129845593</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7244,21 +7234,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7268,10 +7258,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406785</v>
+        <v>406451</v>
       </c>
       <c r="R68" t="n">
-        <v>6832912</v>
+        <v>6832712</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7318,19 +7308,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845593</v>
+        <v>129845590</v>
       </c>
       <c r="B69" t="n">
         <v>79700</v>
@@ -7365,10 +7355,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406451</v>
+        <v>406421</v>
       </c>
       <c r="R69" t="n">
-        <v>6832712</v>
+        <v>6833142</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7427,10 +7417,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845590</v>
+        <v>129845452</v>
       </c>
       <c r="B70" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7438,34 +7428,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406421</v>
+        <v>406630</v>
       </c>
       <c r="R70" t="n">
-        <v>6833142</v>
+        <v>6832941</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7512,52 +7510,53 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845452</v>
+        <v>129845642</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -7567,10 +7566,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406630</v>
+        <v>406547</v>
       </c>
       <c r="R71" t="n">
-        <v>6832941</v>
+        <v>6832775</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7611,18 +7610,19 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845606</v>
+        <v>129845415</v>
       </c>
       <c r="B77" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406394</v>
+        <v>406317</v>
       </c>
       <c r="R77" t="n">
-        <v>6833197</v>
+        <v>6832733</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8199,19 +8199,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845415</v>
+        <v>129845600</v>
       </c>
       <c r="B78" t="n">
         <v>79700</v>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406317</v>
+        <v>406582</v>
       </c>
       <c r="R78" t="n">
-        <v>6832733</v>
+        <v>6832826</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8296,19 +8296,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845600</v>
+        <v>129845420</v>
       </c>
       <c r="B79" t="n">
         <v>79700</v>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406582</v>
+        <v>406424</v>
       </c>
       <c r="R79" t="n">
-        <v>6832826</v>
+        <v>6832865</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8393,22 +8393,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129845420</v>
+        <v>129845606</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406424</v>
+        <v>406394</v>
       </c>
       <c r="R80" t="n">
-        <v>6832865</v>
+        <v>6833197</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8490,12 +8490,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8700,10 +8700,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845621</v>
+        <v>129845454</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8733,7 +8733,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406672</v>
+        <v>406675</v>
       </c>
       <c r="R83" t="n">
-        <v>6832840</v>
+        <v>6832988</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8793,22 +8793,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845454</v>
+        <v>129845621</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8838,7 +8838,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406675</v>
+        <v>406672</v>
       </c>
       <c r="R84" t="n">
-        <v>6832988</v>
+        <v>6832840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8898,12 +8898,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845479</v>
+        <v>129845634</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,34 +9525,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406408</v>
+        <v>406781</v>
       </c>
       <c r="R91" t="n">
-        <v>6832975</v>
+        <v>6832843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9599,57 +9607,65 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845480</v>
+        <v>129845464</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>58106</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406277</v>
+        <v>406416</v>
       </c>
       <c r="R92" t="n">
-        <v>6832823</v>
+        <v>6832880</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9724,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845608</v>
+        <v>129845457</v>
       </c>
       <c r="B93" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9735,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9759,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406399</v>
+        <v>406265</v>
       </c>
       <c r="R93" t="n">
-        <v>6833177</v>
+        <v>6832808</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9793,22 +9809,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845457</v>
+        <v>129845608</v>
       </c>
       <c r="B94" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9832,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9856,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406265</v>
+        <v>406399</v>
       </c>
       <c r="R94" t="n">
-        <v>6832808</v>
+        <v>6833177</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9890,22 +9906,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845418</v>
+        <v>129845479</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9929,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9953,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406377</v>
+        <v>406408</v>
       </c>
       <c r="R95" t="n">
-        <v>6832837</v>
+        <v>6832975</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +10015,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845594</v>
+        <v>129845480</v>
       </c>
       <c r="B96" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,21 +10026,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10050,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406506</v>
+        <v>406277</v>
       </c>
       <c r="R96" t="n">
-        <v>6832725</v>
+        <v>6832823</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10084,19 +10100,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845408</v>
+        <v>129845418</v>
       </c>
       <c r="B97" t="n">
         <v>79700</v>
@@ -10131,10 +10147,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406368</v>
+        <v>406377</v>
       </c>
       <c r="R97" t="n">
-        <v>6833202</v>
+        <v>6832837</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10193,10 +10209,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845634</v>
+        <v>129845594</v>
       </c>
       <c r="B98" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10204,42 +10220,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406781</v>
+        <v>406506</v>
       </c>
       <c r="R98" t="n">
-        <v>6832843</v>
+        <v>6832725</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,53 +10306,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845464</v>
+        <v>129845408</v>
       </c>
       <c r="B99" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406416</v>
+        <v>406368</v>
       </c>
       <c r="R99" t="n">
-        <v>6832880</v>
+        <v>6833202</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10605,10 +10605,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845426</v>
+        <v>129845646</v>
       </c>
       <c r="B102" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10616,21 +10616,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10640,10 +10640,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406796</v>
+        <v>406290</v>
       </c>
       <c r="R102" t="n">
-        <v>6832917</v>
+        <v>6832901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10690,19 +10690,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845407</v>
+        <v>129845426</v>
       </c>
       <c r="B103" t="n">
         <v>79700</v>
@@ -10737,10 +10737,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406416</v>
+        <v>406796</v>
       </c>
       <c r="R103" t="n">
-        <v>6833166</v>
+        <v>6832917</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10799,10 +10799,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845646</v>
+        <v>129845407</v>
       </c>
       <c r="B104" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406290</v>
+        <v>406416</v>
       </c>
       <c r="R104" t="n">
-        <v>6832901</v>
+        <v>6833166</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,12 +10884,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11187,10 +11187,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845448</v>
+        <v>129845439</v>
       </c>
       <c r="B108" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11198,42 +11198,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406396</v>
+        <v>406377</v>
       </c>
       <c r="R108" t="n">
-        <v>6832853</v>
+        <v>6832840</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11397,10 +11389,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845439</v>
+        <v>129845448</v>
       </c>
       <c r="B110" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11408,34 +11400,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406377</v>
+        <v>406396</v>
       </c>
       <c r="R110" t="n">
-        <v>6832840</v>
+        <v>6832853</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11494,53 +11494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845644</v>
+        <v>129845421</v>
       </c>
       <c r="B111" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406457</v>
+        <v>406500</v>
       </c>
       <c r="R111" t="n">
-        <v>6832809</v>
+        <v>6832933</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11587,22 +11579,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845640</v>
+        <v>129845644</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>58106</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11610,30 +11602,29 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11643,10 +11634,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406404</v>
+        <v>406457</v>
       </c>
       <c r="R112" t="n">
-        <v>6832729</v>
+        <v>6832809</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11687,7 +11678,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11706,45 +11696,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845430</v>
+        <v>129845640</v>
       </c>
       <c r="B113" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406465</v>
+        <v>406404</v>
       </c>
       <c r="R113" t="n">
-        <v>6833093</v>
+        <v>6832729</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11785,28 +11784,29 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845421</v>
+        <v>129845433</v>
       </c>
       <c r="B114" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406500</v>
+        <v>406438</v>
       </c>
       <c r="R114" t="n">
-        <v>6832933</v>
+        <v>6833114</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11900,7 +11900,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845433</v>
+        <v>129845430</v>
       </c>
       <c r="B115" t="n">
         <v>79671</v>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406438</v>
+        <v>406465</v>
       </c>
       <c r="R115" t="n">
-        <v>6833114</v>
+        <v>6833093</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12094,7 +12094,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845635</v>
+        <v>129845628</v>
       </c>
       <c r="B117" t="n">
         <v>57733</v>
@@ -12127,7 +12127,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12137,10 +12137,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406677</v>
+        <v>406541</v>
       </c>
       <c r="R117" t="n">
-        <v>6832986</v>
+        <v>6832823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845628</v>
+        <v>129845635</v>
       </c>
       <c r="B118" t="n">
         <v>57733</v>
@@ -12232,7 +12232,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -12242,10 +12242,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406541</v>
+        <v>406677</v>
       </c>
       <c r="R118" t="n">
-        <v>6832823</v>
+        <v>6832986</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12304,10 +12304,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845436</v>
+        <v>129845458</v>
       </c>
       <c r="B119" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12315,21 +12315,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406315</v>
+        <v>406531</v>
       </c>
       <c r="R119" t="n">
-        <v>6832667</v>
+        <v>6832927</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12401,10 +12401,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845458</v>
+        <v>129845436</v>
       </c>
       <c r="B120" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406531</v>
+        <v>406315</v>
       </c>
       <c r="R120" t="n">
-        <v>6832927</v>
+        <v>6832667</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12498,10 +12498,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845494</v>
+        <v>129845591</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12509,21 +12509,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12533,10 +12533,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406710</v>
+        <v>406439</v>
       </c>
       <c r="R121" t="n">
-        <v>6832990</v>
+        <v>6833139</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12583,22 +12583,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129845495</v>
+        <v>129845588</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12606,21 +12606,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406668</v>
+        <v>406440</v>
       </c>
       <c r="R122" t="n">
-        <v>6833007</v>
+        <v>6833101</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12680,22 +12680,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845484</v>
+        <v>129845451</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12703,26 +12703,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -12730,10 +12735,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406310</v>
+        <v>406595</v>
       </c>
       <c r="R123" t="n">
-        <v>6832729</v>
+        <v>6832931</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,7 +12779,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12793,10 +12797,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845591</v>
+        <v>129845494</v>
       </c>
       <c r="B124" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12804,21 +12808,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12828,10 +12832,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406439</v>
+        <v>406710</v>
       </c>
       <c r="R124" t="n">
-        <v>6833139</v>
+        <v>6832990</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12878,22 +12882,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845588</v>
+        <v>129845495</v>
       </c>
       <c r="B125" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12901,21 +12905,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12925,10 +12929,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406440</v>
+        <v>406668</v>
       </c>
       <c r="R125" t="n">
-        <v>6833101</v>
+        <v>6833007</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12975,22 +12979,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845432</v>
+        <v>129845484</v>
       </c>
       <c r="B126" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12998,34 +13002,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406373</v>
+        <v>406310</v>
       </c>
       <c r="R126" t="n">
-        <v>6833176</v>
+        <v>6832729</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13066,6 +13073,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13084,10 +13092,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845451</v>
+        <v>129845432</v>
       </c>
       <c r="B127" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13095,42 +13103,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406595</v>
+        <v>406373</v>
       </c>
       <c r="R127" t="n">
-        <v>6832931</v>
+        <v>6833176</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -3942,10 +3942,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845481</v>
+        <v>129845592</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406278</v>
+        <v>406370</v>
       </c>
       <c r="R35" t="n">
-        <v>6832795</v>
+        <v>6832711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,19 +4027,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845483</v>
+        <v>129845481</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406344</v>
+        <v>406278</v>
       </c>
       <c r="R36" t="n">
-        <v>6832706</v>
+        <v>6832795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845657</v>
+        <v>129845483</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406495</v>
+        <v>406344</v>
       </c>
       <c r="R37" t="n">
-        <v>6832766</v>
+        <v>6832706</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,22 +4221,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845455</v>
+        <v>129845657</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406486</v>
+        <v>406495</v>
       </c>
       <c r="R38" t="n">
-        <v>6833057</v>
+        <v>6832766</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,22 +4318,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129845592</v>
+        <v>129845455</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406370</v>
+        <v>406486</v>
       </c>
       <c r="R39" t="n">
-        <v>6832711</v>
+        <v>6833057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,22 +4415,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845490</v>
+        <v>129845631</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4438,34 +4438,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406560</v>
+        <v>406698</v>
       </c>
       <c r="R40" t="n">
-        <v>6832885</v>
+        <v>6832875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4512,22 +4520,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845491</v>
+        <v>129845611</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4535,21 +4543,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4559,10 +4567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406588</v>
+        <v>406276</v>
       </c>
       <c r="R41" t="n">
-        <v>6832866</v>
+        <v>6832761</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4609,22 +4617,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845492</v>
+        <v>129845431</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4632,37 +4640,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406591</v>
+        <v>406368</v>
       </c>
       <c r="R42" t="n">
-        <v>6832966</v>
+        <v>6833201</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4703,7 +4708,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4722,10 +4726,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845660</v>
+        <v>129845456</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4733,21 +4737,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4757,10 +4761,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406728</v>
+        <v>406442</v>
       </c>
       <c r="R43" t="n">
-        <v>6832848</v>
+        <v>6833041</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4807,22 +4811,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845611</v>
+        <v>129845490</v>
       </c>
       <c r="B44" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4834,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4858,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406276</v>
+        <v>406560</v>
       </c>
       <c r="R44" t="n">
-        <v>6832761</v>
+        <v>6832885</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,22 +4908,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845431</v>
+        <v>129845491</v>
       </c>
       <c r="B45" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,21 +4931,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4951,10 +4955,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406368</v>
+        <v>406588</v>
       </c>
       <c r="R45" t="n">
-        <v>6833201</v>
+        <v>6832866</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5013,10 +5017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845456</v>
+        <v>129845492</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5024,34 +5028,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406442</v>
+        <v>406591</v>
       </c>
       <c r="R46" t="n">
-        <v>6833041</v>
+        <v>6832966</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5092,6 +5099,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5110,10 +5118,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845601</v>
+        <v>129845660</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5121,21 +5129,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5145,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406583</v>
+        <v>406728</v>
       </c>
       <c r="R47" t="n">
-        <v>6832841</v>
+        <v>6832848</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5207,10 +5215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845631</v>
+        <v>129845601</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5218,42 +5226,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406698</v>
+        <v>406583</v>
       </c>
       <c r="R48" t="n">
-        <v>6832875</v>
+        <v>6832841</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845593</v>
+        <v>129845452</v>
       </c>
       <c r="B68" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7234,34 +7234,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406451</v>
+        <v>406630</v>
       </c>
       <c r="R68" t="n">
-        <v>6832712</v>
+        <v>6832941</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7308,57 +7316,66 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845590</v>
+        <v>129845642</v>
       </c>
       <c r="B69" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406421</v>
+        <v>406547</v>
       </c>
       <c r="R69" t="n">
-        <v>6833142</v>
+        <v>6832775</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7399,6 +7416,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7417,10 +7435,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845452</v>
+        <v>129845593</v>
       </c>
       <c r="B70" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7428,42 +7446,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406630</v>
+        <v>406451</v>
       </c>
       <c r="R70" t="n">
-        <v>6832941</v>
+        <v>6832712</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7510,66 +7520,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845642</v>
+        <v>129845590</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406547</v>
+        <v>406421</v>
       </c>
       <c r="R71" t="n">
-        <v>6832775</v>
+        <v>6833142</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7610,7 +7611,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8502,37 +8502,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845444</v>
+        <v>129845465</v>
       </c>
       <c r="B81" t="n">
-        <v>91620</v>
+        <v>58106</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406601</v>
+        <v>406542</v>
       </c>
       <c r="R81" t="n">
-        <v>6832858</v>
+        <v>6832915</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8584,7 +8589,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8603,10 +8607,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845647</v>
+        <v>129845444</v>
       </c>
       <c r="B82" t="n">
-        <v>78838</v>
+        <v>91620</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8614,34 +8618,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406274</v>
+        <v>406601</v>
       </c>
       <c r="R82" t="n">
-        <v>6832759</v>
+        <v>6832858</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8682,28 +8689,29 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845454</v>
+        <v>129845647</v>
       </c>
       <c r="B83" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8711,42 +8719,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406675</v>
+        <v>406274</v>
       </c>
       <c r="R83" t="n">
-        <v>6832988</v>
+        <v>6832759</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8793,22 +8793,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845621</v>
+        <v>129845454</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8838,7 +8838,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406672</v>
+        <v>406675</v>
       </c>
       <c r="R84" t="n">
-        <v>6832840</v>
+        <v>6832988</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8898,39 +8898,39 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845465</v>
+        <v>129845621</v>
       </c>
       <c r="B85" t="n">
-        <v>58106</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8943,7 +8943,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406542</v>
+        <v>406672</v>
       </c>
       <c r="R85" t="n">
-        <v>6832915</v>
+        <v>6832840</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9003,12 +9003,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845629</v>
+        <v>129845646</v>
       </c>
       <c r="B100" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,42 +10414,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406618</v>
+        <v>406290</v>
       </c>
       <c r="R100" t="n">
-        <v>6832773</v>
+        <v>6832901</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10508,10 +10500,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845615</v>
+        <v>129845426</v>
       </c>
       <c r="B101" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10519,21 +10511,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10543,10 +10535,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406583</v>
+        <v>406796</v>
       </c>
       <c r="R101" t="n">
-        <v>6832911</v>
+        <v>6832917</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10593,22 +10585,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845646</v>
+        <v>129845407</v>
       </c>
       <c r="B102" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10616,21 +10608,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10640,10 +10632,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406290</v>
+        <v>406416</v>
       </c>
       <c r="R102" t="n">
-        <v>6832901</v>
+        <v>6833166</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10690,22 +10682,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845426</v>
+        <v>129845629</v>
       </c>
       <c r="B103" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10713,34 +10705,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406796</v>
+        <v>406618</v>
       </c>
       <c r="R103" t="n">
-        <v>6832917</v>
+        <v>6832773</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10787,22 +10787,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B104" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R104" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,12 +10884,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11494,45 +11494,53 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845421</v>
+        <v>129845644</v>
       </c>
       <c r="B111" t="n">
-        <v>79700</v>
+        <v>58106</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406500</v>
+        <v>406457</v>
       </c>
       <c r="R111" t="n">
-        <v>6832933</v>
+        <v>6832809</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11579,65 +11587,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845644</v>
+        <v>129845421</v>
       </c>
       <c r="B112" t="n">
-        <v>58106</v>
+        <v>79700</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406457</v>
+        <v>406500</v>
       </c>
       <c r="R112" t="n">
-        <v>6832809</v>
+        <v>6832933</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11684,12 +11684,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129845598</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845599</v>
+        <v>129845425</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406635</v>
+        <v>406832</v>
       </c>
       <c r="R3" t="n">
-        <v>6832779</v>
+        <v>6832816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845425</v>
+        <v>129845419</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406832</v>
+        <v>406387</v>
       </c>
       <c r="R4" t="n">
-        <v>6832816</v>
+        <v>6832850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845419</v>
+        <v>129845599</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406387</v>
+        <v>406635</v>
       </c>
       <c r="R5" t="n">
-        <v>6832850</v>
+        <v>6832779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>129845438</v>
       </c>
       <c r="B6" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129845441</v>
       </c>
       <c r="B7" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845443</v>
+        <v>129845661</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>78750</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406333</v>
+        <v>406352</v>
       </c>
       <c r="R8" t="n">
-        <v>6832733</v>
+        <v>6832709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845661</v>
+        <v>129845630</v>
       </c>
       <c r="B9" t="n">
-        <v>78747</v>
+        <v>57734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,34 +1365,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406352</v>
+        <v>406631</v>
       </c>
       <c r="R9" t="n">
-        <v>6832709</v>
+        <v>6832822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
         <v>129845427</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129845417</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845630</v>
+        <v>129845443</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406631</v>
+        <v>406333</v>
       </c>
       <c r="R12" t="n">
-        <v>6832822</v>
+        <v>6832733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,22 +1746,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845467</v>
+        <v>129845655</v>
       </c>
       <c r="B13" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,37 +1769,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406359</v>
+        <v>406473</v>
       </c>
       <c r="R13" t="n">
-        <v>6832764</v>
+        <v>6832798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,29 +1837,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845610</v>
+        <v>129845604</v>
       </c>
       <c r="B14" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406262</v>
+        <v>406424</v>
       </c>
       <c r="R14" t="n">
-        <v>6832854</v>
+        <v>6832657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845614</v>
+        <v>129845467</v>
       </c>
       <c r="B15" t="n">
-        <v>79671</v>
+        <v>78841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,34 +1963,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406492</v>
+        <v>406359</v>
       </c>
       <c r="R15" t="n">
-        <v>6832753</v>
+        <v>6832764</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2035,28 +2034,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845618</v>
+        <v>129845429</v>
       </c>
       <c r="B16" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406791</v>
+        <v>406472</v>
       </c>
       <c r="R16" t="n">
-        <v>6832845</v>
+        <v>6833103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,22 +2138,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845429</v>
+        <v>129845613</v>
       </c>
       <c r="B17" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406472</v>
+        <v>406388</v>
       </c>
       <c r="R17" t="n">
-        <v>6833103</v>
+        <v>6832683</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,57 +2235,66 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845613</v>
+        <v>129845462</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406388</v>
+        <v>406713</v>
       </c>
       <c r="R18" t="n">
-        <v>6832683</v>
+        <v>6832904</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2326,28 +2335,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845617</v>
+        <v>129845610</v>
       </c>
       <c r="B19" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406626</v>
+        <v>406262</v>
       </c>
       <c r="R19" t="n">
-        <v>6832781</v>
+        <v>6832854</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845655</v>
+        <v>129845614</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406473</v>
+        <v>406492</v>
       </c>
       <c r="R20" t="n">
-        <v>6832798</v>
+        <v>6832753</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845604</v>
+        <v>129845618</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406424</v>
+        <v>406791</v>
       </c>
       <c r="R21" t="n">
-        <v>6832657</v>
+        <v>6832845</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,54 +2645,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845462</v>
+        <v>129845617</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406713</v>
+        <v>406626</v>
       </c>
       <c r="R22" t="n">
-        <v>6832904</v>
+        <v>6832781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,64 +2724,72 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129845488</v>
+        <v>129845460</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406528</v>
+        <v>406431</v>
       </c>
       <c r="R23" t="n">
-        <v>6832873</v>
+        <v>6832825</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2821,6 +2830,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2839,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129845652</v>
+        <v>129845619</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406408</v>
+        <v>406776</v>
       </c>
       <c r="R24" t="n">
-        <v>6832778</v>
+        <v>6832860</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129845659</v>
+        <v>129845488</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2971,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406556</v>
+        <v>406528</v>
       </c>
       <c r="R25" t="n">
-        <v>6832846</v>
+        <v>6832873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,22 +3031,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845422</v>
+        <v>129845652</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3054,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406513</v>
+        <v>406408</v>
       </c>
       <c r="R26" t="n">
-        <v>6832869</v>
+        <v>6832778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3118,22 +3128,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845413</v>
+        <v>129845659</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3151,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3175,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406266</v>
+        <v>406556</v>
       </c>
       <c r="R27" t="n">
-        <v>6832827</v>
+        <v>6832846</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3215,66 +3225,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129845460</v>
+        <v>129845422</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406431</v>
+        <v>406513</v>
       </c>
       <c r="R28" t="n">
-        <v>6832825</v>
+        <v>6832869</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,7 +3316,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129845619</v>
+        <v>129845413</v>
       </c>
       <c r="B29" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406776</v>
+        <v>406266</v>
       </c>
       <c r="R29" t="n">
-        <v>6832860</v>
+        <v>6832827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,22 +3419,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845639</v>
+        <v>129845636</v>
       </c>
       <c r="B30" t="n">
-        <v>78839</v>
+        <v>57734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,34 +3442,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406276</v>
+        <v>406595</v>
       </c>
       <c r="R30" t="n">
-        <v>6832761</v>
+        <v>6833001</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,10 +3536,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845412</v>
+        <v>129845449</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,34 +3547,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406426</v>
+        <v>406498</v>
       </c>
       <c r="R31" t="n">
-        <v>6832990</v>
+        <v>6832913</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3625,40 +3641,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845636</v>
+        <v>129845463</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3668,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406595</v>
+        <v>406746</v>
       </c>
       <c r="R32" t="n">
-        <v>6833001</v>
+        <v>6832985</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3712,28 +3729,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845449</v>
+        <v>129845639</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>78842</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3741,42 +3759,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406498</v>
+        <v>406276</v>
       </c>
       <c r="R33" t="n">
-        <v>6832913</v>
+        <v>6832761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3823,66 +3833,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845463</v>
+        <v>129845412</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406746</v>
+        <v>406426</v>
       </c>
       <c r="R34" t="n">
-        <v>6832985</v>
+        <v>6832990</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3923,7 +3924,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3942,10 +3942,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845592</v>
+        <v>129845657</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406370</v>
+        <v>406495</v>
       </c>
       <c r="R35" t="n">
-        <v>6832711</v>
+        <v>6832766</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4042,7 +4042,7 @@
         <v>129845481</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>129845483</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845657</v>
+        <v>129845592</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406495</v>
+        <v>406370</v>
       </c>
       <c r="R38" t="n">
-        <v>6832766</v>
+        <v>6832711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4333,7 +4333,7 @@
         <v>129845455</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845631</v>
+        <v>129845492</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4438,31 +4438,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4470,10 +4465,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406698</v>
+        <v>406591</v>
       </c>
       <c r="R40" t="n">
-        <v>6832875</v>
+        <v>6832966</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4514,28 +4509,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845611</v>
+        <v>129845660</v>
       </c>
       <c r="B41" t="n">
-        <v>79671</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4543,21 +4539,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4567,10 +4563,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406276</v>
+        <v>406728</v>
       </c>
       <c r="R41" t="n">
-        <v>6832761</v>
+        <v>6832848</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4629,10 +4625,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845431</v>
+        <v>129845491</v>
       </c>
       <c r="B42" t="n">
-        <v>79671</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4640,21 +4636,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4664,10 +4660,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406368</v>
+        <v>406588</v>
       </c>
       <c r="R42" t="n">
-        <v>6833201</v>
+        <v>6832866</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,10 +4722,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845456</v>
+        <v>129845490</v>
       </c>
       <c r="B43" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4737,21 +4733,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4761,10 +4757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406442</v>
+        <v>406560</v>
       </c>
       <c r="R43" t="n">
-        <v>6833041</v>
+        <v>6832885</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,10 +4819,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845490</v>
+        <v>129845601</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4834,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4858,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406560</v>
+        <v>406583</v>
       </c>
       <c r="R44" t="n">
-        <v>6832885</v>
+        <v>6832841</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4908,22 +4904,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845491</v>
+        <v>129845611</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4931,21 +4927,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4955,10 +4951,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406588</v>
+        <v>406276</v>
       </c>
       <c r="R45" t="n">
-        <v>6832866</v>
+        <v>6832761</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5005,22 +5001,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845492</v>
+        <v>129845431</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5028,37 +5024,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406591</v>
+        <v>406368</v>
       </c>
       <c r="R46" t="n">
-        <v>6832966</v>
+        <v>6833201</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5099,7 +5092,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5118,10 +5110,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845660</v>
+        <v>129845456</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5129,21 +5121,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5153,10 +5145,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406728</v>
+        <v>406442</v>
       </c>
       <c r="R47" t="n">
-        <v>6832848</v>
+        <v>6833041</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5203,22 +5195,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845601</v>
+        <v>129845631</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5226,34 +5218,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406583</v>
+        <v>406698</v>
       </c>
       <c r="R48" t="n">
-        <v>6832841</v>
+        <v>6832875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5315,7 +5315,7 @@
         <v>129845626</v>
       </c>
       <c r="B49" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5417,10 +5417,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845624</v>
+        <v>129845638</v>
       </c>
       <c r="B50" t="n">
-        <v>57896</v>
+        <v>78842</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5428,42 +5428,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406494</v>
+        <v>406290</v>
       </c>
       <c r="R50" t="n">
-        <v>6832766</v>
+        <v>6832900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5522,10 +5514,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845638</v>
+        <v>129845612</v>
       </c>
       <c r="B51" t="n">
-        <v>78839</v>
+        <v>79674</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5533,21 +5525,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5557,10 +5549,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406290</v>
+        <v>406379</v>
       </c>
       <c r="R51" t="n">
-        <v>6832900</v>
+        <v>6832756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5619,10 +5611,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845612</v>
+        <v>129845416</v>
       </c>
       <c r="B52" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5630,21 +5622,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5654,10 +5646,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406379</v>
+        <v>406362</v>
       </c>
       <c r="R52" t="n">
-        <v>6832756</v>
+        <v>6832766</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5704,66 +5696,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845461</v>
+        <v>129845589</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406589</v>
+        <v>406406</v>
       </c>
       <c r="R53" t="n">
-        <v>6832990</v>
+        <v>6833199</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5804,29 +5787,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845589</v>
+        <v>129845624</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>57895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5834,34 +5816,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406406</v>
+        <v>406494</v>
       </c>
       <c r="R54" t="n">
-        <v>6833199</v>
+        <v>6832766</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5920,45 +5910,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845416</v>
+        <v>129845461</v>
       </c>
       <c r="B55" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406362</v>
+        <v>406589</v>
       </c>
       <c r="R55" t="n">
-        <v>6832766</v>
+        <v>6832990</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5999,6 +5998,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845625</v>
+        <v>129845632</v>
       </c>
       <c r="B56" t="n">
-        <v>91620</v>
+        <v>57734</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,30 +6028,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6059,10 +6060,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406472</v>
+        <v>406667</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6832849</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6103,7 +6104,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845487</v>
+        <v>129845633</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6133,34 +6133,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406409</v>
+        <v>406674</v>
       </c>
       <c r="R57" t="n">
-        <v>6832824</v>
+        <v>6832801</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6207,22 +6215,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845466</v>
+        <v>129845627</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>57734</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6230,34 +6238,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406266</v>
+        <v>406539</v>
       </c>
       <c r="R58" t="n">
-        <v>6832810</v>
+        <v>6832767</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,12 +6320,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6319,7 +6335,7 @@
         <v>129845410</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6416,7 +6432,7 @@
         <v>129845602</v>
       </c>
       <c r="B60" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,10 +6526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845632</v>
+        <v>129845466</v>
       </c>
       <c r="B61" t="n">
-        <v>57733</v>
+        <v>78841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6521,42 +6537,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406667</v>
+        <v>406266</v>
       </c>
       <c r="R61" t="n">
-        <v>6832849</v>
+        <v>6832810</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6603,22 +6611,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845633</v>
+        <v>129845487</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,42 +6634,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406674</v>
+        <v>406409</v>
       </c>
       <c r="R62" t="n">
-        <v>6832801</v>
+        <v>6832824</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6708,22 +6708,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845627</v>
+        <v>129845625</v>
       </c>
       <c r="B63" t="n">
-        <v>57733</v>
+        <v>91623</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,31 +6731,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6763,7 +6762,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406539</v>
+        <v>406472</v>
       </c>
       <c r="R63" t="n">
         <v>6832767</v>
@@ -6807,6 +6806,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>129845435</v>
       </c>
       <c r="B65" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>129845654</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>129845493</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845452</v>
+        <v>129845590</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7234,42 +7234,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406630</v>
+        <v>406421</v>
       </c>
       <c r="R68" t="n">
-        <v>6832941</v>
+        <v>6833142</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7316,66 +7308,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845642</v>
+        <v>129845593</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406547</v>
+        <v>406451</v>
       </c>
       <c r="R69" t="n">
-        <v>6832775</v>
+        <v>6832712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7416,7 +7399,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7435,45 +7417,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845593</v>
+        <v>129845642</v>
       </c>
       <c r="B70" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406451</v>
+        <v>406547</v>
       </c>
       <c r="R70" t="n">
-        <v>6832712</v>
+        <v>6832775</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7514,6 +7505,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7532,10 +7524,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845590</v>
+        <v>129845434</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,21 +7535,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7567,10 +7559,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406421</v>
+        <v>406499</v>
       </c>
       <c r="R71" t="n">
-        <v>6833142</v>
+        <v>6833054</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7617,22 +7609,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845434</v>
+        <v>129845440</v>
       </c>
       <c r="B72" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7664,10 +7656,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406499</v>
+        <v>406445</v>
       </c>
       <c r="R72" t="n">
-        <v>6833054</v>
+        <v>6832921</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7726,10 +7718,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845440</v>
+        <v>129845605</v>
       </c>
       <c r="B73" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7761,10 +7753,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406445</v>
+        <v>406440</v>
       </c>
       <c r="R73" t="n">
-        <v>6832921</v>
+        <v>6833100</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7811,22 +7803,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845605</v>
+        <v>129845607</v>
       </c>
       <c r="B74" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7858,10 +7850,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406440</v>
+        <v>406407</v>
       </c>
       <c r="R74" t="n">
-        <v>6833100</v>
+        <v>6833199</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7920,10 +7912,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845607</v>
+        <v>129845452</v>
       </c>
       <c r="B75" t="n">
-        <v>79671</v>
+        <v>57734</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,34 +7923,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406407</v>
+        <v>406630</v>
       </c>
       <c r="R75" t="n">
-        <v>6833199</v>
+        <v>6832941</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,12 +8005,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8020,7 +8020,7 @@
         <v>129845486</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845415</v>
+        <v>129845420</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406317</v>
+        <v>406424</v>
       </c>
       <c r="R77" t="n">
-        <v>6832733</v>
+        <v>6832865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8211,10 +8211,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845600</v>
+        <v>129845415</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406582</v>
+        <v>406317</v>
       </c>
       <c r="R78" t="n">
-        <v>6832826</v>
+        <v>6832733</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8296,22 +8296,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845420</v>
+        <v>129845600</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406424</v>
+        <v>406582</v>
       </c>
       <c r="R79" t="n">
-        <v>6832865</v>
+        <v>6832826</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8393,12 +8393,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8408,7 +8408,7 @@
         <v>129845606</v>
       </c>
       <c r="B80" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8502,53 +8502,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845465</v>
+        <v>129845647</v>
       </c>
       <c r="B81" t="n">
-        <v>58106</v>
+        <v>78841</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406542</v>
+        <v>406274</v>
       </c>
       <c r="R81" t="n">
-        <v>6832915</v>
+        <v>6832759</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8595,22 +8587,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845444</v>
+        <v>129845621</v>
       </c>
       <c r="B82" t="n">
-        <v>91620</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8618,26 +8610,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8645,10 +8642,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406601</v>
+        <v>406672</v>
       </c>
       <c r="R82" t="n">
-        <v>6832858</v>
+        <v>6832840</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8689,29 +8686,28 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845647</v>
+        <v>129845444</v>
       </c>
       <c r="B83" t="n">
-        <v>78838</v>
+        <v>91623</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8719,34 +8715,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406274</v>
+        <v>406601</v>
       </c>
       <c r="R83" t="n">
-        <v>6832759</v>
+        <v>6832858</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8787,18 +8786,19 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8808,7 +8808,7 @@
         <v>129845454</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8910,27 +8910,27 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845621</v>
+        <v>129845465</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>58108</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8943,7 +8943,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406672</v>
+        <v>406542</v>
       </c>
       <c r="R85" t="n">
-        <v>6832840</v>
+        <v>6832915</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9003,22 +9003,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845656</v>
+        <v>129845653</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406480</v>
+        <v>406430</v>
       </c>
       <c r="R86" t="n">
         <v>6832777</v>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845653</v>
+        <v>129845656</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406430</v>
+        <v>406480</v>
       </c>
       <c r="R87" t="n">
         <v>6832777</v>
@@ -9212,7 +9212,7 @@
         <v>129845423</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>129845437</v>
       </c>
       <c r="B90" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>129845634</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9619,53 +9619,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845464</v>
+        <v>129845418</v>
       </c>
       <c r="B92" t="n">
-        <v>58106</v>
+        <v>79703</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406416</v>
+        <v>406377</v>
       </c>
       <c r="R92" t="n">
-        <v>6832880</v>
+        <v>6832837</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9724,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845457</v>
+        <v>129845408</v>
       </c>
       <c r="B93" t="n">
-        <v>78839</v>
+        <v>79703</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9735,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9759,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406265</v>
+        <v>406368</v>
       </c>
       <c r="R93" t="n">
-        <v>6832808</v>
+        <v>6833202</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9821,45 +9813,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845608</v>
+        <v>129845464</v>
       </c>
       <c r="B94" t="n">
-        <v>79671</v>
+        <v>58108</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406399</v>
+        <v>406416</v>
       </c>
       <c r="R94" t="n">
-        <v>6833177</v>
+        <v>6832880</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9906,22 +9906,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845479</v>
+        <v>129845457</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9929,21 +9929,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406408</v>
+        <v>406265</v>
       </c>
       <c r="R95" t="n">
-        <v>6832975</v>
+        <v>6832808</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10015,10 +10015,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845480</v>
+        <v>129845608</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10026,21 +10026,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406277</v>
+        <v>406399</v>
       </c>
       <c r="R96" t="n">
-        <v>6832823</v>
+        <v>6833177</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10100,22 +10100,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845418</v>
+        <v>129845479</v>
       </c>
       <c r="B97" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10123,21 +10123,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406377</v>
+        <v>406408</v>
       </c>
       <c r="R97" t="n">
-        <v>6832837</v>
+        <v>6832975</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10209,10 +10209,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845594</v>
+        <v>129845480</v>
       </c>
       <c r="B98" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10220,21 +10220,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406506</v>
+        <v>406277</v>
       </c>
       <c r="R98" t="n">
-        <v>6832725</v>
+        <v>6832823</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10294,22 +10294,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845408</v>
+        <v>129845594</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406368</v>
+        <v>406506</v>
       </c>
       <c r="R99" t="n">
-        <v>6833202</v>
+        <v>6832725</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10391,12 +10391,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
         <v>129845646</v>
       </c>
       <c r="B100" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>129845426</v>
       </c>
       <c r="B101" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>129845407</v>
       </c>
       <c r="B102" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>129845629</v>
       </c>
       <c r="B103" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>129845615</v>
       </c>
       <c r="B104" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>129845485</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845597</v>
+        <v>129845450</v>
       </c>
       <c r="B106" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,34 +11004,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406615</v>
+        <v>406508</v>
       </c>
       <c r="R106" t="n">
-        <v>6832770</v>
+        <v>6832877</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11078,22 +11086,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845595</v>
+        <v>129845448</v>
       </c>
       <c r="B107" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,34 +11109,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406455</v>
+        <v>406396</v>
       </c>
       <c r="R107" t="n">
-        <v>6832823</v>
+        <v>6832853</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11175,22 +11191,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845439</v>
+        <v>129845597</v>
       </c>
       <c r="B108" t="n">
-        <v>79671</v>
+        <v>79703</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11198,21 +11214,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11222,10 +11238,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406377</v>
+        <v>406615</v>
       </c>
       <c r="R108" t="n">
-        <v>6832840</v>
+        <v>6832770</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11272,22 +11288,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845450</v>
+        <v>129845595</v>
       </c>
       <c r="B109" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11295,42 +11311,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406508</v>
+        <v>406455</v>
       </c>
       <c r="R109" t="n">
-        <v>6832877</v>
+        <v>6832823</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11377,22 +11385,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845448</v>
+        <v>129845439</v>
       </c>
       <c r="B110" t="n">
-        <v>57733</v>
+        <v>79674</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11400,42 +11408,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406396</v>
+        <v>406377</v>
       </c>
       <c r="R110" t="n">
-        <v>6832853</v>
+        <v>6832840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11494,53 +11494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845644</v>
+        <v>129845433</v>
       </c>
       <c r="B111" t="n">
-        <v>58106</v>
+        <v>79674</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406457</v>
+        <v>406438</v>
       </c>
       <c r="R111" t="n">
-        <v>6832809</v>
+        <v>6833114</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11587,22 +11579,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845421</v>
+        <v>129845430</v>
       </c>
       <c r="B112" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11610,21 +11602,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11634,10 +11626,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406500</v>
+        <v>406465</v>
       </c>
       <c r="R112" t="n">
-        <v>6832933</v>
+        <v>6833093</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11696,54 +11688,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845640</v>
+        <v>129845421</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406404</v>
+        <v>406500</v>
       </c>
       <c r="R113" t="n">
-        <v>6832729</v>
+        <v>6832933</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11784,64 +11767,71 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845433</v>
+        <v>129845644</v>
       </c>
       <c r="B114" t="n">
-        <v>79671</v>
+        <v>58108</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406438</v>
+        <v>406457</v>
       </c>
       <c r="R114" t="n">
-        <v>6833114</v>
+        <v>6832809</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11888,57 +11878,66 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845430</v>
+        <v>129845640</v>
       </c>
       <c r="B115" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406465</v>
+        <v>406404</v>
       </c>
       <c r="R115" t="n">
-        <v>6833093</v>
+        <v>6832729</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11979,18 +11978,19 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -12000,7 +12000,7 @@
         <v>129845596</v>
       </c>
       <c r="B116" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845628</v>
+        <v>129845458</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>78842</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12105,42 +12105,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406541</v>
+        <v>406531</v>
       </c>
       <c r="R117" t="n">
-        <v>6832823</v>
+        <v>6832927</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12187,22 +12179,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845635</v>
+        <v>129845436</v>
       </c>
       <c r="B118" t="n">
-        <v>57733</v>
+        <v>79674</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12210,42 +12202,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406677</v>
+        <v>406315</v>
       </c>
       <c r="R118" t="n">
-        <v>6832986</v>
+        <v>6832667</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12292,22 +12276,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845458</v>
+        <v>129845628</v>
       </c>
       <c r="B119" t="n">
-        <v>78839</v>
+        <v>57734</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12315,34 +12299,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406531</v>
+        <v>406541</v>
       </c>
       <c r="R119" t="n">
-        <v>6832927</v>
+        <v>6832823</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12389,22 +12381,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845436</v>
+        <v>129845635</v>
       </c>
       <c r="B120" t="n">
-        <v>79671</v>
+        <v>57734</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,34 +12404,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406315</v>
+        <v>406677</v>
       </c>
       <c r="R120" t="n">
-        <v>6832667</v>
+        <v>6832986</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,22 +12486,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845591</v>
+        <v>129845588</v>
       </c>
       <c r="B121" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12533,10 +12533,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406439</v>
+        <v>406440</v>
       </c>
       <c r="R121" t="n">
-        <v>6833139</v>
+        <v>6833101</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12595,10 +12595,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129845588</v>
+        <v>129845591</v>
       </c>
       <c r="B122" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406440</v>
+        <v>406439</v>
       </c>
       <c r="R122" t="n">
-        <v>6833101</v>
+        <v>6833139</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12692,10 +12692,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845451</v>
+        <v>129845432</v>
       </c>
       <c r="B123" t="n">
-        <v>57733</v>
+        <v>79674</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12703,42 +12703,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406595</v>
+        <v>406373</v>
       </c>
       <c r="R123" t="n">
-        <v>6832931</v>
+        <v>6833176</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12797,10 +12789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845494</v>
+        <v>129845495</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12832,10 +12824,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406710</v>
+        <v>406668</v>
       </c>
       <c r="R124" t="n">
-        <v>6832990</v>
+        <v>6833007</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12894,10 +12886,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845495</v>
+        <v>129845484</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12923,16 +12915,19 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406668</v>
+        <v>406310</v>
       </c>
       <c r="R125" t="n">
-        <v>6833007</v>
+        <v>6832729</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12973,6 +12968,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12991,10 +12987,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845484</v>
+        <v>129845494</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13020,19 +13016,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406310</v>
+        <v>406710</v>
       </c>
       <c r="R126" t="n">
-        <v>6832729</v>
+        <v>6832990</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13073,7 +13066,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13092,10 +13084,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845432</v>
+        <v>129845451</v>
       </c>
       <c r="B127" t="n">
-        <v>79671</v>
+        <v>57734</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13103,34 +13095,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406373</v>
+        <v>406595</v>
       </c>
       <c r="R127" t="n">
-        <v>6833176</v>
+        <v>6832931</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845489</v>
+        <v>129845414</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13200,21 +13200,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406542</v>
+        <v>406313</v>
       </c>
       <c r="R128" t="n">
-        <v>6832915</v>
+        <v>6832656</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13286,10 +13286,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845658</v>
+        <v>129845424</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13297,21 +13297,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406563</v>
+        <v>406533</v>
       </c>
       <c r="R129" t="n">
-        <v>6832887</v>
+        <v>6832861</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13371,57 +13371,65 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129845482</v>
+        <v>129845623</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>56927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406282</v>
+        <v>406310</v>
       </c>
       <c r="R130" t="n">
-        <v>6832624</v>
+        <v>6832901</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13468,22 +13476,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845411</v>
+        <v>129845482</v>
       </c>
       <c r="B131" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13491,21 +13499,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13515,10 +13523,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406442</v>
+        <v>406282</v>
       </c>
       <c r="R131" t="n">
-        <v>6833040</v>
+        <v>6832624</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13577,10 +13585,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845414</v>
+        <v>129845489</v>
       </c>
       <c r="B132" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13588,21 +13596,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13612,10 +13620,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406313</v>
+        <v>406542</v>
       </c>
       <c r="R132" t="n">
-        <v>6832656</v>
+        <v>6832915</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13674,10 +13682,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845603</v>
+        <v>129845658</v>
       </c>
       <c r="B133" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13685,21 +13693,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13709,10 +13717,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406764</v>
+        <v>406563</v>
       </c>
       <c r="R133" t="n">
-        <v>6832925</v>
+        <v>6832887</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13771,10 +13779,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845424</v>
+        <v>129845453</v>
       </c>
       <c r="B134" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13782,34 +13790,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406533</v>
+        <v>406716</v>
       </c>
       <c r="R134" t="n">
-        <v>6832861</v>
+        <v>6832970</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13868,10 +13884,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845453</v>
+        <v>129845411</v>
       </c>
       <c r="B135" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13879,42 +13895,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406716</v>
+        <v>406442</v>
       </c>
       <c r="R135" t="n">
-        <v>6832970</v>
+        <v>6833040</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13973,53 +13981,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845623</v>
+        <v>129845603</v>
       </c>
       <c r="B136" t="n">
-        <v>56926</v>
+        <v>79703</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406310</v>
+        <v>406764</v>
       </c>
       <c r="R136" t="n">
-        <v>6832901</v>
+        <v>6832925</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
         <v>129845446</v>
       </c>
       <c r="B137" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>129845478</v>
       </c>
       <c r="B138" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>129845497</v>
       </c>
       <c r="B139" t="n">
-        <v>92022</v>
+        <v>92025</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845598</v>
+        <v>129845438</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406626</v>
+        <v>406361</v>
       </c>
       <c r="R2" t="n">
-        <v>6832781</v>
+        <v>6832815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845425</v>
+        <v>129845441</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406832</v>
+        <v>406638</v>
       </c>
       <c r="R3" t="n">
-        <v>6832816</v>
+        <v>6832869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845419</v>
+        <v>129845599</v>
       </c>
       <c r="B4" t="n">
         <v>79703</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406387</v>
+        <v>406635</v>
       </c>
       <c r="R4" t="n">
-        <v>6832850</v>
+        <v>6832779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845599</v>
+        <v>129845598</v>
       </c>
       <c r="B5" t="n">
         <v>79703</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406635</v>
+        <v>406626</v>
       </c>
       <c r="R5" t="n">
-        <v>6832779</v>
+        <v>6832781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845438</v>
+        <v>129845425</v>
       </c>
       <c r="B6" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406361</v>
+        <v>406832</v>
       </c>
       <c r="R6" t="n">
-        <v>6832815</v>
+        <v>6832816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845441</v>
+        <v>129845419</v>
       </c>
       <c r="B7" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406638</v>
+        <v>406387</v>
       </c>
       <c r="R7" t="n">
-        <v>6832869</v>
+        <v>6832850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845661</v>
+        <v>129845630</v>
       </c>
       <c r="B8" t="n">
-        <v>78750</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406352</v>
+        <v>406631</v>
       </c>
       <c r="R8" t="n">
-        <v>6832709</v>
+        <v>6832822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845630</v>
+        <v>129845443</v>
       </c>
       <c r="B9" t="n">
-        <v>57734</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1387,7 +1395,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1397,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406631</v>
+        <v>406333</v>
       </c>
       <c r="R9" t="n">
-        <v>6832822</v>
+        <v>6832733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,22 +1455,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845427</v>
+        <v>129845661</v>
       </c>
       <c r="B10" t="n">
-        <v>79703</v>
+        <v>78750</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406794</v>
+        <v>406352</v>
       </c>
       <c r="R10" t="n">
-        <v>6832934</v>
+        <v>6832709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,19 +1552,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845417</v>
+        <v>129845427</v>
       </c>
       <c r="B11" t="n">
         <v>79703</v>
@@ -1591,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406346</v>
+        <v>406794</v>
       </c>
       <c r="R11" t="n">
-        <v>6832798</v>
+        <v>6832934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845443</v>
+        <v>129845417</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>79703</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,42 +1672,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406333</v>
+        <v>406346</v>
       </c>
       <c r="R12" t="n">
-        <v>6832733</v>
+        <v>6832798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845655</v>
+        <v>129845604</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406473</v>
+        <v>406424</v>
       </c>
       <c r="R13" t="n">
-        <v>6832798</v>
+        <v>6832657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845604</v>
+        <v>129845467</v>
       </c>
       <c r="B14" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,34 +1866,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406424</v>
+        <v>406359</v>
       </c>
       <c r="R14" t="n">
-        <v>6832657</v>
+        <v>6832764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,55 +1937,62 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845467</v>
+        <v>129845462</v>
       </c>
       <c r="B15" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1990,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406359</v>
+        <v>406713</v>
       </c>
       <c r="R15" t="n">
-        <v>6832764</v>
+        <v>6832904</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845429</v>
+        <v>129845655</v>
       </c>
       <c r="B16" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406472</v>
+        <v>406473</v>
       </c>
       <c r="R16" t="n">
-        <v>6833103</v>
+        <v>6832798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,19 +2148,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845613</v>
+        <v>129845610</v>
       </c>
       <c r="B17" t="n">
         <v>79674</v>
@@ -2185,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406388</v>
+        <v>406262</v>
       </c>
       <c r="R17" t="n">
-        <v>6832683</v>
+        <v>6832854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,54 +2257,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845462</v>
+        <v>129845614</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406713</v>
+        <v>406492</v>
       </c>
       <c r="R18" t="n">
-        <v>6832904</v>
+        <v>6832753</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2335,26 +2336,25 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845610</v>
+        <v>129845618</v>
       </c>
       <c r="B19" t="n">
         <v>79674</v>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406262</v>
+        <v>406791</v>
       </c>
       <c r="R19" t="n">
-        <v>6832854</v>
+        <v>6832845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845614</v>
+        <v>129845429</v>
       </c>
       <c r="B20" t="n">
         <v>79674</v>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406492</v>
+        <v>406472</v>
       </c>
       <c r="R20" t="n">
-        <v>6832753</v>
+        <v>6833103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,19 +2536,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845618</v>
+        <v>129845613</v>
       </c>
       <c r="B21" t="n">
         <v>79674</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406791</v>
+        <v>406388</v>
       </c>
       <c r="R21" t="n">
-        <v>6832845</v>
+        <v>6832683</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,54 +2742,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129845460</v>
+        <v>129845488</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406431</v>
+        <v>406528</v>
       </c>
       <c r="R23" t="n">
-        <v>6832825</v>
+        <v>6832873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,7 +2821,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2849,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129845619</v>
+        <v>129845652</v>
       </c>
       <c r="B24" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406776</v>
+        <v>406408</v>
       </c>
       <c r="R24" t="n">
-        <v>6832860</v>
+        <v>6832778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,7 +2936,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129845488</v>
+        <v>129845659</v>
       </c>
       <c r="B25" t="n">
         <v>79084</v>
@@ -2981,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406528</v>
+        <v>406556</v>
       </c>
       <c r="R25" t="n">
-        <v>6832873</v>
+        <v>6832846</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,22 +3021,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845652</v>
+        <v>129845619</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406408</v>
+        <v>406776</v>
       </c>
       <c r="R26" t="n">
-        <v>6832778</v>
+        <v>6832860</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,45 +3130,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845659</v>
+        <v>129845460</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406556</v>
+        <v>406431</v>
       </c>
       <c r="R27" t="n">
-        <v>6832846</v>
+        <v>6832825</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3219,18 +3218,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3641,54 +3641,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845463</v>
+        <v>129845412</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406746</v>
+        <v>406426</v>
       </c>
       <c r="R32" t="n">
-        <v>6832985</v>
+        <v>6832990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3729,7 +3720,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3748,45 +3738,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845639</v>
+        <v>129845463</v>
       </c>
       <c r="B33" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406276</v>
+        <v>406746</v>
       </c>
       <c r="R33" t="n">
-        <v>6832761</v>
+        <v>6832985</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3827,28 +3826,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845412</v>
+        <v>129845639</v>
       </c>
       <c r="B34" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406426</v>
+        <v>406276</v>
       </c>
       <c r="R34" t="n">
-        <v>6832990</v>
+        <v>6832761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3930,22 +3930,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845657</v>
+        <v>129845455</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406495</v>
+        <v>406486</v>
       </c>
       <c r="R35" t="n">
-        <v>6832766</v>
+        <v>6833057</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,19 +4027,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845481</v>
+        <v>129845657</v>
       </c>
       <c r="B36" t="n">
         <v>79084</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406278</v>
+        <v>406495</v>
       </c>
       <c r="R36" t="n">
-        <v>6832795</v>
+        <v>6832766</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4124,19 +4124,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845483</v>
+        <v>129845481</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406344</v>
+        <v>406278</v>
       </c>
       <c r="R37" t="n">
-        <v>6832706</v>
+        <v>6832795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845592</v>
+        <v>129845483</v>
       </c>
       <c r="B38" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406370</v>
+        <v>406344</v>
       </c>
       <c r="R38" t="n">
-        <v>6832711</v>
+        <v>6832706</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,22 +4318,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129845455</v>
+        <v>129845592</v>
       </c>
       <c r="B39" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406486</v>
+        <v>406370</v>
       </c>
       <c r="R39" t="n">
-        <v>6833057</v>
+        <v>6832711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,12 +4415,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845611</v>
+        <v>129845631</v>
       </c>
       <c r="B45" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,34 +4927,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406276</v>
+        <v>406698</v>
       </c>
       <c r="R45" t="n">
-        <v>6832761</v>
+        <v>6832875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5013,7 +5021,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845431</v>
+        <v>129845611</v>
       </c>
       <c r="B46" t="n">
         <v>79674</v>
@@ -5048,10 +5056,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406368</v>
+        <v>406276</v>
       </c>
       <c r="R46" t="n">
-        <v>6833201</v>
+        <v>6832761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,22 +5106,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845456</v>
+        <v>129845431</v>
       </c>
       <c r="B47" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5121,21 +5129,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5145,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406442</v>
+        <v>406368</v>
       </c>
       <c r="R47" t="n">
-        <v>6833041</v>
+        <v>6833201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5207,10 +5215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845631</v>
+        <v>129845456</v>
       </c>
       <c r="B48" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5218,42 +5226,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406698</v>
+        <v>406442</v>
       </c>
       <c r="R48" t="n">
-        <v>6832875</v>
+        <v>6833041</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5300,12 +5300,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5417,10 +5417,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845638</v>
+        <v>129845624</v>
       </c>
       <c r="B50" t="n">
-        <v>78842</v>
+        <v>57895</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5428,34 +5428,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406290</v>
+        <v>406494</v>
       </c>
       <c r="R50" t="n">
-        <v>6832900</v>
+        <v>6832766</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5514,10 +5522,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845612</v>
+        <v>129845416</v>
       </c>
       <c r="B51" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,21 +5533,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5549,10 +5557,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406379</v>
+        <v>406362</v>
       </c>
       <c r="R51" t="n">
-        <v>6832756</v>
+        <v>6832766</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,19 +5607,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845416</v>
+        <v>129845589</v>
       </c>
       <c r="B52" t="n">
         <v>79703</v>
@@ -5646,10 +5654,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406362</v>
+        <v>406406</v>
       </c>
       <c r="R52" t="n">
-        <v>6832766</v>
+        <v>6833199</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5696,57 +5704,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845589</v>
+        <v>129845461</v>
       </c>
       <c r="B53" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406406</v>
+        <v>406589</v>
       </c>
       <c r="R53" t="n">
-        <v>6833199</v>
+        <v>6832990</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5787,28 +5804,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845624</v>
+        <v>129845638</v>
       </c>
       <c r="B54" t="n">
-        <v>57895</v>
+        <v>78842</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5816,42 +5834,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406494</v>
+        <v>406290</v>
       </c>
       <c r="R54" t="n">
-        <v>6832766</v>
+        <v>6832900</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5910,54 +5920,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845461</v>
+        <v>129845612</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406589</v>
+        <v>406379</v>
       </c>
       <c r="R55" t="n">
-        <v>6832990</v>
+        <v>6832756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5998,29 +5999,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845632</v>
+        <v>129845435</v>
       </c>
       <c r="B56" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,42 +6028,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406667</v>
+        <v>406455</v>
       </c>
       <c r="R56" t="n">
-        <v>6832849</v>
+        <v>6833027</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6110,22 +6102,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845633</v>
+        <v>129845625</v>
       </c>
       <c r="B57" t="n">
-        <v>57734</v>
+        <v>91623</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6133,31 +6125,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6165,10 +6156,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406674</v>
+        <v>406472</v>
       </c>
       <c r="R57" t="n">
-        <v>6832801</v>
+        <v>6832767</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,6 +6200,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6227,10 +6219,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845627</v>
+        <v>129845487</v>
       </c>
       <c r="B58" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6238,42 +6230,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406539</v>
+        <v>406409</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6832824</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6320,19 +6304,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845410</v>
+        <v>129845602</v>
       </c>
       <c r="B59" t="n">
         <v>79703</v>
@@ -6367,10 +6351,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406487</v>
+        <v>406791</v>
       </c>
       <c r="R59" t="n">
-        <v>6833064</v>
+        <v>6832844</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6417,22 +6401,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845602</v>
+        <v>129845466</v>
       </c>
       <c r="B60" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6440,21 +6424,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6448,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406791</v>
+        <v>406266</v>
       </c>
       <c r="R60" t="n">
-        <v>6832844</v>
+        <v>6832810</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,22 +6498,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845466</v>
+        <v>129845410</v>
       </c>
       <c r="B61" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6537,21 +6521,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6545,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406266</v>
+        <v>406487</v>
       </c>
       <c r="R61" t="n">
-        <v>6832810</v>
+        <v>6833064</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6623,10 +6607,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845487</v>
+        <v>129845632</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6634,34 +6618,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406409</v>
+        <v>406667</v>
       </c>
       <c r="R62" t="n">
-        <v>6832824</v>
+        <v>6832849</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6708,22 +6700,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845625</v>
+        <v>129845633</v>
       </c>
       <c r="B63" t="n">
-        <v>91623</v>
+        <v>57734</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,30 +6723,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6762,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406472</v>
+        <v>406674</v>
       </c>
       <c r="R63" t="n">
-        <v>6832767</v>
+        <v>6832801</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6806,7 +6799,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6825,41 +6817,40 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845459</v>
+        <v>129845627</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6869,10 +6860,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406331</v>
+        <v>406539</v>
       </c>
       <c r="R64" t="n">
-        <v>6832715</v>
+        <v>6832767</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6913,64 +6904,72 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845435</v>
+        <v>129845459</v>
       </c>
       <c r="B65" t="n">
-        <v>79674</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406455</v>
+        <v>406331</v>
       </c>
       <c r="R65" t="n">
-        <v>6833027</v>
+        <v>6832715</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,6 +7010,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845654</v>
+        <v>129845452</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,34 +7040,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406460</v>
+        <v>406630</v>
       </c>
       <c r="R66" t="n">
-        <v>6832823</v>
+        <v>6832941</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7114,57 +7122,66 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845493</v>
+        <v>129845642</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406785</v>
+        <v>406547</v>
       </c>
       <c r="R67" t="n">
-        <v>6832912</v>
+        <v>6832775</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7205,28 +7222,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845590</v>
+        <v>129845654</v>
       </c>
       <c r="B68" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7234,21 +7252,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7258,10 +7276,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406421</v>
+        <v>406460</v>
       </c>
       <c r="R68" t="n">
-        <v>6833142</v>
+        <v>6832823</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7320,10 +7338,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845593</v>
+        <v>129845493</v>
       </c>
       <c r="B69" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7331,21 +7349,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7355,10 +7373,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406451</v>
+        <v>406785</v>
       </c>
       <c r="R69" t="n">
-        <v>6832712</v>
+        <v>6832912</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7405,66 +7423,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845642</v>
+        <v>129845590</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406547</v>
+        <v>406421</v>
       </c>
       <c r="R70" t="n">
-        <v>6832775</v>
+        <v>6833142</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7505,7 +7514,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7524,10 +7532,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845434</v>
+        <v>129845593</v>
       </c>
       <c r="B71" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7535,21 +7543,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7559,10 +7567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406499</v>
+        <v>406451</v>
       </c>
       <c r="R71" t="n">
-        <v>6833054</v>
+        <v>6832712</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7609,19 +7617,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845440</v>
+        <v>129845434</v>
       </c>
       <c r="B72" t="n">
         <v>79674</v>
@@ -7656,10 +7664,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406445</v>
+        <v>406499</v>
       </c>
       <c r="R72" t="n">
-        <v>6832921</v>
+        <v>6833054</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7718,7 +7726,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845605</v>
+        <v>129845440</v>
       </c>
       <c r="B73" t="n">
         <v>79674</v>
@@ -7753,10 +7761,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406440</v>
+        <v>406445</v>
       </c>
       <c r="R73" t="n">
-        <v>6833100</v>
+        <v>6832921</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7803,19 +7811,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845607</v>
+        <v>129845605</v>
       </c>
       <c r="B74" t="n">
         <v>79674</v>
@@ -7850,10 +7858,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406407</v>
+        <v>406440</v>
       </c>
       <c r="R74" t="n">
-        <v>6833199</v>
+        <v>6833100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7912,10 +7920,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845452</v>
+        <v>129845607</v>
       </c>
       <c r="B75" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7923,42 +7931,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406630</v>
+        <v>406407</v>
       </c>
       <c r="R75" t="n">
-        <v>6832941</v>
+        <v>6833199</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,22 +8005,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129845486</v>
+        <v>129845600</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,21 +8028,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406350</v>
+        <v>406582</v>
       </c>
       <c r="R76" t="n">
-        <v>6832772</v>
+        <v>6832826</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8102,22 +8102,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845420</v>
+        <v>129845486</v>
       </c>
       <c r="B77" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406424</v>
+        <v>406350</v>
       </c>
       <c r="R77" t="n">
-        <v>6832865</v>
+        <v>6832772</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8211,7 +8211,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845415</v>
+        <v>129845420</v>
       </c>
       <c r="B78" t="n">
         <v>79703</v>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406317</v>
+        <v>406424</v>
       </c>
       <c r="R78" t="n">
-        <v>6832733</v>
+        <v>6832865</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8308,7 +8308,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845600</v>
+        <v>129845415</v>
       </c>
       <c r="B79" t="n">
         <v>79703</v>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406582</v>
+        <v>406317</v>
       </c>
       <c r="R79" t="n">
-        <v>6832826</v>
+        <v>6832733</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8393,12 +8393,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845647</v>
+        <v>129845444</v>
       </c>
       <c r="B81" t="n">
-        <v>78841</v>
+        <v>91623</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,34 +8513,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406274</v>
+        <v>406601</v>
       </c>
       <c r="R81" t="n">
-        <v>6832759</v>
+        <v>6832858</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8581,28 +8584,29 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845621</v>
+        <v>129845647</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>78841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8610,42 +8614,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406672</v>
+        <v>406274</v>
       </c>
       <c r="R82" t="n">
-        <v>6832840</v>
+        <v>6832759</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8704,10 +8700,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845444</v>
+        <v>129845454</v>
       </c>
       <c r="B83" t="n">
-        <v>91623</v>
+        <v>57734</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,26 +8711,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8742,10 +8743,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406601</v>
+        <v>406675</v>
       </c>
       <c r="R83" t="n">
-        <v>6832858</v>
+        <v>6832988</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8786,7 +8787,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8805,10 +8805,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845454</v>
+        <v>129845621</v>
       </c>
       <c r="B84" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8838,7 +8838,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406675</v>
+        <v>406672</v>
       </c>
       <c r="R84" t="n">
-        <v>6832988</v>
+        <v>6832840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8898,12 +8898,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9209,45 +9209,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845423</v>
+        <v>129845641</v>
       </c>
       <c r="B88" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406531</v>
+        <v>406618</v>
       </c>
       <c r="R88" t="n">
-        <v>6832868</v>
+        <v>6832813</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9288,72 +9297,64 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845641</v>
+        <v>129845423</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406618</v>
+        <v>406531</v>
       </c>
       <c r="R89" t="n">
-        <v>6832813</v>
+        <v>6832868</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9394,19 +9395,18 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845634</v>
+        <v>129845479</v>
       </c>
       <c r="B91" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,42 +9525,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406781</v>
+        <v>406408</v>
       </c>
       <c r="R91" t="n">
-        <v>6832843</v>
+        <v>6832975</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9607,22 +9599,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845418</v>
+        <v>129845480</v>
       </c>
       <c r="B92" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9630,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9654,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406377</v>
+        <v>406277</v>
       </c>
       <c r="R92" t="n">
-        <v>6832837</v>
+        <v>6832823</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,7 +9708,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845408</v>
+        <v>129845594</v>
       </c>
       <c r="B93" t="n">
         <v>79703</v>
@@ -9751,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406368</v>
+        <v>406506</v>
       </c>
       <c r="R93" t="n">
-        <v>6833202</v>
+        <v>6832725</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9801,65 +9793,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845464</v>
+        <v>129845418</v>
       </c>
       <c r="B94" t="n">
-        <v>58108</v>
+        <v>79703</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406416</v>
+        <v>406377</v>
       </c>
       <c r="R94" t="n">
-        <v>6832880</v>
+        <v>6832837</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9918,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845457</v>
+        <v>129845408</v>
       </c>
       <c r="B95" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9929,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9953,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406265</v>
+        <v>406368</v>
       </c>
       <c r="R95" t="n">
-        <v>6832808</v>
+        <v>6833202</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10015,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845608</v>
+        <v>129845634</v>
       </c>
       <c r="B96" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10026,34 +10010,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406399</v>
+        <v>406781</v>
       </c>
       <c r="R96" t="n">
-        <v>6833177</v>
+        <v>6832843</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10112,45 +10104,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845479</v>
+        <v>129845464</v>
       </c>
       <c r="B97" t="n">
-        <v>79084</v>
+        <v>58108</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406408</v>
+        <v>406416</v>
       </c>
       <c r="R97" t="n">
-        <v>6832975</v>
+        <v>6832880</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10209,10 +10209,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845480</v>
+        <v>129845457</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10220,21 +10220,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406277</v>
+        <v>406265</v>
       </c>
       <c r="R98" t="n">
-        <v>6832823</v>
+        <v>6832808</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845594</v>
+        <v>129845608</v>
       </c>
       <c r="B99" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406506</v>
+        <v>406399</v>
       </c>
       <c r="R99" t="n">
-        <v>6832725</v>
+        <v>6833177</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10403,10 +10403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845646</v>
+        <v>129845407</v>
       </c>
       <c r="B100" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,21 +10414,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406290</v>
+        <v>406416</v>
       </c>
       <c r="R100" t="n">
-        <v>6832901</v>
+        <v>6833166</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10488,22 +10488,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845426</v>
+        <v>129845629</v>
       </c>
       <c r="B101" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10511,34 +10511,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406796</v>
+        <v>406618</v>
       </c>
       <c r="R101" t="n">
-        <v>6832917</v>
+        <v>6832773</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10585,22 +10593,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B102" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,21 +10616,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10632,10 +10640,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R102" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10682,22 +10690,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845629</v>
+        <v>129845646</v>
       </c>
       <c r="B103" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,42 +10713,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406618</v>
+        <v>406290</v>
       </c>
       <c r="R103" t="n">
-        <v>6832773</v>
+        <v>6832901</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10799,10 +10799,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845615</v>
+        <v>129845426</v>
       </c>
       <c r="B104" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406583</v>
+        <v>406796</v>
       </c>
       <c r="R104" t="n">
-        <v>6832911</v>
+        <v>6832917</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,22 +10884,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845485</v>
+        <v>129845439</v>
       </c>
       <c r="B105" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406320</v>
+        <v>406377</v>
       </c>
       <c r="R105" t="n">
-        <v>6832742</v>
+        <v>6832840</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10993,10 +10993,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845450</v>
+        <v>129845485</v>
       </c>
       <c r="B106" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,42 +11004,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406508</v>
+        <v>406320</v>
       </c>
       <c r="R106" t="n">
-        <v>6832877</v>
+        <v>6832742</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11098,10 +11090,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845448</v>
+        <v>129845595</v>
       </c>
       <c r="B107" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11109,42 +11101,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406396</v>
+        <v>406455</v>
       </c>
       <c r="R107" t="n">
-        <v>6832853</v>
+        <v>6832823</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11191,12 +11175,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11300,10 +11284,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845595</v>
+        <v>129845450</v>
       </c>
       <c r="B109" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11311,34 +11295,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406455</v>
+        <v>406508</v>
       </c>
       <c r="R109" t="n">
-        <v>6832823</v>
+        <v>6832877</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11385,22 +11377,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845439</v>
+        <v>129845448</v>
       </c>
       <c r="B110" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11408,34 +11400,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406377</v>
+        <v>406396</v>
       </c>
       <c r="R110" t="n">
-        <v>6832840</v>
+        <v>6832853</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11494,45 +11494,53 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845433</v>
+        <v>129845644</v>
       </c>
       <c r="B111" t="n">
-        <v>79674</v>
+        <v>58108</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406438</v>
+        <v>406457</v>
       </c>
       <c r="R111" t="n">
-        <v>6833114</v>
+        <v>6832809</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11579,19 +11587,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845430</v>
+        <v>129845433</v>
       </c>
       <c r="B112" t="n">
         <v>79674</v>
@@ -11626,10 +11634,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406465</v>
+        <v>406438</v>
       </c>
       <c r="R112" t="n">
-        <v>6833093</v>
+        <v>6833114</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11688,10 +11696,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845421</v>
+        <v>129845430</v>
       </c>
       <c r="B113" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11699,21 +11707,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11723,10 +11731,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406500</v>
+        <v>406465</v>
       </c>
       <c r="R113" t="n">
-        <v>6832933</v>
+        <v>6833093</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11785,53 +11793,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845644</v>
+        <v>129845421</v>
       </c>
       <c r="B114" t="n">
-        <v>58108</v>
+        <v>79703</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406457</v>
+        <v>406500</v>
       </c>
       <c r="R114" t="n">
-        <v>6832809</v>
+        <v>6832933</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11878,12 +11878,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845458</v>
+        <v>129845628</v>
       </c>
       <c r="B117" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12105,34 +12105,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406531</v>
+        <v>406541</v>
       </c>
       <c r="R117" t="n">
-        <v>6832927</v>
+        <v>6832823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12179,22 +12187,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845436</v>
+        <v>129845635</v>
       </c>
       <c r="B118" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12202,34 +12210,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406315</v>
+        <v>406677</v>
       </c>
       <c r="R118" t="n">
-        <v>6832667</v>
+        <v>6832986</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12276,22 +12292,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845628</v>
+        <v>129845458</v>
       </c>
       <c r="B119" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12299,42 +12315,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406541</v>
+        <v>406531</v>
       </c>
       <c r="R119" t="n">
-        <v>6832823</v>
+        <v>6832927</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12381,22 +12389,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845635</v>
+        <v>129845436</v>
       </c>
       <c r="B120" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12404,42 +12412,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406677</v>
+        <v>406315</v>
       </c>
       <c r="R120" t="n">
-        <v>6832986</v>
+        <v>6832667</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,22 +12486,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845588</v>
+        <v>129845495</v>
       </c>
       <c r="B121" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12509,21 +12509,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12533,10 +12533,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406440</v>
+        <v>406668</v>
       </c>
       <c r="R121" t="n">
-        <v>6833101</v>
+        <v>6833007</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12583,22 +12583,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129845591</v>
+        <v>129845484</v>
       </c>
       <c r="B122" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12606,34 +12606,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406439</v>
+        <v>406310</v>
       </c>
       <c r="R122" t="n">
-        <v>6833139</v>
+        <v>6832729</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12674,28 +12677,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845432</v>
+        <v>129845494</v>
       </c>
       <c r="B123" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12703,21 +12707,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12727,10 +12731,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406373</v>
+        <v>406710</v>
       </c>
       <c r="R123" t="n">
-        <v>6833176</v>
+        <v>6832990</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12789,10 +12793,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845495</v>
+        <v>129845591</v>
       </c>
       <c r="B124" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12800,21 +12804,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12824,10 +12828,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406668</v>
+        <v>406439</v>
       </c>
       <c r="R124" t="n">
-        <v>6833007</v>
+        <v>6833139</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12874,22 +12878,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845484</v>
+        <v>129845588</v>
       </c>
       <c r="B125" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12897,37 +12901,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406310</v>
+        <v>406440</v>
       </c>
       <c r="R125" t="n">
-        <v>6832729</v>
+        <v>6833101</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12968,29 +12969,28 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845494</v>
+        <v>129845451</v>
       </c>
       <c r="B126" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12998,34 +12998,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406710</v>
+        <v>406595</v>
       </c>
       <c r="R126" t="n">
-        <v>6832990</v>
+        <v>6832931</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13084,10 +13092,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845451</v>
+        <v>129845432</v>
       </c>
       <c r="B127" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13095,42 +13103,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406595</v>
+        <v>406373</v>
       </c>
       <c r="R127" t="n">
-        <v>6832931</v>
+        <v>6833176</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845414</v>
+        <v>129845482</v>
       </c>
       <c r="B128" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13200,21 +13200,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406313</v>
+        <v>406282</v>
       </c>
       <c r="R128" t="n">
-        <v>6832656</v>
+        <v>6832624</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13286,10 +13286,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845424</v>
+        <v>129845489</v>
       </c>
       <c r="B129" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13297,21 +13297,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406533</v>
+        <v>406542</v>
       </c>
       <c r="R129" t="n">
-        <v>6832861</v>
+        <v>6832915</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13383,53 +13383,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129845623</v>
+        <v>129845658</v>
       </c>
       <c r="B130" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406310</v>
+        <v>406563</v>
       </c>
       <c r="R130" t="n">
-        <v>6832901</v>
+        <v>6832887</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13488,45 +13480,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845482</v>
+        <v>129845623</v>
       </c>
       <c r="B131" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406282</v>
+        <v>406310</v>
       </c>
       <c r="R131" t="n">
-        <v>6832624</v>
+        <v>6832901</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13573,22 +13573,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845489</v>
+        <v>129845603</v>
       </c>
       <c r="B132" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13596,21 +13596,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13620,10 +13620,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406542</v>
+        <v>406764</v>
       </c>
       <c r="R132" t="n">
-        <v>6832915</v>
+        <v>6832925</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13670,22 +13670,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845658</v>
+        <v>129845414</v>
       </c>
       <c r="B133" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13693,21 +13693,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406563</v>
+        <v>406313</v>
       </c>
       <c r="R133" t="n">
-        <v>6832887</v>
+        <v>6832656</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13767,22 +13767,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845453</v>
+        <v>129845411</v>
       </c>
       <c r="B134" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13790,42 +13790,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406716</v>
+        <v>406442</v>
       </c>
       <c r="R134" t="n">
-        <v>6832970</v>
+        <v>6833040</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13884,7 +13876,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845411</v>
+        <v>129845424</v>
       </c>
       <c r="B135" t="n">
         <v>79703</v>
@@ -13919,10 +13911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406442</v>
+        <v>406533</v>
       </c>
       <c r="R135" t="n">
-        <v>6833040</v>
+        <v>6832861</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13981,10 +13973,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845603</v>
+        <v>129845453</v>
       </c>
       <c r="B136" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13992,34 +13984,42 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406764</v>
+        <v>406716</v>
       </c>
       <c r="R136" t="n">
-        <v>6832925</v>
+        <v>6832970</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845438</v>
+        <v>129845425</v>
       </c>
       <c r="B2" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406361</v>
+        <v>406832</v>
       </c>
       <c r="R2" t="n">
-        <v>6832815</v>
+        <v>6832816</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845441</v>
+        <v>129845419</v>
       </c>
       <c r="B3" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406638</v>
+        <v>406387</v>
       </c>
       <c r="R3" t="n">
-        <v>6832869</v>
+        <v>6832850</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845599</v>
+        <v>129845438</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406635</v>
+        <v>406361</v>
       </c>
       <c r="R4" t="n">
-        <v>6832779</v>
+        <v>6832815</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845598</v>
+        <v>129845441</v>
       </c>
       <c r="B5" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406626</v>
+        <v>406638</v>
       </c>
       <c r="R5" t="n">
-        <v>6832781</v>
+        <v>6832869</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,19 +1051,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845425</v>
+        <v>129845599</v>
       </c>
       <c r="B6" t="n">
         <v>79703</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406832</v>
+        <v>406635</v>
       </c>
       <c r="R6" t="n">
-        <v>6832816</v>
+        <v>6832779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,19 +1148,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845419</v>
+        <v>129845598</v>
       </c>
       <c r="B7" t="n">
         <v>79703</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406387</v>
+        <v>406626</v>
       </c>
       <c r="R7" t="n">
-        <v>6832850</v>
+        <v>6832781</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845443</v>
+        <v>129845661</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>78750</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,42 +1373,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406333</v>
+        <v>406352</v>
       </c>
       <c r="R9" t="n">
-        <v>6832733</v>
+        <v>6832709</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,22 +1447,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845661</v>
+        <v>129845443</v>
       </c>
       <c r="B10" t="n">
-        <v>78750</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,34 +1470,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406352</v>
+        <v>406333</v>
       </c>
       <c r="R10" t="n">
-        <v>6832709</v>
+        <v>6832733</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,12 +1552,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845604</v>
+        <v>129845655</v>
       </c>
       <c r="B13" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406424</v>
+        <v>406473</v>
       </c>
       <c r="R13" t="n">
-        <v>6832657</v>
+        <v>6832798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845467</v>
+        <v>129845610</v>
       </c>
       <c r="B14" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,37 +1866,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406359</v>
+        <v>406262</v>
       </c>
       <c r="R14" t="n">
-        <v>6832764</v>
+        <v>6832854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1937,73 +1934,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845462</v>
+        <v>129845614</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406713</v>
+        <v>406492</v>
       </c>
       <c r="R15" t="n">
-        <v>6832904</v>
+        <v>6832753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,29 +2031,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845655</v>
+        <v>129845618</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2060,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406473</v>
+        <v>406791</v>
       </c>
       <c r="R16" t="n">
-        <v>6832798</v>
+        <v>6832845</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,7 +2146,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845610</v>
+        <v>129845429</v>
       </c>
       <c r="B17" t="n">
         <v>79674</v>
@@ -2195,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406262</v>
+        <v>406472</v>
       </c>
       <c r="R17" t="n">
-        <v>6832854</v>
+        <v>6833103</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,19 +2231,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845614</v>
+        <v>129845613</v>
       </c>
       <c r="B18" t="n">
         <v>79674</v>
@@ -2292,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406492</v>
+        <v>406388</v>
       </c>
       <c r="R18" t="n">
-        <v>6832753</v>
+        <v>6832683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,7 +2340,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845618</v>
+        <v>129845617</v>
       </c>
       <c r="B19" t="n">
         <v>79674</v>
@@ -2389,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406791</v>
+        <v>406626</v>
       </c>
       <c r="R19" t="n">
-        <v>6832845</v>
+        <v>6832781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845429</v>
+        <v>129845604</v>
       </c>
       <c r="B20" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406472</v>
+        <v>406424</v>
       </c>
       <c r="R20" t="n">
-        <v>6833103</v>
+        <v>6832657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,22 +2522,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845613</v>
+        <v>129845467</v>
       </c>
       <c r="B21" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,34 +2545,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406388</v>
+        <v>406359</v>
       </c>
       <c r="R21" t="n">
-        <v>6832683</v>
+        <v>6832764</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2627,63 +2616,73 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845617</v>
+        <v>129845462</v>
       </c>
       <c r="B22" t="n">
-        <v>79674</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406626</v>
+        <v>406713</v>
       </c>
       <c r="R22" t="n">
-        <v>6832781</v>
+        <v>6832904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2724,25 +2723,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129845488</v>
+        <v>129845652</v>
       </c>
       <c r="B23" t="n">
         <v>79084</v>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406528</v>
+        <v>406408</v>
       </c>
       <c r="R23" t="n">
-        <v>6832873</v>
+        <v>6832778</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,19 +2827,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129845652</v>
+        <v>129845488</v>
       </c>
       <c r="B24" t="n">
         <v>79084</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406408</v>
+        <v>406528</v>
       </c>
       <c r="R24" t="n">
-        <v>6832778</v>
+        <v>6832873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,12 +2924,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3130,54 +3130,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845460</v>
+        <v>129845422</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406431</v>
+        <v>406513</v>
       </c>
       <c r="R27" t="n">
-        <v>6832825</v>
+        <v>6832869</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,7 +3209,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3237,7 +3227,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129845422</v>
+        <v>129845413</v>
       </c>
       <c r="B28" t="n">
         <v>79703</v>
@@ -3272,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406513</v>
+        <v>406266</v>
       </c>
       <c r="R28" t="n">
-        <v>6832869</v>
+        <v>6832827</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3334,45 +3324,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129845413</v>
+        <v>129845460</v>
       </c>
       <c r="B29" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406266</v>
+        <v>406431</v>
       </c>
       <c r="R29" t="n">
-        <v>6832827</v>
+        <v>6832825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3413,6 +3412,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845449</v>
+        <v>129845412</v>
       </c>
       <c r="B31" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3547,42 +3547,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406498</v>
+        <v>406426</v>
       </c>
       <c r="R31" t="n">
-        <v>6832913</v>
+        <v>6832990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3641,10 +3633,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845412</v>
+        <v>129845449</v>
       </c>
       <c r="B32" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3652,34 +3644,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406426</v>
+        <v>406498</v>
       </c>
       <c r="R32" t="n">
-        <v>6832990</v>
+        <v>6832913</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845657</v>
+        <v>129845483</v>
       </c>
       <c r="B36" t="n">
         <v>79084</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406495</v>
+        <v>406344</v>
       </c>
       <c r="R36" t="n">
-        <v>6832766</v>
+        <v>6832706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4124,12 +4124,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845483</v>
+        <v>129845657</v>
       </c>
       <c r="B38" t="n">
         <v>79084</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406344</v>
+        <v>406495</v>
       </c>
       <c r="R38" t="n">
-        <v>6832706</v>
+        <v>6832766</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,12 +4318,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845660</v>
+        <v>129845490</v>
       </c>
       <c r="B41" t="n">
         <v>79084</v>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406728</v>
+        <v>406560</v>
       </c>
       <c r="R41" t="n">
-        <v>6832848</v>
+        <v>6832885</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4613,19 +4613,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845491</v>
+        <v>129845660</v>
       </c>
       <c r="B42" t="n">
         <v>79084</v>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406588</v>
+        <v>406728</v>
       </c>
       <c r="R42" t="n">
-        <v>6832866</v>
+        <v>6832848</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,22 +4710,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845490</v>
+        <v>129845611</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4733,21 +4733,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406560</v>
+        <v>406276</v>
       </c>
       <c r="R43" t="n">
-        <v>6832885</v>
+        <v>6832761</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4807,22 +4807,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845601</v>
+        <v>129845431</v>
       </c>
       <c r="B44" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406583</v>
+        <v>406368</v>
       </c>
       <c r="R44" t="n">
-        <v>6832841</v>
+        <v>6833201</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,22 +4904,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845631</v>
+        <v>129845456</v>
       </c>
       <c r="B45" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,42 +4927,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406698</v>
+        <v>406442</v>
       </c>
       <c r="R45" t="n">
-        <v>6832875</v>
+        <v>6833041</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,22 +5001,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845611</v>
+        <v>129845631</v>
       </c>
       <c r="B46" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5032,34 +5024,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406276</v>
+        <v>406698</v>
       </c>
       <c r="R46" t="n">
-        <v>6832761</v>
+        <v>6832875</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5118,10 +5118,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845431</v>
+        <v>129845491</v>
       </c>
       <c r="B47" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5129,21 +5129,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406368</v>
+        <v>406588</v>
       </c>
       <c r="R47" t="n">
-        <v>6833201</v>
+        <v>6832866</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845456</v>
+        <v>129845601</v>
       </c>
       <c r="B48" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5226,21 +5226,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406442</v>
+        <v>406583</v>
       </c>
       <c r="R48" t="n">
-        <v>6833041</v>
+        <v>6832841</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5300,12 +5300,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5417,10 +5417,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845624</v>
+        <v>129845416</v>
       </c>
       <c r="B50" t="n">
-        <v>57895</v>
+        <v>79703</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5428,39 +5428,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406494</v>
+        <v>406362</v>
       </c>
       <c r="R50" t="n">
         <v>6832766</v>
@@ -5510,19 +5502,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845416</v>
+        <v>129845589</v>
       </c>
       <c r="B51" t="n">
         <v>79703</v>
@@ -5557,10 +5549,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406362</v>
+        <v>406406</v>
       </c>
       <c r="R51" t="n">
-        <v>6832766</v>
+        <v>6833199</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5607,22 +5599,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845589</v>
+        <v>129845624</v>
       </c>
       <c r="B52" t="n">
-        <v>79703</v>
+        <v>57895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5630,34 +5622,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406406</v>
+        <v>406494</v>
       </c>
       <c r="R52" t="n">
-        <v>6833199</v>
+        <v>6832766</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845435</v>
+        <v>129845466</v>
       </c>
       <c r="B56" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,21 +6028,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406455</v>
+        <v>406266</v>
       </c>
       <c r="R56" t="n">
-        <v>6833027</v>
+        <v>6832810</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845625</v>
+        <v>129845632</v>
       </c>
       <c r="B57" t="n">
-        <v>91623</v>
+        <v>57734</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6125,30 +6125,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6156,10 +6157,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406472</v>
+        <v>406667</v>
       </c>
       <c r="R57" t="n">
-        <v>6832767</v>
+        <v>6832849</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6200,7 +6201,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845487</v>
+        <v>129845633</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6230,34 +6230,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406409</v>
+        <v>406674</v>
       </c>
       <c r="R58" t="n">
-        <v>6832824</v>
+        <v>6832801</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,22 +6312,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845602</v>
+        <v>129845627</v>
       </c>
       <c r="B59" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6327,34 +6335,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406791</v>
+        <v>406539</v>
       </c>
       <c r="R59" t="n">
-        <v>6832844</v>
+        <v>6832767</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6413,10 +6429,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845466</v>
+        <v>129845625</v>
       </c>
       <c r="B60" t="n">
-        <v>78841</v>
+        <v>91623</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6424,34 +6440,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406266</v>
+        <v>406472</v>
       </c>
       <c r="R60" t="n">
-        <v>6832810</v>
+        <v>6832767</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6492,18 +6515,19 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6607,10 +6631,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845632</v>
+        <v>129845602</v>
       </c>
       <c r="B62" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6618,42 +6642,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406667</v>
+        <v>406791</v>
       </c>
       <c r="R62" t="n">
-        <v>6832849</v>
+        <v>6832844</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6712,10 +6728,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845633</v>
+        <v>129845435</v>
       </c>
       <c r="B63" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,42 +6739,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406674</v>
+        <v>406455</v>
       </c>
       <c r="R63" t="n">
-        <v>6832801</v>
+        <v>6833027</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6805,22 +6813,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845627</v>
+        <v>129845487</v>
       </c>
       <c r="B64" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,42 +6836,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406539</v>
+        <v>406409</v>
       </c>
       <c r="R64" t="n">
-        <v>6832767</v>
+        <v>6832824</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6910,12 +6910,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7134,54 +7134,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845642</v>
+        <v>129845434</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406547</v>
+        <v>406499</v>
       </c>
       <c r="R67" t="n">
-        <v>6832775</v>
+        <v>6833054</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7222,29 +7213,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845654</v>
+        <v>129845440</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7252,21 +7242,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7276,10 +7266,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406460</v>
+        <v>406445</v>
       </c>
       <c r="R68" t="n">
-        <v>6832823</v>
+        <v>6832921</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7326,22 +7316,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845493</v>
+        <v>129845605</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7349,21 +7339,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7373,10 +7363,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406785</v>
+        <v>406440</v>
       </c>
       <c r="R69" t="n">
-        <v>6832912</v>
+        <v>6833100</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7423,22 +7413,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845590</v>
+        <v>129845607</v>
       </c>
       <c r="B70" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7446,21 +7436,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7470,10 +7460,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406421</v>
+        <v>406407</v>
       </c>
       <c r="R70" t="n">
-        <v>6833142</v>
+        <v>6833199</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7532,10 +7522,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845593</v>
+        <v>129845654</v>
       </c>
       <c r="B71" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,21 +7533,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7567,10 +7557,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406451</v>
+        <v>406460</v>
       </c>
       <c r="R71" t="n">
-        <v>6832712</v>
+        <v>6832823</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7629,10 +7619,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845434</v>
+        <v>129845493</v>
       </c>
       <c r="B72" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,21 +7630,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7664,10 +7654,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406499</v>
+        <v>406785</v>
       </c>
       <c r="R72" t="n">
-        <v>6833054</v>
+        <v>6832912</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7726,10 +7716,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845440</v>
+        <v>129845590</v>
       </c>
       <c r="B73" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,21 +7727,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7761,10 +7751,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406445</v>
+        <v>406421</v>
       </c>
       <c r="R73" t="n">
-        <v>6832921</v>
+        <v>6833142</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7811,22 +7801,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845605</v>
+        <v>129845593</v>
       </c>
       <c r="B74" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,21 +7824,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7858,10 +7848,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406440</v>
+        <v>406451</v>
       </c>
       <c r="R74" t="n">
-        <v>6833100</v>
+        <v>6832712</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7920,45 +7910,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845607</v>
+        <v>129845642</v>
       </c>
       <c r="B75" t="n">
-        <v>79674</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406407</v>
+        <v>406547</v>
       </c>
       <c r="R75" t="n">
-        <v>6833199</v>
+        <v>6832775</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7999,6 +7998,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8017,10 +8017,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129845600</v>
+        <v>129845606</v>
       </c>
       <c r="B76" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,21 +8028,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406582</v>
+        <v>406394</v>
       </c>
       <c r="R76" t="n">
-        <v>6832826</v>
+        <v>6833197</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129845606</v>
+        <v>129845600</v>
       </c>
       <c r="B80" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406394</v>
+        <v>406582</v>
       </c>
       <c r="R80" t="n">
-        <v>6833197</v>
+        <v>6832826</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8502,37 +8502,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845444</v>
+        <v>129845465</v>
       </c>
       <c r="B81" t="n">
-        <v>91623</v>
+        <v>58108</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406601</v>
+        <v>406542</v>
       </c>
       <c r="R81" t="n">
-        <v>6832858</v>
+        <v>6832915</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8584,7 +8589,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8603,10 +8607,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845647</v>
+        <v>129845454</v>
       </c>
       <c r="B82" t="n">
-        <v>78841</v>
+        <v>57734</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8614,34 +8618,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406274</v>
+        <v>406675</v>
       </c>
       <c r="R82" t="n">
-        <v>6832759</v>
+        <v>6832988</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8688,22 +8700,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845454</v>
+        <v>129845621</v>
       </c>
       <c r="B83" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8711,16 +8723,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8733,7 +8745,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8743,10 +8755,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406675</v>
+        <v>406672</v>
       </c>
       <c r="R83" t="n">
-        <v>6832988</v>
+        <v>6832840</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8793,22 +8805,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845621</v>
+        <v>129845647</v>
       </c>
       <c r="B84" t="n">
-        <v>57737</v>
+        <v>78841</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8816,42 +8828,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406672</v>
+        <v>406274</v>
       </c>
       <c r="R84" t="n">
-        <v>6832840</v>
+        <v>6832759</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8910,42 +8914,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845465</v>
+        <v>129845444</v>
       </c>
       <c r="B85" t="n">
-        <v>58108</v>
+        <v>91623</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -8953,10 +8952,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406542</v>
+        <v>406601</v>
       </c>
       <c r="R85" t="n">
-        <v>6832915</v>
+        <v>6832858</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8997,6 +8996,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845653</v>
+        <v>129845423</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9026,21 +9026,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406430</v>
+        <v>406531</v>
       </c>
       <c r="R86" t="n">
-        <v>6832777</v>
+        <v>6832868</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,57 +9100,66 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845656</v>
+        <v>129845641</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406480</v>
+        <v>406618</v>
       </c>
       <c r="R87" t="n">
-        <v>6832777</v>
+        <v>6832813</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9191,6 +9200,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9209,43 +9219,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845641</v>
+        <v>129845437</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9253,10 +9257,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406618</v>
+        <v>406331</v>
       </c>
       <c r="R88" t="n">
-        <v>6832813</v>
+        <v>6832676</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9304,22 +9308,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845423</v>
+        <v>129845656</v>
       </c>
       <c r="B89" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9327,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9351,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406531</v>
+        <v>406480</v>
       </c>
       <c r="R89" t="n">
-        <v>6832868</v>
+        <v>6832777</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9401,22 +9405,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845437</v>
+        <v>129845653</v>
       </c>
       <c r="B90" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9424,37 +9428,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406331</v>
+        <v>406430</v>
       </c>
       <c r="R90" t="n">
-        <v>6832676</v>
+        <v>6832777</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9495,29 +9496,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845479</v>
+        <v>129845457</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,21 +9525,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406408</v>
+        <v>406265</v>
       </c>
       <c r="R91" t="n">
-        <v>6832975</v>
+        <v>6832808</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9611,10 +9611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845480</v>
+        <v>129845608</v>
       </c>
       <c r="B92" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9622,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406277</v>
+        <v>406399</v>
       </c>
       <c r="R92" t="n">
-        <v>6832823</v>
+        <v>6833177</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9696,22 +9696,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845594</v>
+        <v>129845634</v>
       </c>
       <c r="B93" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,34 +9719,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406506</v>
+        <v>406781</v>
       </c>
       <c r="R93" t="n">
-        <v>6832725</v>
+        <v>6832843</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845418</v>
+        <v>129845479</v>
       </c>
       <c r="B94" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9840,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406377</v>
+        <v>406408</v>
       </c>
       <c r="R94" t="n">
-        <v>6832837</v>
+        <v>6832975</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845408</v>
+        <v>129845480</v>
       </c>
       <c r="B95" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406368</v>
+        <v>406277</v>
       </c>
       <c r="R95" t="n">
-        <v>6833202</v>
+        <v>6832823</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,27 +10007,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845634</v>
+        <v>129845464</v>
       </c>
       <c r="B96" t="n">
-        <v>57734</v>
+        <v>58108</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10032,7 +10040,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10042,10 +10050,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406781</v>
+        <v>406416</v>
       </c>
       <c r="R96" t="n">
-        <v>6832843</v>
+        <v>6832880</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10092,65 +10100,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845464</v>
+        <v>129845594</v>
       </c>
       <c r="B97" t="n">
-        <v>58108</v>
+        <v>79703</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406416</v>
+        <v>406506</v>
       </c>
       <c r="R97" t="n">
-        <v>6832880</v>
+        <v>6832725</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10197,22 +10197,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845457</v>
+        <v>129845418</v>
       </c>
       <c r="B98" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10220,21 +10220,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406265</v>
+        <v>406377</v>
       </c>
       <c r="R98" t="n">
-        <v>6832808</v>
+        <v>6832837</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845608</v>
+        <v>129845408</v>
       </c>
       <c r="B99" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406399</v>
+        <v>406368</v>
       </c>
       <c r="R99" t="n">
-        <v>6833177</v>
+        <v>6833202</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10391,22 +10391,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B100" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,21 +10414,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R100" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10488,22 +10488,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845629</v>
+        <v>129845646</v>
       </c>
       <c r="B101" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10511,42 +10511,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406618</v>
+        <v>406290</v>
       </c>
       <c r="R101" t="n">
-        <v>6832773</v>
+        <v>6832901</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10605,10 +10597,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845615</v>
+        <v>129845426</v>
       </c>
       <c r="B102" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10616,21 +10608,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10640,10 +10632,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406583</v>
+        <v>406796</v>
       </c>
       <c r="R102" t="n">
-        <v>6832911</v>
+        <v>6832917</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10690,22 +10682,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845646</v>
+        <v>129845407</v>
       </c>
       <c r="B103" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10713,21 +10705,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10737,10 +10729,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406290</v>
+        <v>406416</v>
       </c>
       <c r="R103" t="n">
-        <v>6832901</v>
+        <v>6833166</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10787,22 +10779,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845426</v>
+        <v>129845629</v>
       </c>
       <c r="B104" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,34 +10802,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406796</v>
+        <v>406618</v>
       </c>
       <c r="R104" t="n">
-        <v>6832917</v>
+        <v>6832773</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,22 +10884,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845439</v>
+        <v>129845597</v>
       </c>
       <c r="B105" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406377</v>
+        <v>406615</v>
       </c>
       <c r="R105" t="n">
-        <v>6832840</v>
+        <v>6832770</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10981,22 +10981,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845485</v>
+        <v>129845595</v>
       </c>
       <c r="B106" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406320</v>
+        <v>406455</v>
       </c>
       <c r="R106" t="n">
-        <v>6832742</v>
+        <v>6832823</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11078,22 +11078,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845595</v>
+        <v>129845450</v>
       </c>
       <c r="B107" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,34 +11101,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406455</v>
+        <v>406508</v>
       </c>
       <c r="R107" t="n">
-        <v>6832823</v>
+        <v>6832877</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11175,22 +11183,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845597</v>
+        <v>129845448</v>
       </c>
       <c r="B108" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11198,34 +11206,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406615</v>
+        <v>406396</v>
       </c>
       <c r="R108" t="n">
-        <v>6832770</v>
+        <v>6832853</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11272,22 +11288,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845450</v>
+        <v>129845485</v>
       </c>
       <c r="B109" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11295,42 +11311,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406508</v>
+        <v>406320</v>
       </c>
       <c r="R109" t="n">
-        <v>6832877</v>
+        <v>6832742</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11389,10 +11397,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845448</v>
+        <v>129845439</v>
       </c>
       <c r="B110" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11400,42 +11408,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406396</v>
+        <v>406377</v>
       </c>
       <c r="R110" t="n">
-        <v>6832853</v>
+        <v>6832840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11494,53 +11494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845644</v>
+        <v>129845421</v>
       </c>
       <c r="B111" t="n">
-        <v>58108</v>
+        <v>79703</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406457</v>
+        <v>406500</v>
       </c>
       <c r="R111" t="n">
-        <v>6832809</v>
+        <v>6832933</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11587,12 +11579,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11793,45 +11785,53 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845421</v>
+        <v>129845644</v>
       </c>
       <c r="B114" t="n">
-        <v>79703</v>
+        <v>58108</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406500</v>
+        <v>406457</v>
       </c>
       <c r="R114" t="n">
-        <v>6832933</v>
+        <v>6832809</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11878,12 +11878,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -11997,10 +11997,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845596</v>
+        <v>129845628</v>
       </c>
       <c r="B116" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,34 +12008,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406536</v>
+        <v>406541</v>
       </c>
       <c r="R116" t="n">
-        <v>6832770</v>
+        <v>6832823</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12094,7 +12102,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845628</v>
+        <v>129845635</v>
       </c>
       <c r="B117" t="n">
         <v>57734</v>
@@ -12127,7 +12135,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12137,10 +12145,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406541</v>
+        <v>406677</v>
       </c>
       <c r="R117" t="n">
-        <v>6832823</v>
+        <v>6832986</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12199,10 +12207,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845635</v>
+        <v>129845458</v>
       </c>
       <c r="B118" t="n">
-        <v>57734</v>
+        <v>78842</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12210,42 +12218,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406677</v>
+        <v>406531</v>
       </c>
       <c r="R118" t="n">
-        <v>6832986</v>
+        <v>6832927</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12292,22 +12292,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845458</v>
+        <v>129845436</v>
       </c>
       <c r="B119" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12315,21 +12315,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406531</v>
+        <v>406315</v>
       </c>
       <c r="R119" t="n">
-        <v>6832927</v>
+        <v>6832667</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12401,10 +12401,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845436</v>
+        <v>129845596</v>
       </c>
       <c r="B120" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406315</v>
+        <v>406536</v>
       </c>
       <c r="R120" t="n">
-        <v>6832667</v>
+        <v>6832770</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,19 +12486,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845495</v>
+        <v>129845494</v>
       </c>
       <c r="B121" t="n">
         <v>79084</v>
@@ -12533,10 +12533,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406668</v>
+        <v>406710</v>
       </c>
       <c r="R121" t="n">
-        <v>6833007</v>
+        <v>6832990</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12696,7 +12696,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845494</v>
+        <v>129845495</v>
       </c>
       <c r="B123" t="n">
         <v>79084</v>
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406710</v>
+        <v>406668</v>
       </c>
       <c r="R123" t="n">
-        <v>6832990</v>
+        <v>6833007</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12793,10 +12793,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845591</v>
+        <v>129845451</v>
       </c>
       <c r="B124" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12804,34 +12804,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406439</v>
+        <v>406595</v>
       </c>
       <c r="R124" t="n">
-        <v>6833139</v>
+        <v>6832931</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12878,22 +12886,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845588</v>
+        <v>129845432</v>
       </c>
       <c r="B125" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12901,21 +12909,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12925,10 +12933,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406440</v>
+        <v>406373</v>
       </c>
       <c r="R125" t="n">
-        <v>6833101</v>
+        <v>6833176</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12975,22 +12983,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845451</v>
+        <v>129845588</v>
       </c>
       <c r="B126" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12998,42 +13006,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406595</v>
+        <v>406440</v>
       </c>
       <c r="R126" t="n">
-        <v>6832931</v>
+        <v>6833101</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13080,22 +13080,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845432</v>
+        <v>129845591</v>
       </c>
       <c r="B127" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406373</v>
+        <v>406439</v>
       </c>
       <c r="R127" t="n">
-        <v>6833176</v>
+        <v>6833139</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13177,22 +13177,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845482</v>
+        <v>129845453</v>
       </c>
       <c r="B128" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13200,34 +13200,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406282</v>
+        <v>406716</v>
       </c>
       <c r="R128" t="n">
-        <v>6832624</v>
+        <v>6832970</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13286,45 +13294,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845489</v>
+        <v>129845623</v>
       </c>
       <c r="B129" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406542</v>
+        <v>406310</v>
       </c>
       <c r="R129" t="n">
-        <v>6832915</v>
+        <v>6832901</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13371,12 +13387,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -13480,53 +13496,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845623</v>
+        <v>129845482</v>
       </c>
       <c r="B131" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406310</v>
+        <v>406282</v>
       </c>
       <c r="R131" t="n">
-        <v>6832901</v>
+        <v>6832624</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13573,22 +13581,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845603</v>
+        <v>129845489</v>
       </c>
       <c r="B132" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13596,21 +13604,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13620,10 +13628,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406764</v>
+        <v>406542</v>
       </c>
       <c r="R132" t="n">
-        <v>6832925</v>
+        <v>6832915</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13670,12 +13678,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -13876,7 +13884,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845424</v>
+        <v>129845603</v>
       </c>
       <c r="B135" t="n">
         <v>79703</v>
@@ -13911,10 +13919,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406533</v>
+        <v>406764</v>
       </c>
       <c r="R135" t="n">
-        <v>6832861</v>
+        <v>6832925</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13961,22 +13969,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845453</v>
+        <v>129845424</v>
       </c>
       <c r="B136" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13984,42 +13992,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406716</v>
+        <v>406533</v>
       </c>
       <c r="R136" t="n">
-        <v>6832970</v>
+        <v>6832861</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845425</v>
+        <v>129845438</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406832</v>
+        <v>406361</v>
       </c>
       <c r="R2" t="n">
-        <v>6832816</v>
+        <v>6832815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845419</v>
+        <v>129845441</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406387</v>
+        <v>406638</v>
       </c>
       <c r="R3" t="n">
-        <v>6832850</v>
+        <v>6832869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845438</v>
+        <v>129845599</v>
       </c>
       <c r="B4" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406361</v>
+        <v>406635</v>
       </c>
       <c r="R4" t="n">
-        <v>6832815</v>
+        <v>6832779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845441</v>
+        <v>129845598</v>
       </c>
       <c r="B5" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406638</v>
+        <v>406626</v>
       </c>
       <c r="R5" t="n">
-        <v>6832869</v>
+        <v>6832781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845599</v>
+        <v>129845425</v>
       </c>
       <c r="B6" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406635</v>
+        <v>406832</v>
       </c>
       <c r="R6" t="n">
-        <v>6832779</v>
+        <v>6832816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845598</v>
+        <v>129845419</v>
       </c>
       <c r="B7" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406626</v>
+        <v>406387</v>
       </c>
       <c r="R7" t="n">
-        <v>6832781</v>
+        <v>6832850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
         <v>129845630</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129845661</v>
       </c>
       <c r="B9" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845443</v>
+        <v>129845427</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406333</v>
+        <v>406794</v>
       </c>
       <c r="R10" t="n">
-        <v>6832733</v>
+        <v>6832934</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845427</v>
+        <v>129845417</v>
       </c>
       <c r="B11" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406794</v>
+        <v>406346</v>
       </c>
       <c r="R11" t="n">
-        <v>6832934</v>
+        <v>6832798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845417</v>
+        <v>129845443</v>
       </c>
       <c r="B12" t="n">
-        <v>79703</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,34 +1664,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406346</v>
+        <v>406333</v>
       </c>
       <c r="R12" t="n">
-        <v>6832798</v>
+        <v>6832733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,7 +1761,7 @@
         <v>129845655</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845610</v>
+        <v>129845604</v>
       </c>
       <c r="B14" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406262</v>
+        <v>406424</v>
       </c>
       <c r="R14" t="n">
-        <v>6832854</v>
+        <v>6832657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845614</v>
+        <v>129845467</v>
       </c>
       <c r="B15" t="n">
-        <v>79674</v>
+        <v>78844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,34 +1963,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406492</v>
+        <v>406359</v>
       </c>
       <c r="R15" t="n">
-        <v>6832753</v>
+        <v>6832764</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,63 +2034,73 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845618</v>
+        <v>129845462</v>
       </c>
       <c r="B16" t="n">
-        <v>79674</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406791</v>
+        <v>406713</v>
       </c>
       <c r="R16" t="n">
-        <v>6832845</v>
+        <v>6832904</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2128,28 +2141,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845429</v>
+        <v>129845610</v>
       </c>
       <c r="B17" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2181,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406472</v>
+        <v>406262</v>
       </c>
       <c r="R17" t="n">
-        <v>6833103</v>
+        <v>6832854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,22 +2245,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845613</v>
+        <v>129845614</v>
       </c>
       <c r="B18" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2278,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406388</v>
+        <v>406492</v>
       </c>
       <c r="R18" t="n">
-        <v>6832683</v>
+        <v>6832753</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845617</v>
+        <v>129845618</v>
       </c>
       <c r="B19" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406626</v>
+        <v>406791</v>
       </c>
       <c r="R19" t="n">
-        <v>6832781</v>
+        <v>6832845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845604</v>
+        <v>129845429</v>
       </c>
       <c r="B20" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406424</v>
+        <v>406472</v>
       </c>
       <c r="R20" t="n">
-        <v>6832657</v>
+        <v>6833103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2522,22 +2536,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845467</v>
+        <v>129845613</v>
       </c>
       <c r="B21" t="n">
-        <v>78841</v>
+        <v>79677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2545,37 +2559,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406359</v>
+        <v>406388</v>
       </c>
       <c r="R21" t="n">
-        <v>6832764</v>
+        <v>6832683</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,73 +2627,63 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845462</v>
+        <v>129845617</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79677</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406713</v>
+        <v>406626</v>
       </c>
       <c r="R22" t="n">
-        <v>6832904</v>
+        <v>6832781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,29 +2724,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129845652</v>
+        <v>129845488</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406408</v>
+        <v>406528</v>
       </c>
       <c r="R23" t="n">
-        <v>6832778</v>
+        <v>6832873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,22 +2827,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129845488</v>
+        <v>129845652</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406528</v>
+        <v>406408</v>
       </c>
       <c r="R24" t="n">
-        <v>6832873</v>
+        <v>6832778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,12 +2924,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -2939,7 +2939,7 @@
         <v>129845659</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845619</v>
+        <v>129845422</v>
       </c>
       <c r="B26" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406776</v>
+        <v>406513</v>
       </c>
       <c r="R26" t="n">
-        <v>6832860</v>
+        <v>6832869</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3118,22 +3118,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845422</v>
+        <v>129845413</v>
       </c>
       <c r="B27" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406513</v>
+        <v>406266</v>
       </c>
       <c r="R27" t="n">
-        <v>6832869</v>
+        <v>6832827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,45 +3227,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129845413</v>
+        <v>129845460</v>
       </c>
       <c r="B28" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406266</v>
+        <v>406431</v>
       </c>
       <c r="R28" t="n">
-        <v>6832827</v>
+        <v>6832825</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3306,6 +3315,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3324,54 +3334,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129845460</v>
+        <v>129845619</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79677</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406431</v>
+        <v>406776</v>
       </c>
       <c r="R29" t="n">
-        <v>6832825</v>
+        <v>6832860</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,29 +3413,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845636</v>
+        <v>129845639</v>
       </c>
       <c r="B30" t="n">
-        <v>57734</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,42 +3442,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406595</v>
+        <v>406276</v>
       </c>
       <c r="R30" t="n">
-        <v>6833001</v>
+        <v>6832761</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3539,7 +3531,7 @@
         <v>129845412</v>
       </c>
       <c r="B31" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,10 +3625,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845449</v>
+        <v>129845636</v>
       </c>
       <c r="B32" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,7 +3658,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3676,10 +3668,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406498</v>
+        <v>406595</v>
       </c>
       <c r="R32" t="n">
-        <v>6832913</v>
+        <v>6833001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,53 +3718,52 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845463</v>
+        <v>129845449</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3782,10 +3773,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406746</v>
+        <v>406498</v>
       </c>
       <c r="R33" t="n">
-        <v>6832985</v>
+        <v>6832913</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3826,7 +3817,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3845,45 +3835,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845639</v>
+        <v>129845463</v>
       </c>
       <c r="B34" t="n">
-        <v>78842</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406276</v>
+        <v>406746</v>
       </c>
       <c r="R34" t="n">
-        <v>6832761</v>
+        <v>6832985</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3924,28 +3923,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845455</v>
+        <v>129845657</v>
       </c>
       <c r="B35" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406486</v>
+        <v>406495</v>
       </c>
       <c r="R35" t="n">
-        <v>6833057</v>
+        <v>6832766</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,22 +4027,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845483</v>
+        <v>129845481</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406344</v>
+        <v>406278</v>
       </c>
       <c r="R36" t="n">
-        <v>6832706</v>
+        <v>6832795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4136,10 +4136,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845481</v>
+        <v>129845483</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406278</v>
+        <v>406344</v>
       </c>
       <c r="R37" t="n">
-        <v>6832795</v>
+        <v>6832706</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845657</v>
+        <v>129845592</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406495</v>
+        <v>406370</v>
       </c>
       <c r="R38" t="n">
-        <v>6832766</v>
+        <v>6832711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129845592</v>
+        <v>129845455</v>
       </c>
       <c r="B39" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4341,21 +4341,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406370</v>
+        <v>406486</v>
       </c>
       <c r="R39" t="n">
-        <v>6832711</v>
+        <v>6833057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4415,12 +4415,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
         <v>129845492</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845490</v>
+        <v>129845491</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406560</v>
+        <v>406588</v>
       </c>
       <c r="R41" t="n">
-        <v>6832885</v>
+        <v>6832866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4625,10 +4625,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845660</v>
+        <v>129845601</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4636,21 +4636,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406728</v>
+        <v>406583</v>
       </c>
       <c r="R42" t="n">
-        <v>6832848</v>
+        <v>6832841</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,10 +4722,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845611</v>
+        <v>129845660</v>
       </c>
       <c r="B43" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4733,21 +4733,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406276</v>
+        <v>406728</v>
       </c>
       <c r="R43" t="n">
-        <v>6832761</v>
+        <v>6832848</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845431</v>
+        <v>129845490</v>
       </c>
       <c r="B44" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406368</v>
+        <v>406560</v>
       </c>
       <c r="R44" t="n">
-        <v>6833201</v>
+        <v>6832885</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845456</v>
+        <v>129845631</v>
       </c>
       <c r="B45" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,34 +4927,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406442</v>
+        <v>406698</v>
       </c>
       <c r="R45" t="n">
-        <v>6833041</v>
+        <v>6832875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,22 +5009,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845631</v>
+        <v>129845611</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>79677</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5024,42 +5032,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406698</v>
+        <v>406276</v>
       </c>
       <c r="R46" t="n">
-        <v>6832875</v>
+        <v>6832761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5118,10 +5118,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845491</v>
+        <v>129845431</v>
       </c>
       <c r="B47" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5129,21 +5129,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406588</v>
+        <v>406368</v>
       </c>
       <c r="R47" t="n">
-        <v>6832866</v>
+        <v>6833201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845601</v>
+        <v>129845456</v>
       </c>
       <c r="B48" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5226,21 +5226,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406583</v>
+        <v>406442</v>
       </c>
       <c r="R48" t="n">
-        <v>6832841</v>
+        <v>6833041</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5300,22 +5300,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845626</v>
+        <v>129845612</v>
       </c>
       <c r="B49" t="n">
-        <v>91623</v>
+        <v>79677</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5323,41 +5323,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406533</v>
+        <v>406379</v>
       </c>
       <c r="R49" t="n">
-        <v>6832761</v>
+        <v>6832756</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5398,7 +5391,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5420,7 +5412,7 @@
         <v>129845416</v>
       </c>
       <c r="B50" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5517,7 +5509,7 @@
         <v>129845589</v>
       </c>
       <c r="B51" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5614,7 +5606,7 @@
         <v>129845624</v>
       </c>
       <c r="B52" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5719,7 +5711,7 @@
         <v>129845461</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5826,7 +5818,7 @@
         <v>129845638</v>
       </c>
       <c r="B54" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5920,10 +5912,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845612</v>
+        <v>129845626</v>
       </c>
       <c r="B55" t="n">
-        <v>79674</v>
+        <v>91626</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5931,34 +5923,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406379</v>
+        <v>406533</v>
       </c>
       <c r="R55" t="n">
-        <v>6832756</v>
+        <v>6832761</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5999,6 +5998,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845466</v>
+        <v>129845625</v>
       </c>
       <c r="B56" t="n">
-        <v>78841</v>
+        <v>91626</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,34 +6028,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406266</v>
+        <v>406472</v>
       </c>
       <c r="R56" t="n">
-        <v>6832810</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,28 +6103,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845632</v>
+        <v>129845466</v>
       </c>
       <c r="B57" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6125,42 +6133,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406667</v>
+        <v>406266</v>
       </c>
       <c r="R57" t="n">
-        <v>6832849</v>
+        <v>6832810</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6207,22 +6207,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845633</v>
+        <v>129845435</v>
       </c>
       <c r="B58" t="n">
-        <v>57734</v>
+        <v>79677</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6230,42 +6230,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406674</v>
+        <v>406455</v>
       </c>
       <c r="R58" t="n">
-        <v>6832801</v>
+        <v>6833027</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6312,22 +6304,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845627</v>
+        <v>129845487</v>
       </c>
       <c r="B59" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6335,42 +6327,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406539</v>
+        <v>406409</v>
       </c>
       <c r="R59" t="n">
-        <v>6832767</v>
+        <v>6832824</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6417,22 +6401,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845625</v>
+        <v>129845410</v>
       </c>
       <c r="B60" t="n">
-        <v>91623</v>
+        <v>79706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6440,41 +6424,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406472</v>
+        <v>406487</v>
       </c>
       <c r="R60" t="n">
-        <v>6832767</v>
+        <v>6833064</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6515,29 +6492,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845410</v>
+        <v>129845602</v>
       </c>
       <c r="B61" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6569,10 +6545,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406487</v>
+        <v>406791</v>
       </c>
       <c r="R61" t="n">
-        <v>6833064</v>
+        <v>6832844</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6619,22 +6595,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845602</v>
+        <v>129845632</v>
       </c>
       <c r="B62" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6642,34 +6618,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406791</v>
+        <v>406667</v>
       </c>
       <c r="R62" t="n">
-        <v>6832844</v>
+        <v>6832849</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6728,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845435</v>
+        <v>129845633</v>
       </c>
       <c r="B63" t="n">
-        <v>79674</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6739,34 +6723,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406455</v>
+        <v>406674</v>
       </c>
       <c r="R63" t="n">
-        <v>6833027</v>
+        <v>6832801</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6813,22 +6805,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845487</v>
+        <v>129845627</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6836,34 +6828,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406409</v>
+        <v>406539</v>
       </c>
       <c r="R64" t="n">
-        <v>6832824</v>
+        <v>6832767</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6910,12 +6910,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -6925,7 +6925,7 @@
         <v>129845459</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845452</v>
+        <v>129845654</v>
       </c>
       <c r="B66" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,42 +7040,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406630</v>
+        <v>406460</v>
       </c>
       <c r="R66" t="n">
-        <v>6832941</v>
+        <v>6832823</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7122,22 +7114,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845434</v>
+        <v>129845493</v>
       </c>
       <c r="B67" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7145,21 +7137,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7169,10 +7161,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406499</v>
+        <v>406785</v>
       </c>
       <c r="R67" t="n">
-        <v>6833054</v>
+        <v>6832912</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7231,10 +7223,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845440</v>
+        <v>129845590</v>
       </c>
       <c r="B68" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7242,21 +7234,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7266,10 +7258,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406445</v>
+        <v>406421</v>
       </c>
       <c r="R68" t="n">
-        <v>6832921</v>
+        <v>6833142</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7316,22 +7308,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845605</v>
+        <v>129845593</v>
       </c>
       <c r="B69" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7339,21 +7331,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7363,10 +7355,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406440</v>
+        <v>406451</v>
       </c>
       <c r="R69" t="n">
-        <v>6833100</v>
+        <v>6832712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7425,10 +7417,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845607</v>
+        <v>129845452</v>
       </c>
       <c r="B70" t="n">
-        <v>79674</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,34 +7428,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406407</v>
+        <v>406630</v>
       </c>
       <c r="R70" t="n">
-        <v>6833199</v>
+        <v>6832941</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7510,57 +7510,66 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845654</v>
+        <v>129845642</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406460</v>
+        <v>406547</v>
       </c>
       <c r="R71" t="n">
-        <v>6832823</v>
+        <v>6832775</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7601,6 +7610,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7619,10 +7629,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845493</v>
+        <v>129845434</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7630,21 +7640,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7654,10 +7664,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406785</v>
+        <v>406499</v>
       </c>
       <c r="R72" t="n">
-        <v>6832912</v>
+        <v>6833054</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7716,10 +7726,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845590</v>
+        <v>129845440</v>
       </c>
       <c r="B73" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7727,21 +7737,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7751,10 +7761,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406421</v>
+        <v>406445</v>
       </c>
       <c r="R73" t="n">
-        <v>6833142</v>
+        <v>6832921</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7801,22 +7811,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845593</v>
+        <v>129845605</v>
       </c>
       <c r="B74" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7824,21 +7834,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7848,10 +7858,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406451</v>
+        <v>406440</v>
       </c>
       <c r="R74" t="n">
-        <v>6832712</v>
+        <v>6833100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7910,54 +7920,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845642</v>
+        <v>129845607</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79677</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406547</v>
+        <v>406407</v>
       </c>
       <c r="R75" t="n">
-        <v>6832775</v>
+        <v>6833199</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,7 +7999,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>129845606</v>
       </c>
       <c r="B76" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>129845486</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>129845420</v>
       </c>
       <c r="B78" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>129845415</v>
       </c>
       <c r="B79" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>129845600</v>
       </c>
       <c r="B80" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8502,27 +8502,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845465</v>
+        <v>129845454</v>
       </c>
       <c r="B81" t="n">
-        <v>58108</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8535,7 +8535,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406542</v>
+        <v>406675</v>
       </c>
       <c r="R81" t="n">
-        <v>6832915</v>
+        <v>6832988</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8607,27 +8607,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845454</v>
+        <v>129845465</v>
       </c>
       <c r="B82" t="n">
-        <v>57734</v>
+        <v>58111</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8640,7 +8640,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406675</v>
+        <v>406542</v>
       </c>
       <c r="R82" t="n">
-        <v>6832988</v>
+        <v>6832915</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8712,10 +8712,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845621</v>
+        <v>129845444</v>
       </c>
       <c r="B83" t="n">
-        <v>57737</v>
+        <v>91626</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8723,31 +8723,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8755,10 +8750,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406672</v>
+        <v>406601</v>
       </c>
       <c r="R83" t="n">
-        <v>6832840</v>
+        <v>6832858</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8799,28 +8794,29 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845647</v>
+        <v>129845621</v>
       </c>
       <c r="B84" t="n">
-        <v>78841</v>
+        <v>57740</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8828,34 +8824,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406274</v>
+        <v>406672</v>
       </c>
       <c r="R84" t="n">
-        <v>6832759</v>
+        <v>6832840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8914,10 +8918,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845444</v>
+        <v>129845647</v>
       </c>
       <c r="B85" t="n">
-        <v>91623</v>
+        <v>78844</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8925,37 +8929,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406601</v>
+        <v>406274</v>
       </c>
       <c r="R85" t="n">
-        <v>6832858</v>
+        <v>6832759</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8996,29 +8997,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845423</v>
+        <v>129845653</v>
       </c>
       <c r="B86" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9026,21 +9026,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406531</v>
+        <v>406430</v>
       </c>
       <c r="R86" t="n">
-        <v>6832868</v>
+        <v>6832777</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,66 +9100,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845641</v>
+        <v>129845656</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406618</v>
+        <v>406480</v>
       </c>
       <c r="R87" t="n">
-        <v>6832813</v>
+        <v>6832777</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9200,7 +9191,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9219,10 +9209,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845437</v>
+        <v>129845423</v>
       </c>
       <c r="B88" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9230,37 +9220,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406331</v>
+        <v>406531</v>
       </c>
       <c r="R88" t="n">
-        <v>6832676</v>
+        <v>6832868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9301,7 +9288,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9320,45 +9306,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845656</v>
+        <v>129845641</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406480</v>
+        <v>406618</v>
       </c>
       <c r="R89" t="n">
-        <v>6832777</v>
+        <v>6832813</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9399,6 +9394,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9417,10 +9413,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845653</v>
+        <v>129845437</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9428,34 +9424,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406430</v>
+        <v>406331</v>
       </c>
       <c r="R90" t="n">
-        <v>6832777</v>
+        <v>6832676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9496,28 +9495,29 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845457</v>
+        <v>129845479</v>
       </c>
       <c r="B91" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,21 +9525,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406265</v>
+        <v>406408</v>
       </c>
       <c r="R91" t="n">
-        <v>6832808</v>
+        <v>6832975</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9611,10 +9611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845608</v>
+        <v>129845480</v>
       </c>
       <c r="B92" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9622,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406399</v>
+        <v>406277</v>
       </c>
       <c r="R92" t="n">
-        <v>6833177</v>
+        <v>6832823</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9696,22 +9696,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845634</v>
+        <v>129845594</v>
       </c>
       <c r="B93" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,42 +9719,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406781</v>
+        <v>406506</v>
       </c>
       <c r="R93" t="n">
-        <v>6832843</v>
+        <v>6832725</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845479</v>
+        <v>129845408</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406408</v>
+        <v>406368</v>
       </c>
       <c r="R94" t="n">
-        <v>6832975</v>
+        <v>6833202</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845480</v>
+        <v>129845457</v>
       </c>
       <c r="B95" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406277</v>
+        <v>406265</v>
       </c>
       <c r="R95" t="n">
-        <v>6832823</v>
+        <v>6832808</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,53 +9999,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845464</v>
+        <v>129845418</v>
       </c>
       <c r="B96" t="n">
-        <v>58108</v>
+        <v>79706</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406416</v>
+        <v>406377</v>
       </c>
       <c r="R96" t="n">
-        <v>6832880</v>
+        <v>6832837</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10112,10 +10096,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845594</v>
+        <v>129845634</v>
       </c>
       <c r="B97" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10123,34 +10107,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406506</v>
+        <v>406781</v>
       </c>
       <c r="R97" t="n">
-        <v>6832725</v>
+        <v>6832843</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10209,45 +10201,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845418</v>
+        <v>129845464</v>
       </c>
       <c r="B98" t="n">
-        <v>79703</v>
+        <v>58111</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406377</v>
+        <v>406416</v>
       </c>
       <c r="R98" t="n">
-        <v>6832837</v>
+        <v>6832880</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845408</v>
+        <v>129845608</v>
       </c>
       <c r="B99" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406368</v>
+        <v>406399</v>
       </c>
       <c r="R99" t="n">
-        <v>6833202</v>
+        <v>6833177</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10391,22 +10391,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845615</v>
+        <v>129845426</v>
       </c>
       <c r="B100" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,21 +10414,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406583</v>
+        <v>406796</v>
       </c>
       <c r="R100" t="n">
-        <v>6832911</v>
+        <v>6832917</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10488,22 +10488,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845646</v>
+        <v>129845407</v>
       </c>
       <c r="B101" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10511,21 +10511,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406290</v>
+        <v>406416</v>
       </c>
       <c r="R101" t="n">
-        <v>6832901</v>
+        <v>6833166</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10585,22 +10585,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845426</v>
+        <v>129845646</v>
       </c>
       <c r="B102" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,21 +10608,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10632,10 +10632,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406796</v>
+        <v>406290</v>
       </c>
       <c r="R102" t="n">
-        <v>6832917</v>
+        <v>6832901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10682,22 +10682,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B103" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,21 +10705,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R103" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10779,12 +10779,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -10794,7 +10794,7 @@
         <v>129845629</v>
       </c>
       <c r="B104" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845597</v>
+        <v>129845485</v>
       </c>
       <c r="B105" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406615</v>
+        <v>406320</v>
       </c>
       <c r="R105" t="n">
-        <v>6832770</v>
+        <v>6832742</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10981,22 +10981,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845595</v>
+        <v>129845439</v>
       </c>
       <c r="B106" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406455</v>
+        <v>406377</v>
       </c>
       <c r="R106" t="n">
-        <v>6832823</v>
+        <v>6832840</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11078,22 +11078,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845450</v>
+        <v>129845595</v>
       </c>
       <c r="B107" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,42 +11101,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406508</v>
+        <v>406455</v>
       </c>
       <c r="R107" t="n">
-        <v>6832877</v>
+        <v>6832823</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11183,22 +11175,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845448</v>
+        <v>129845450</v>
       </c>
       <c r="B108" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11238,10 +11230,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406396</v>
+        <v>406508</v>
       </c>
       <c r="R108" t="n">
-        <v>6832853</v>
+        <v>6832877</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11300,10 +11292,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845485</v>
+        <v>129845448</v>
       </c>
       <c r="B109" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11311,34 +11303,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406320</v>
+        <v>406396</v>
       </c>
       <c r="R109" t="n">
-        <v>6832742</v>
+        <v>6832853</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11397,10 +11397,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845439</v>
+        <v>129845597</v>
       </c>
       <c r="B110" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11408,21 +11408,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406377</v>
+        <v>406615</v>
       </c>
       <c r="R110" t="n">
-        <v>6832840</v>
+        <v>6832770</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11482,57 +11482,65 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845421</v>
+        <v>129845644</v>
       </c>
       <c r="B111" t="n">
-        <v>79703</v>
+        <v>58111</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406500</v>
+        <v>406457</v>
       </c>
       <c r="R111" t="n">
-        <v>6832933</v>
+        <v>6832809</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11579,57 +11587,66 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845433</v>
+        <v>129845640</v>
       </c>
       <c r="B112" t="n">
-        <v>79674</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406438</v>
+        <v>406404</v>
       </c>
       <c r="R112" t="n">
-        <v>6833114</v>
+        <v>6832729</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11670,28 +11687,29 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845430</v>
+        <v>129845421</v>
       </c>
       <c r="B113" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11699,21 +11717,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11723,10 +11741,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406465</v>
+        <v>406500</v>
       </c>
       <c r="R113" t="n">
-        <v>6833093</v>
+        <v>6832933</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11785,53 +11803,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845644</v>
+        <v>129845433</v>
       </c>
       <c r="B114" t="n">
-        <v>58108</v>
+        <v>79677</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406457</v>
+        <v>406438</v>
       </c>
       <c r="R114" t="n">
-        <v>6832809</v>
+        <v>6833114</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11878,66 +11888,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845640</v>
+        <v>129845430</v>
       </c>
       <c r="B115" t="n">
-        <v>8450</v>
+        <v>79677</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406404</v>
+        <v>406465</v>
       </c>
       <c r="R115" t="n">
-        <v>6832729</v>
+        <v>6833093</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11978,29 +11979,28 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845628</v>
+        <v>129845596</v>
       </c>
       <c r="B116" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,42 +12008,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406541</v>
+        <v>406536</v>
       </c>
       <c r="R116" t="n">
-        <v>6832823</v>
+        <v>6832770</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12102,10 +12094,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845635</v>
+        <v>129845628</v>
       </c>
       <c r="B117" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12135,7 +12127,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12145,10 +12137,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406677</v>
+        <v>406541</v>
       </c>
       <c r="R117" t="n">
-        <v>6832986</v>
+        <v>6832823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12207,10 +12199,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845458</v>
+        <v>129845635</v>
       </c>
       <c r="B118" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12218,34 +12210,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406531</v>
+        <v>406677</v>
       </c>
       <c r="R118" t="n">
-        <v>6832927</v>
+        <v>6832986</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12292,12 +12292,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12307,7 +12307,7 @@
         <v>129845436</v>
       </c>
       <c r="B119" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12401,10 +12401,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845596</v>
+        <v>129845458</v>
       </c>
       <c r="B120" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406536</v>
+        <v>406531</v>
       </c>
       <c r="R120" t="n">
-        <v>6832770</v>
+        <v>6832927</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,22 +12486,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845494</v>
+        <v>129845495</v>
       </c>
       <c r="B121" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12533,10 +12533,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406710</v>
+        <v>406668</v>
       </c>
       <c r="R121" t="n">
-        <v>6832990</v>
+        <v>6833007</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12598,7 +12598,7 @@
         <v>129845484</v>
       </c>
       <c r="B122" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12696,10 +12696,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845495</v>
+        <v>129845494</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406668</v>
+        <v>406710</v>
       </c>
       <c r="R123" t="n">
-        <v>6833007</v>
+        <v>6832990</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12793,10 +12793,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845451</v>
+        <v>129845588</v>
       </c>
       <c r="B124" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12804,42 +12804,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406595</v>
+        <v>406440</v>
       </c>
       <c r="R124" t="n">
-        <v>6832931</v>
+        <v>6833101</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12886,22 +12878,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845432</v>
+        <v>129845591</v>
       </c>
       <c r="B125" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12909,21 +12901,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12933,10 +12925,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406373</v>
+        <v>406439</v>
       </c>
       <c r="R125" t="n">
-        <v>6833176</v>
+        <v>6833139</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12983,22 +12975,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845588</v>
+        <v>129845451</v>
       </c>
       <c r="B126" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13006,34 +12998,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406440</v>
+        <v>406595</v>
       </c>
       <c r="R126" t="n">
-        <v>6833101</v>
+        <v>6832931</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13080,22 +13080,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845591</v>
+        <v>129845432</v>
       </c>
       <c r="B127" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406439</v>
+        <v>406373</v>
       </c>
       <c r="R127" t="n">
-        <v>6833139</v>
+        <v>6833176</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13177,22 +13177,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845453</v>
+        <v>129845414</v>
       </c>
       <c r="B128" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13200,42 +13200,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406716</v>
+        <v>406313</v>
       </c>
       <c r="R128" t="n">
-        <v>6832970</v>
+        <v>6832656</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13294,53 +13286,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845623</v>
+        <v>129845411</v>
       </c>
       <c r="B129" t="n">
-        <v>56927</v>
+        <v>79706</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406310</v>
+        <v>406442</v>
       </c>
       <c r="R129" t="n">
-        <v>6832901</v>
+        <v>6833040</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13387,22 +13371,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129845658</v>
+        <v>129845603</v>
       </c>
       <c r="B130" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13410,21 +13394,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13434,10 +13418,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406563</v>
+        <v>406764</v>
       </c>
       <c r="R130" t="n">
-        <v>6832887</v>
+        <v>6832925</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13496,10 +13480,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845482</v>
+        <v>129845424</v>
       </c>
       <c r="B131" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13507,21 +13491,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13531,10 +13515,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406282</v>
+        <v>406533</v>
       </c>
       <c r="R131" t="n">
-        <v>6832624</v>
+        <v>6832861</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13593,45 +13577,53 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845489</v>
+        <v>129845623</v>
       </c>
       <c r="B132" t="n">
-        <v>79084</v>
+        <v>56930</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406542</v>
+        <v>406310</v>
       </c>
       <c r="R132" t="n">
-        <v>6832915</v>
+        <v>6832901</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13678,22 +13670,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845414</v>
+        <v>129845453</v>
       </c>
       <c r="B133" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13701,34 +13693,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406313</v>
+        <v>406716</v>
       </c>
       <c r="R133" t="n">
-        <v>6832656</v>
+        <v>6832970</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13787,10 +13787,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845411</v>
+        <v>129845482</v>
       </c>
       <c r="B134" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13798,21 +13798,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13822,10 +13822,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406442</v>
+        <v>406282</v>
       </c>
       <c r="R134" t="n">
-        <v>6833040</v>
+        <v>6832624</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13884,10 +13884,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845603</v>
+        <v>129845489</v>
       </c>
       <c r="B135" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13895,21 +13895,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13919,10 +13919,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406764</v>
+        <v>406542</v>
       </c>
       <c r="R135" t="n">
-        <v>6832925</v>
+        <v>6832915</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13969,22 +13969,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845424</v>
+        <v>129845658</v>
       </c>
       <c r="B136" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13992,21 +13992,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14016,10 +14016,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406533</v>
+        <v>406563</v>
       </c>
       <c r="R136" t="n">
-        <v>6832861</v>
+        <v>6832887</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14081,7 +14081,7 @@
         <v>129845446</v>
       </c>
       <c r="B137" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>129845478</v>
       </c>
       <c r="B138" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>129845497</v>
       </c>
       <c r="B139" t="n">
-        <v>92025</v>
+        <v>92028</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -1855,45 +1855,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845604</v>
+        <v>129845462</v>
       </c>
       <c r="B14" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406424</v>
+        <v>406713</v>
       </c>
       <c r="R14" t="n">
-        <v>6832657</v>
+        <v>6832904</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,28 +1943,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845467</v>
+        <v>129845604</v>
       </c>
       <c r="B15" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,37 +1973,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406359</v>
+        <v>406424</v>
       </c>
       <c r="R15" t="n">
-        <v>6832764</v>
+        <v>6832657</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2034,62 +2041,55 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845462</v>
+        <v>129845467</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>78844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406713</v>
+        <v>406359</v>
       </c>
       <c r="R16" t="n">
-        <v>6832904</v>
+        <v>6832764</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845639</v>
+        <v>129845412</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406276</v>
+        <v>406426</v>
       </c>
       <c r="R30" t="n">
-        <v>6832761</v>
+        <v>6832990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3516,22 +3516,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845412</v>
+        <v>129845636</v>
       </c>
       <c r="B31" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,34 +3539,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406426</v>
+        <v>406595</v>
       </c>
       <c r="R31" t="n">
-        <v>6832990</v>
+        <v>6833001</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3613,19 +3621,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845636</v>
+        <v>129845449</v>
       </c>
       <c r="B32" t="n">
         <v>57737</v>
@@ -3658,7 +3666,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3668,10 +3676,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406595</v>
+        <v>406498</v>
       </c>
       <c r="R32" t="n">
-        <v>6833001</v>
+        <v>6832913</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3718,22 +3726,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845449</v>
+        <v>129845639</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3741,42 +3749,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406498</v>
+        <v>406276</v>
       </c>
       <c r="R33" t="n">
-        <v>6832913</v>
+        <v>6832761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3823,12 +3823,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845491</v>
+        <v>129845660</v>
       </c>
       <c r="B41" t="n">
         <v>79087</v>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406588</v>
+        <v>406728</v>
       </c>
       <c r="R41" t="n">
-        <v>6832866</v>
+        <v>6832848</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4613,22 +4613,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845601</v>
+        <v>129845491</v>
       </c>
       <c r="B42" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4636,21 +4636,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406583</v>
+        <v>406588</v>
       </c>
       <c r="R42" t="n">
-        <v>6832841</v>
+        <v>6832866</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,19 +4710,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845660</v>
+        <v>129845490</v>
       </c>
       <c r="B43" t="n">
         <v>79087</v>
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406728</v>
+        <v>406560</v>
       </c>
       <c r="R43" t="n">
-        <v>6832848</v>
+        <v>6832885</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4807,22 +4807,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845490</v>
+        <v>129845601</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406560</v>
+        <v>406583</v>
       </c>
       <c r="R44" t="n">
-        <v>6832885</v>
+        <v>6832841</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,12 +4904,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845625</v>
+        <v>129845435</v>
       </c>
       <c r="B56" t="n">
-        <v>91626</v>
+        <v>79677</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,41 +6028,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406472</v>
+        <v>406455</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6833027</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6103,64 +6096,72 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845466</v>
+        <v>129845459</v>
       </c>
       <c r="B57" t="n">
-        <v>78844</v>
+        <v>8451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406266</v>
+        <v>406331</v>
       </c>
       <c r="R57" t="n">
-        <v>6832810</v>
+        <v>6832715</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6201,6 +6202,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,10 +6221,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845435</v>
+        <v>129845466</v>
       </c>
       <c r="B58" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6230,21 +6232,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6254,10 +6256,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406455</v>
+        <v>406266</v>
       </c>
       <c r="R58" t="n">
-        <v>6833027</v>
+        <v>6832810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6316,10 +6318,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845487</v>
+        <v>129845625</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6327,34 +6329,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406409</v>
+        <v>406472</v>
       </c>
       <c r="R59" t="n">
-        <v>6832824</v>
+        <v>6832767</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6395,28 +6404,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845410</v>
+        <v>129845487</v>
       </c>
       <c r="B60" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6424,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6448,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406487</v>
+        <v>406409</v>
       </c>
       <c r="R60" t="n">
-        <v>6833064</v>
+        <v>6832824</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6510,7 +6520,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845602</v>
+        <v>129845410</v>
       </c>
       <c r="B61" t="n">
         <v>79706</v>
@@ -6545,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406791</v>
+        <v>406487</v>
       </c>
       <c r="R61" t="n">
-        <v>6832844</v>
+        <v>6833064</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6595,22 +6605,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845632</v>
+        <v>129845602</v>
       </c>
       <c r="B62" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6618,42 +6628,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406667</v>
+        <v>406791</v>
       </c>
       <c r="R62" t="n">
-        <v>6832849</v>
+        <v>6832844</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6712,7 +6714,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845633</v>
+        <v>129845632</v>
       </c>
       <c r="B63" t="n">
         <v>57737</v>
@@ -6755,10 +6757,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406674</v>
+        <v>406667</v>
       </c>
       <c r="R63" t="n">
-        <v>6832801</v>
+        <v>6832849</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6817,7 +6819,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845627</v>
+        <v>129845633</v>
       </c>
       <c r="B64" t="n">
         <v>57737</v>
@@ -6850,7 +6852,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6860,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406539</v>
+        <v>406674</v>
       </c>
       <c r="R64" t="n">
-        <v>6832767</v>
+        <v>6832801</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6922,41 +6924,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845459</v>
+        <v>129845627</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -6966,10 +6967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406331</v>
+        <v>406539</v>
       </c>
       <c r="R65" t="n">
-        <v>6832715</v>
+        <v>6832767</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7010,19 +7011,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845454</v>
+        <v>129845444</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>91626</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,31 +8513,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406675</v>
+        <v>406601</v>
       </c>
       <c r="R81" t="n">
-        <v>6832988</v>
+        <v>6832858</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8589,6 +8584,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8607,27 +8603,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845465</v>
+        <v>129845621</v>
       </c>
       <c r="B82" t="n">
-        <v>58111</v>
+        <v>57740</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8640,7 +8636,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8650,10 +8646,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406542</v>
+        <v>406672</v>
       </c>
       <c r="R82" t="n">
-        <v>6832915</v>
+        <v>6832840</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8700,22 +8696,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845444</v>
+        <v>129845647</v>
       </c>
       <c r="B83" t="n">
-        <v>91626</v>
+        <v>78844</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8723,37 +8719,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406601</v>
+        <v>406274</v>
       </c>
       <c r="R83" t="n">
-        <v>6832858</v>
+        <v>6832759</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8794,29 +8787,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845621</v>
+        <v>129845454</v>
       </c>
       <c r="B84" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8824,16 +8816,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8846,7 +8838,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -8856,10 +8848,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406672</v>
+        <v>406675</v>
       </c>
       <c r="R84" t="n">
-        <v>6832840</v>
+        <v>6832988</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8906,57 +8898,65 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129845647</v>
+        <v>129845465</v>
       </c>
       <c r="B85" t="n">
-        <v>78844</v>
+        <v>58111</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406274</v>
+        <v>406542</v>
       </c>
       <c r="R85" t="n">
-        <v>6832759</v>
+        <v>6832915</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9003,12 +9003,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9209,45 +9209,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845423</v>
+        <v>129845641</v>
       </c>
       <c r="B88" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406531</v>
+        <v>406618</v>
       </c>
       <c r="R88" t="n">
-        <v>6832868</v>
+        <v>6832813</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9288,61 +9297,56 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845641</v>
+        <v>129845437</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>79677</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9350,10 +9354,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406618</v>
+        <v>406331</v>
       </c>
       <c r="R89" t="n">
-        <v>6832813</v>
+        <v>6832676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9401,22 +9405,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845437</v>
+        <v>129845423</v>
       </c>
       <c r="B90" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9424,37 +9428,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406331</v>
+        <v>406531</v>
       </c>
       <c r="R90" t="n">
-        <v>6832676</v>
+        <v>6832868</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9495,7 +9496,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845594</v>
+        <v>129845608</v>
       </c>
       <c r="B93" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406506</v>
+        <v>406399</v>
       </c>
       <c r="R93" t="n">
-        <v>6832725</v>
+        <v>6833177</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,7 +9805,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845408</v>
+        <v>129845594</v>
       </c>
       <c r="B94" t="n">
         <v>79706</v>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406368</v>
+        <v>406506</v>
       </c>
       <c r="R94" t="n">
-        <v>6833202</v>
+        <v>6832725</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9890,22 +9890,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845457</v>
+        <v>129845418</v>
       </c>
       <c r="B95" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406265</v>
+        <v>406377</v>
       </c>
       <c r="R95" t="n">
-        <v>6832808</v>
+        <v>6832837</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,7 +9999,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845418</v>
+        <v>129845408</v>
       </c>
       <c r="B96" t="n">
         <v>79706</v>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406377</v>
+        <v>406368</v>
       </c>
       <c r="R96" t="n">
-        <v>6832837</v>
+        <v>6833202</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845608</v>
+        <v>129845457</v>
       </c>
       <c r="B99" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406399</v>
+        <v>406265</v>
       </c>
       <c r="R99" t="n">
-        <v>6833177</v>
+        <v>6832808</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10391,12 +10391,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845439</v>
+        <v>129845595</v>
       </c>
       <c r="B106" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406377</v>
+        <v>406455</v>
       </c>
       <c r="R106" t="n">
-        <v>6832840</v>
+        <v>6832823</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11078,22 +11078,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845595</v>
+        <v>129845450</v>
       </c>
       <c r="B107" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,34 +11101,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406455</v>
+        <v>406508</v>
       </c>
       <c r="R107" t="n">
-        <v>6832823</v>
+        <v>6832877</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11175,19 +11183,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845450</v>
+        <v>129845448</v>
       </c>
       <c r="B108" t="n">
         <v>57737</v>
@@ -11230,10 +11238,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406508</v>
+        <v>406396</v>
       </c>
       <c r="R108" t="n">
-        <v>6832877</v>
+        <v>6832853</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11292,10 +11300,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845448</v>
+        <v>129845439</v>
       </c>
       <c r="B109" t="n">
-        <v>57737</v>
+        <v>79677</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11303,42 +11311,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406396</v>
+        <v>406377</v>
       </c>
       <c r="R109" t="n">
-        <v>6832853</v>
+        <v>6832840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -4528,7 +4528,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845660</v>
+        <v>129845491</v>
       </c>
       <c r="B41" t="n">
         <v>79087</v>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406728</v>
+        <v>406588</v>
       </c>
       <c r="R41" t="n">
-        <v>6832848</v>
+        <v>6832866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4613,22 +4613,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845491</v>
+        <v>129845601</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4636,21 +4636,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406588</v>
+        <v>406583</v>
       </c>
       <c r="R42" t="n">
-        <v>6832866</v>
+        <v>6832841</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,19 +4710,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845490</v>
+        <v>129845660</v>
       </c>
       <c r="B43" t="n">
         <v>79087</v>
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406560</v>
+        <v>406728</v>
       </c>
       <c r="R43" t="n">
-        <v>6832885</v>
+        <v>6832848</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4807,22 +4807,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845601</v>
+        <v>129845490</v>
       </c>
       <c r="B44" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4830,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406583</v>
+        <v>406560</v>
       </c>
       <c r="R44" t="n">
-        <v>6832841</v>
+        <v>6832885</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,12 +4904,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845654</v>
+        <v>129845452</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,34 +7040,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406460</v>
+        <v>406630</v>
       </c>
       <c r="R66" t="n">
-        <v>6832823</v>
+        <v>6832941</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7114,57 +7122,66 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845493</v>
+        <v>129845642</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406785</v>
+        <v>406547</v>
       </c>
       <c r="R67" t="n">
-        <v>6832912</v>
+        <v>6832775</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7205,28 +7222,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845590</v>
+        <v>129845434</v>
       </c>
       <c r="B68" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7234,21 +7252,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7258,10 +7276,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406421</v>
+        <v>406499</v>
       </c>
       <c r="R68" t="n">
-        <v>6833142</v>
+        <v>6833054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7308,22 +7326,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845593</v>
+        <v>129845440</v>
       </c>
       <c r="B69" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7331,21 +7349,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7355,10 +7373,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406451</v>
+        <v>406445</v>
       </c>
       <c r="R69" t="n">
-        <v>6832712</v>
+        <v>6832921</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7405,22 +7423,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845452</v>
+        <v>129845605</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>79677</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7428,42 +7446,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406630</v>
+        <v>406440</v>
       </c>
       <c r="R70" t="n">
-        <v>6832941</v>
+        <v>6833100</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7510,66 +7520,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845642</v>
+        <v>129845607</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>79677</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406547</v>
+        <v>406407</v>
       </c>
       <c r="R71" t="n">
-        <v>6832775</v>
+        <v>6833199</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7610,7 +7611,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7629,10 +7629,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845434</v>
+        <v>129845654</v>
       </c>
       <c r="B72" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,21 +7640,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406499</v>
+        <v>406460</v>
       </c>
       <c r="R72" t="n">
-        <v>6833054</v>
+        <v>6832823</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7714,22 +7714,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845440</v>
+        <v>129845493</v>
       </c>
       <c r="B73" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,21 +7737,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406445</v>
+        <v>406785</v>
       </c>
       <c r="R73" t="n">
-        <v>6832921</v>
+        <v>6832912</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7823,10 +7823,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845605</v>
+        <v>129845590</v>
       </c>
       <c r="B74" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,21 +7834,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406440</v>
+        <v>406421</v>
       </c>
       <c r="R74" t="n">
-        <v>6833100</v>
+        <v>6833142</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7920,10 +7920,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845607</v>
+        <v>129845593</v>
       </c>
       <c r="B75" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,21 +7931,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406407</v>
+        <v>406451</v>
       </c>
       <c r="R75" t="n">
-        <v>6833199</v>
+        <v>6832712</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845486</v>
+        <v>129845420</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406350</v>
+        <v>406424</v>
       </c>
       <c r="R77" t="n">
-        <v>6832772</v>
+        <v>6832865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8211,7 +8211,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845420</v>
+        <v>129845415</v>
       </c>
       <c r="B78" t="n">
         <v>79706</v>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406424</v>
+        <v>406317</v>
       </c>
       <c r="R78" t="n">
-        <v>6832865</v>
+        <v>6832733</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8308,7 +8308,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845415</v>
+        <v>129845600</v>
       </c>
       <c r="B79" t="n">
         <v>79706</v>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406317</v>
+        <v>406582</v>
       </c>
       <c r="R79" t="n">
-        <v>6832733</v>
+        <v>6832826</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8393,22 +8393,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129845600</v>
+        <v>129845486</v>
       </c>
       <c r="B80" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406582</v>
+        <v>406350</v>
       </c>
       <c r="R80" t="n">
-        <v>6832826</v>
+        <v>6832772</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8490,12 +8490,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845608</v>
+        <v>129845594</v>
       </c>
       <c r="B93" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406399</v>
+        <v>406506</v>
       </c>
       <c r="R93" t="n">
-        <v>6833177</v>
+        <v>6832725</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,7 +9805,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845594</v>
+        <v>129845408</v>
       </c>
       <c r="B94" t="n">
         <v>79706</v>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406506</v>
+        <v>406368</v>
       </c>
       <c r="R94" t="n">
-        <v>6832725</v>
+        <v>6833202</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9890,22 +9890,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845418</v>
+        <v>129845457</v>
       </c>
       <c r="B95" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406377</v>
+        <v>406265</v>
       </c>
       <c r="R95" t="n">
-        <v>6832837</v>
+        <v>6832808</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,7 +9999,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845408</v>
+        <v>129845418</v>
       </c>
       <c r="B96" t="n">
         <v>79706</v>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406368</v>
+        <v>406377</v>
       </c>
       <c r="R96" t="n">
-        <v>6833202</v>
+        <v>6832837</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845457</v>
+        <v>129845608</v>
       </c>
       <c r="B99" t="n">
-        <v>78845</v>
+        <v>79677</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406265</v>
+        <v>406399</v>
       </c>
       <c r="R99" t="n">
-        <v>6832808</v>
+        <v>6833177</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10391,12 +10391,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10896,10 +10896,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845485</v>
+        <v>129845439</v>
       </c>
       <c r="B105" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406320</v>
+        <v>406377</v>
       </c>
       <c r="R105" t="n">
-        <v>6832742</v>
+        <v>6832840</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10993,10 +10993,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845595</v>
+        <v>129845485</v>
       </c>
       <c r="B106" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406455</v>
+        <v>406320</v>
       </c>
       <c r="R106" t="n">
-        <v>6832823</v>
+        <v>6832742</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11078,12 +11078,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11300,10 +11300,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845439</v>
+        <v>129845597</v>
       </c>
       <c r="B109" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11311,21 +11311,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11335,10 +11335,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406377</v>
+        <v>406615</v>
       </c>
       <c r="R109" t="n">
-        <v>6832840</v>
+        <v>6832770</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11385,19 +11385,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845597</v>
+        <v>129845595</v>
       </c>
       <c r="B110" t="n">
         <v>79706</v>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406615</v>
+        <v>406455</v>
       </c>
       <c r="R110" t="n">
-        <v>6832770</v>
+        <v>6832823</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11494,53 +11494,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129845644</v>
+        <v>129845421</v>
       </c>
       <c r="B111" t="n">
-        <v>58111</v>
+        <v>79706</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406457</v>
+        <v>406500</v>
       </c>
       <c r="R111" t="n">
-        <v>6832809</v>
+        <v>6832933</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11587,22 +11579,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845640</v>
+        <v>129845644</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>58111</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11610,30 +11602,29 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11643,10 +11634,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406404</v>
+        <v>406457</v>
       </c>
       <c r="R112" t="n">
-        <v>6832729</v>
+        <v>6832809</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11687,7 +11678,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11706,10 +11696,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845421</v>
+        <v>129845433</v>
       </c>
       <c r="B113" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11717,21 +11707,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11741,10 +11731,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406500</v>
+        <v>406438</v>
       </c>
       <c r="R113" t="n">
-        <v>6832933</v>
+        <v>6833114</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11803,7 +11793,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845433</v>
+        <v>129845430</v>
       </c>
       <c r="B114" t="n">
         <v>79677</v>
@@ -11838,10 +11828,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406438</v>
+        <v>406465</v>
       </c>
       <c r="R114" t="n">
-        <v>6833114</v>
+        <v>6833093</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11900,45 +11890,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845430</v>
+        <v>129845640</v>
       </c>
       <c r="B115" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406465</v>
+        <v>406404</v>
       </c>
       <c r="R115" t="n">
-        <v>6833093</v>
+        <v>6832729</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11979,18 +11978,19 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845438</v>
+        <v>129845419</v>
       </c>
       <c r="B2" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406361</v>
+        <v>406387</v>
       </c>
       <c r="R2" t="n">
-        <v>6832815</v>
+        <v>6832850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845441</v>
+        <v>129845599</v>
       </c>
       <c r="B3" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406638</v>
+        <v>406635</v>
       </c>
       <c r="R3" t="n">
-        <v>6832869</v>
+        <v>6832779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845599</v>
+        <v>129845598</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406635</v>
+        <v>406626</v>
       </c>
       <c r="R4" t="n">
-        <v>6832779</v>
+        <v>6832781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845598</v>
+        <v>129845425</v>
       </c>
       <c r="B5" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406626</v>
+        <v>406832</v>
       </c>
       <c r="R5" t="n">
-        <v>6832781</v>
+        <v>6832816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845425</v>
+        <v>129845438</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406832</v>
+        <v>406361</v>
       </c>
       <c r="R6" t="n">
-        <v>6832816</v>
+        <v>6832815</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845419</v>
+        <v>129845441</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406387</v>
+        <v>406638</v>
       </c>
       <c r="R7" t="n">
-        <v>6832850</v>
+        <v>6832869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845630</v>
+        <v>129845661</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>78754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406631</v>
+        <v>406352</v>
       </c>
       <c r="R8" t="n">
-        <v>6832822</v>
+        <v>6832709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845661</v>
+        <v>129845427</v>
       </c>
       <c r="B9" t="n">
-        <v>78753</v>
+        <v>79707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406352</v>
+        <v>406794</v>
       </c>
       <c r="R9" t="n">
-        <v>6832709</v>
+        <v>6832934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845427</v>
+        <v>129845417</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406794</v>
+        <v>406346</v>
       </c>
       <c r="R10" t="n">
-        <v>6832934</v>
+        <v>6832798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845417</v>
+        <v>129845630</v>
       </c>
       <c r="B11" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,34 +1559,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406346</v>
+        <v>406631</v>
       </c>
       <c r="R11" t="n">
-        <v>6832798</v>
+        <v>6832822</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,12 +1641,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1758,45 +1758,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845655</v>
+        <v>129845462</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406473</v>
+        <v>406713</v>
       </c>
       <c r="R13" t="n">
-        <v>6832798</v>
+        <v>6832904</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,72 +1846,64 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845462</v>
+        <v>129845610</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406713</v>
+        <v>406262</v>
       </c>
       <c r="R14" t="n">
-        <v>6832904</v>
+        <v>6832854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1943,29 +1944,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845604</v>
+        <v>129845618</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406424</v>
+        <v>406791</v>
       </c>
       <c r="R15" t="n">
-        <v>6832657</v>
+        <v>6832845</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845467</v>
+        <v>129845429</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>79678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2070,37 +2070,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406359</v>
+        <v>406472</v>
       </c>
       <c r="R16" t="n">
-        <v>6832764</v>
+        <v>6833103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,7 +2138,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2160,10 +2156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845610</v>
+        <v>129845614</v>
       </c>
       <c r="B17" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,10 +2191,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406262</v>
+        <v>406492</v>
       </c>
       <c r="R17" t="n">
-        <v>6832854</v>
+        <v>6832753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,10 +2253,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845614</v>
+        <v>129845613</v>
       </c>
       <c r="B18" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,10 +2288,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406492</v>
+        <v>406388</v>
       </c>
       <c r="R18" t="n">
-        <v>6832753</v>
+        <v>6832683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,10 +2350,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845618</v>
+        <v>129845617</v>
       </c>
       <c r="B19" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2389,10 +2385,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406791</v>
+        <v>406626</v>
       </c>
       <c r="R19" t="n">
-        <v>6832845</v>
+        <v>6832781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2447,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845429</v>
+        <v>129845655</v>
       </c>
       <c r="B20" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2458,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406472</v>
+        <v>406473</v>
       </c>
       <c r="R20" t="n">
-        <v>6833103</v>
+        <v>6832798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,22 +2532,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845613</v>
+        <v>129845604</v>
       </c>
       <c r="B21" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2555,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406388</v>
+        <v>406424</v>
       </c>
       <c r="R21" t="n">
-        <v>6832683</v>
+        <v>6832657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2641,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845617</v>
+        <v>129845467</v>
       </c>
       <c r="B22" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2652,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406626</v>
+        <v>406359</v>
       </c>
       <c r="R22" t="n">
-        <v>6832781</v>
+        <v>6832764</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2724,18 +2723,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
         <v>129845488</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>129845652</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>129845659</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845422</v>
+        <v>129845413</v>
       </c>
       <c r="B26" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406513</v>
+        <v>406266</v>
       </c>
       <c r="R26" t="n">
-        <v>6832869</v>
+        <v>6832827</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845413</v>
+        <v>129845422</v>
       </c>
       <c r="B27" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406266</v>
+        <v>406513</v>
       </c>
       <c r="R27" t="n">
-        <v>6832827</v>
+        <v>6832869</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
         <v>129845619</v>
       </c>
       <c r="B29" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>129845412</v>
       </c>
       <c r="B30" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,40 +3528,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845636</v>
+        <v>129845463</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3571,10 +3572,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406595</v>
+        <v>406746</v>
       </c>
       <c r="R31" t="n">
-        <v>6833001</v>
+        <v>6832985</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,28 +3616,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845449</v>
+        <v>129845639</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3644,42 +3646,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406498</v>
+        <v>406276</v>
       </c>
       <c r="R32" t="n">
-        <v>6832913</v>
+        <v>6832761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,22 +3720,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845639</v>
+        <v>129845636</v>
       </c>
       <c r="B33" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3749,34 +3743,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406276</v>
+        <v>406595</v>
       </c>
       <c r="R33" t="n">
-        <v>6832761</v>
+        <v>6833001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3835,41 +3837,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845463</v>
+        <v>129845449</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3879,10 +3880,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406746</v>
+        <v>406498</v>
       </c>
       <c r="R34" t="n">
-        <v>6832985</v>
+        <v>6832913</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3923,7 +3924,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3942,10 +3942,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845657</v>
+        <v>129845481</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406495</v>
+        <v>406278</v>
       </c>
       <c r="R35" t="n">
-        <v>6832766</v>
+        <v>6832795</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,22 +4027,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845481</v>
+        <v>129845483</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406278</v>
+        <v>406344</v>
       </c>
       <c r="R36" t="n">
-        <v>6832795</v>
+        <v>6832706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4136,10 +4136,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845483</v>
+        <v>129845657</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406344</v>
+        <v>406495</v>
       </c>
       <c r="R37" t="n">
-        <v>6832706</v>
+        <v>6832766</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,12 +4221,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4236,7 +4236,7 @@
         <v>129845592</v>
       </c>
       <c r="B38" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>129845455</v>
       </c>
       <c r="B39" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>129845492</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845491</v>
+        <v>129845660</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406588</v>
+        <v>406728</v>
       </c>
       <c r="R41" t="n">
-        <v>6832866</v>
+        <v>6832848</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4613,12 +4613,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4628,7 +4628,7 @@
         <v>129845601</v>
       </c>
       <c r="B42" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4722,10 +4722,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845660</v>
+        <v>129845631</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4733,34 +4733,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406728</v>
+        <v>406698</v>
       </c>
       <c r="R43" t="n">
-        <v>6832848</v>
+        <v>6832875</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,10 +4827,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845490</v>
+        <v>129845456</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,21 +4838,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4854,10 +4862,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406560</v>
+        <v>406442</v>
       </c>
       <c r="R44" t="n">
-        <v>6832885</v>
+        <v>6833041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,10 +4924,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845631</v>
+        <v>129845490</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,42 +4935,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406698</v>
+        <v>406560</v>
       </c>
       <c r="R45" t="n">
-        <v>6832875</v>
+        <v>6832885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,22 +5009,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845611</v>
+        <v>129845491</v>
       </c>
       <c r="B46" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406276</v>
+        <v>406588</v>
       </c>
       <c r="R46" t="n">
-        <v>6832761</v>
+        <v>6832866</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5106,22 +5106,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845431</v>
+        <v>129845611</v>
       </c>
       <c r="B47" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406368</v>
+        <v>406276</v>
       </c>
       <c r="R47" t="n">
-        <v>6833201</v>
+        <v>6832761</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5203,22 +5203,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845456</v>
+        <v>129845431</v>
       </c>
       <c r="B48" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5226,21 +5226,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406442</v>
+        <v>406368</v>
       </c>
       <c r="R48" t="n">
-        <v>6833041</v>
+        <v>6833201</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5312,10 +5312,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845612</v>
+        <v>129845626</v>
       </c>
       <c r="B49" t="n">
-        <v>79677</v>
+        <v>91627</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5323,34 +5323,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406379</v>
+        <v>406533</v>
       </c>
       <c r="R49" t="n">
-        <v>6832756</v>
+        <v>6832761</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5391,6 +5398,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5409,10 +5417,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845416</v>
+        <v>129845638</v>
       </c>
       <c r="B50" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5420,21 +5428,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5444,10 +5452,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406362</v>
+        <v>406290</v>
       </c>
       <c r="R50" t="n">
-        <v>6832766</v>
+        <v>6832900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5494,22 +5502,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845589</v>
+        <v>129845416</v>
       </c>
       <c r="B51" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5541,10 +5549,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406406</v>
+        <v>406362</v>
       </c>
       <c r="R51" t="n">
-        <v>6833199</v>
+        <v>6832766</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5591,22 +5599,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845624</v>
+        <v>129845589</v>
       </c>
       <c r="B52" t="n">
-        <v>57898</v>
+        <v>79707</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5614,42 +5622,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406494</v>
+        <v>406406</v>
       </c>
       <c r="R52" t="n">
-        <v>6832766</v>
+        <v>6833199</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5708,41 +5708,40 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845461</v>
+        <v>129845624</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>57898</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5752,10 +5751,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406589</v>
+        <v>406494</v>
       </c>
       <c r="R53" t="n">
-        <v>6832990</v>
+        <v>6832766</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5796,64 +5795,72 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845638</v>
+        <v>129845461</v>
       </c>
       <c r="B54" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406290</v>
+        <v>406589</v>
       </c>
       <c r="R54" t="n">
-        <v>6832900</v>
+        <v>6832990</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5894,28 +5901,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845626</v>
+        <v>129845612</v>
       </c>
       <c r="B55" t="n">
-        <v>91626</v>
+        <v>79678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5923,41 +5931,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406533</v>
+        <v>406379</v>
       </c>
       <c r="R55" t="n">
-        <v>6832761</v>
+        <v>6832756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5998,7 +5999,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845435</v>
+        <v>129845625</v>
       </c>
       <c r="B56" t="n">
-        <v>79677</v>
+        <v>91627</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,34 +6028,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406455</v>
+        <v>406472</v>
       </c>
       <c r="R56" t="n">
-        <v>6833027</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,72 +6103,64 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845459</v>
+        <v>129845487</v>
       </c>
       <c r="B57" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406331</v>
+        <v>406409</v>
       </c>
       <c r="R57" t="n">
-        <v>6832715</v>
+        <v>6832824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6202,7 +6201,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6221,45 +6219,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845466</v>
+        <v>129845459</v>
       </c>
       <c r="B58" t="n">
-        <v>78844</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406266</v>
+        <v>406331</v>
       </c>
       <c r="R58" t="n">
-        <v>6832810</v>
+        <v>6832715</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6300,6 +6307,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6318,10 +6326,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845625</v>
+        <v>129845435</v>
       </c>
       <c r="B59" t="n">
-        <v>91626</v>
+        <v>79678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6329,41 +6337,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406472</v>
+        <v>406455</v>
       </c>
       <c r="R59" t="n">
-        <v>6832767</v>
+        <v>6833027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6404,29 +6405,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845487</v>
+        <v>129845410</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406409</v>
+        <v>406487</v>
       </c>
       <c r="R60" t="n">
-        <v>6832824</v>
+        <v>6833064</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845410</v>
+        <v>129845602</v>
       </c>
       <c r="B61" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406487</v>
+        <v>406791</v>
       </c>
       <c r="R61" t="n">
-        <v>6833064</v>
+        <v>6832844</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,22 +6605,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845602</v>
+        <v>129845466</v>
       </c>
       <c r="B62" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406791</v>
+        <v>406266</v>
       </c>
       <c r="R62" t="n">
-        <v>6832844</v>
+        <v>6832810</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6702,12 +6702,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845452</v>
+        <v>129845590</v>
       </c>
       <c r="B66" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,42 +7040,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406630</v>
+        <v>406421</v>
       </c>
       <c r="R66" t="n">
-        <v>6832941</v>
+        <v>6833142</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7122,66 +7114,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845642</v>
+        <v>129845593</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406547</v>
+        <v>406451</v>
       </c>
       <c r="R67" t="n">
-        <v>6832775</v>
+        <v>6832712</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7222,7 +7205,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7241,45 +7223,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845434</v>
+        <v>129845642</v>
       </c>
       <c r="B68" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406499</v>
+        <v>406547</v>
       </c>
       <c r="R68" t="n">
-        <v>6833054</v>
+        <v>6832775</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7320,28 +7311,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845440</v>
+        <v>129845434</v>
       </c>
       <c r="B69" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7373,10 +7365,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406445</v>
+        <v>406499</v>
       </c>
       <c r="R69" t="n">
-        <v>6832921</v>
+        <v>6833054</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7435,10 +7427,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845605</v>
+        <v>129845440</v>
       </c>
       <c r="B70" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7470,10 +7462,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406440</v>
+        <v>406445</v>
       </c>
       <c r="R70" t="n">
-        <v>6833100</v>
+        <v>6832921</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7520,22 +7512,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845607</v>
+        <v>129845605</v>
       </c>
       <c r="B71" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7567,10 +7559,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406407</v>
+        <v>406440</v>
       </c>
       <c r="R71" t="n">
-        <v>6833199</v>
+        <v>6833100</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7629,10 +7621,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845654</v>
+        <v>129845607</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,21 +7632,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7664,10 +7656,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406460</v>
+        <v>406407</v>
       </c>
       <c r="R72" t="n">
-        <v>6832823</v>
+        <v>6833199</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7726,10 +7718,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845493</v>
+        <v>129845654</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7761,10 +7753,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406785</v>
+        <v>406460</v>
       </c>
       <c r="R73" t="n">
-        <v>6832912</v>
+        <v>6832823</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7811,22 +7803,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845590</v>
+        <v>129845493</v>
       </c>
       <c r="B74" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,21 +7826,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7858,10 +7850,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406421</v>
+        <v>406785</v>
       </c>
       <c r="R74" t="n">
-        <v>6833142</v>
+        <v>6832912</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7908,22 +7900,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845593</v>
+        <v>129845452</v>
       </c>
       <c r="B75" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,34 +7923,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406451</v>
+        <v>406630</v>
       </c>
       <c r="R75" t="n">
-        <v>6832712</v>
+        <v>6832941</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,22 +8005,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129845606</v>
+        <v>129845486</v>
       </c>
       <c r="B76" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,21 +8028,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406394</v>
+        <v>406350</v>
       </c>
       <c r="R76" t="n">
-        <v>6833197</v>
+        <v>6832772</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8102,12 +8102,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8117,7 +8117,7 @@
         <v>129845420</v>
       </c>
       <c r="B77" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>129845415</v>
       </c>
       <c r="B78" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>129845600</v>
       </c>
       <c r="B79" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129845486</v>
+        <v>129845606</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406350</v>
+        <v>406394</v>
       </c>
       <c r="R80" t="n">
-        <v>6832772</v>
+        <v>6833197</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8490,12 +8490,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8505,7 +8505,7 @@
         <v>129845444</v>
       </c>
       <c r="B81" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8603,10 +8603,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845621</v>
+        <v>129845454</v>
       </c>
       <c r="B82" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8614,16 +8614,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8636,7 +8636,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406672</v>
+        <v>406675</v>
       </c>
       <c r="R82" t="n">
-        <v>6832840</v>
+        <v>6832988</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8696,22 +8696,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845647</v>
+        <v>129845621</v>
       </c>
       <c r="B83" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8719,34 +8719,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406274</v>
+        <v>406672</v>
       </c>
       <c r="R83" t="n">
-        <v>6832759</v>
+        <v>6832840</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8805,10 +8813,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845454</v>
+        <v>129845647</v>
       </c>
       <c r="B84" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8816,42 +8824,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406675</v>
+        <v>406274</v>
       </c>
       <c r="R84" t="n">
-        <v>6832988</v>
+        <v>6832759</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8898,12 +8898,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845653</v>
+        <v>129845423</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9026,21 +9026,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406430</v>
+        <v>406531</v>
       </c>
       <c r="R86" t="n">
-        <v>6832777</v>
+        <v>6832868</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,57 +9100,66 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845656</v>
+        <v>129845641</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406480</v>
+        <v>406618</v>
       </c>
       <c r="R87" t="n">
-        <v>6832777</v>
+        <v>6832813</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9191,6 +9200,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9209,43 +9219,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845641</v>
+        <v>129845437</v>
       </c>
       <c r="B88" t="n">
-        <v>8451</v>
+        <v>79678</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9253,10 +9257,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406618</v>
+        <v>406331</v>
       </c>
       <c r="R88" t="n">
-        <v>6832813</v>
+        <v>6832676</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9304,22 +9308,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845437</v>
+        <v>129845656</v>
       </c>
       <c r="B89" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9327,37 +9331,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406331</v>
+        <v>406480</v>
       </c>
       <c r="R89" t="n">
-        <v>6832676</v>
+        <v>6832777</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9398,29 +9399,28 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845423</v>
+        <v>129845653</v>
       </c>
       <c r="B90" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9428,21 +9428,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406531</v>
+        <v>406430</v>
       </c>
       <c r="R90" t="n">
-        <v>6832868</v>
+        <v>6832777</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9502,22 +9502,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845479</v>
+        <v>129845608</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,21 +9525,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406408</v>
+        <v>406399</v>
       </c>
       <c r="R91" t="n">
-        <v>6832975</v>
+        <v>6833177</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9599,22 +9599,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845480</v>
+        <v>129845479</v>
       </c>
       <c r="B92" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406277</v>
+        <v>406408</v>
       </c>
       <c r="R92" t="n">
-        <v>6832823</v>
+        <v>6832975</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845594</v>
+        <v>129845480</v>
       </c>
       <c r="B93" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406506</v>
+        <v>406277</v>
       </c>
       <c r="R93" t="n">
-        <v>6832725</v>
+        <v>6832823</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9793,22 +9793,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845408</v>
+        <v>129845594</v>
       </c>
       <c r="B94" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406368</v>
+        <v>406506</v>
       </c>
       <c r="R94" t="n">
-        <v>6833202</v>
+        <v>6832725</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9890,22 +9890,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845457</v>
+        <v>129845418</v>
       </c>
       <c r="B95" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406265</v>
+        <v>406377</v>
       </c>
       <c r="R95" t="n">
-        <v>6832808</v>
+        <v>6832837</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845418</v>
+        <v>129845408</v>
       </c>
       <c r="B96" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406377</v>
+        <v>406368</v>
       </c>
       <c r="R96" t="n">
-        <v>6832837</v>
+        <v>6833202</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845608</v>
+        <v>129845457</v>
       </c>
       <c r="B99" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406399</v>
+        <v>406265</v>
       </c>
       <c r="R99" t="n">
-        <v>6833177</v>
+        <v>6832808</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10391,22 +10391,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845426</v>
+        <v>129845646</v>
       </c>
       <c r="B100" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,21 +10414,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406796</v>
+        <v>406290</v>
       </c>
       <c r="R100" t="n">
-        <v>6832917</v>
+        <v>6832901</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10488,22 +10488,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845407</v>
+        <v>129845426</v>
       </c>
       <c r="B101" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406416</v>
+        <v>406796</v>
       </c>
       <c r="R101" t="n">
-        <v>6833166</v>
+        <v>6832917</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10597,10 +10597,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845646</v>
+        <v>129845629</v>
       </c>
       <c r="B102" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,34 +10608,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406290</v>
+        <v>406618</v>
       </c>
       <c r="R102" t="n">
-        <v>6832901</v>
+        <v>6832773</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10697,7 +10705,7 @@
         <v>129845615</v>
       </c>
       <c r="B103" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10791,10 +10799,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845629</v>
+        <v>129845407</v>
       </c>
       <c r="B104" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10802,42 +10810,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406618</v>
+        <v>406416</v>
       </c>
       <c r="R104" t="n">
-        <v>6832773</v>
+        <v>6833166</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,22 +10884,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845439</v>
+        <v>129845597</v>
       </c>
       <c r="B105" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406377</v>
+        <v>406615</v>
       </c>
       <c r="R105" t="n">
-        <v>6832840</v>
+        <v>6832770</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10981,22 +10981,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845485</v>
+        <v>129845439</v>
       </c>
       <c r="B106" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406320</v>
+        <v>406377</v>
       </c>
       <c r="R106" t="n">
-        <v>6832742</v>
+        <v>6832840</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845450</v>
+        <v>129845485</v>
       </c>
       <c r="B107" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,42 +11101,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406508</v>
+        <v>406320</v>
       </c>
       <c r="R107" t="n">
-        <v>6832877</v>
+        <v>6832742</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11195,10 +11187,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845448</v>
+        <v>129845595</v>
       </c>
       <c r="B108" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11206,42 +11198,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406396</v>
+        <v>406455</v>
       </c>
       <c r="R108" t="n">
-        <v>6832853</v>
+        <v>6832823</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11288,22 +11272,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845597</v>
+        <v>129845450</v>
       </c>
       <c r="B109" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11311,34 +11295,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406615</v>
+        <v>406508</v>
       </c>
       <c r="R109" t="n">
-        <v>6832770</v>
+        <v>6832877</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11385,22 +11377,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845595</v>
+        <v>129845448</v>
       </c>
       <c r="B110" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11408,34 +11400,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406455</v>
+        <v>406396</v>
       </c>
       <c r="R110" t="n">
-        <v>6832823</v>
+        <v>6832853</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11482,12 +11482,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11497,7 +11497,7 @@
         <v>129845421</v>
       </c>
       <c r="B111" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11591,53 +11591,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845644</v>
+        <v>129845433</v>
       </c>
       <c r="B112" t="n">
-        <v>58111</v>
+        <v>79678</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406457</v>
+        <v>406438</v>
       </c>
       <c r="R112" t="n">
-        <v>6832809</v>
+        <v>6833114</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11684,22 +11676,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845433</v>
+        <v>129845430</v>
       </c>
       <c r="B113" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11731,10 +11723,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406438</v>
+        <v>406465</v>
       </c>
       <c r="R113" t="n">
-        <v>6833114</v>
+        <v>6833093</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11793,45 +11785,53 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845430</v>
+        <v>129845644</v>
       </c>
       <c r="B114" t="n">
-        <v>79677</v>
+        <v>58111</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406465</v>
+        <v>406457</v>
       </c>
       <c r="R114" t="n">
-        <v>6833093</v>
+        <v>6832809</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11878,12 +11878,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -11997,10 +11997,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845596</v>
+        <v>129845458</v>
       </c>
       <c r="B116" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,21 +12008,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406536</v>
+        <v>406531</v>
       </c>
       <c r="R116" t="n">
-        <v>6832770</v>
+        <v>6832927</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12082,22 +12082,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845628</v>
+        <v>129845596</v>
       </c>
       <c r="B117" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12105,42 +12105,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406541</v>
+        <v>406536</v>
       </c>
       <c r="R117" t="n">
-        <v>6832823</v>
+        <v>6832770</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12199,7 +12191,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845635</v>
+        <v>129845628</v>
       </c>
       <c r="B118" t="n">
         <v>57737</v>
@@ -12232,7 +12224,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -12242,10 +12234,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406677</v>
+        <v>406541</v>
       </c>
       <c r="R118" t="n">
-        <v>6832986</v>
+        <v>6832823</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12304,10 +12296,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845436</v>
+        <v>129845635</v>
       </c>
       <c r="B119" t="n">
-        <v>79677</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12315,34 +12307,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406315</v>
+        <v>406677</v>
       </c>
       <c r="R119" t="n">
-        <v>6832667</v>
+        <v>6832986</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12389,22 +12389,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845458</v>
+        <v>129845436</v>
       </c>
       <c r="B120" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406531</v>
+        <v>406315</v>
       </c>
       <c r="R120" t="n">
-        <v>6832927</v>
+        <v>6832667</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12498,10 +12498,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129845495</v>
+        <v>129845588</v>
       </c>
       <c r="B121" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12509,21 +12509,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12533,10 +12533,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406668</v>
+        <v>406440</v>
       </c>
       <c r="R121" t="n">
-        <v>6833007</v>
+        <v>6833101</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12583,22 +12583,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129845484</v>
+        <v>129845591</v>
       </c>
       <c r="B122" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12606,37 +12606,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406310</v>
+        <v>406439</v>
       </c>
       <c r="R122" t="n">
-        <v>6832729</v>
+        <v>6833139</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12677,19 +12674,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12699,7 +12695,7 @@
         <v>129845494</v>
       </c>
       <c r="B123" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12793,10 +12789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845588</v>
+        <v>129845495</v>
       </c>
       <c r="B124" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12804,21 +12800,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12828,10 +12824,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406440</v>
+        <v>406668</v>
       </c>
       <c r="R124" t="n">
-        <v>6833101</v>
+        <v>6833007</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12878,22 +12874,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845591</v>
+        <v>129845484</v>
       </c>
       <c r="B125" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12901,34 +12897,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406439</v>
+        <v>406310</v>
       </c>
       <c r="R125" t="n">
-        <v>6833139</v>
+        <v>6832729</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12969,18 +12968,19 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13095,7 +13095,7 @@
         <v>129845432</v>
       </c>
       <c r="B127" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>129845414</v>
       </c>
       <c r="B128" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>129845411</v>
       </c>
       <c r="B129" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>129845603</v>
       </c>
       <c r="B130" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>129845424</v>
       </c>
       <c r="B131" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13577,32 +13577,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845623</v>
+        <v>129845453</v>
       </c>
       <c r="B132" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13610,7 +13610,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13620,10 +13620,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406310</v>
+        <v>406716</v>
       </c>
       <c r="R132" t="n">
-        <v>6832901</v>
+        <v>6832970</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13670,44 +13670,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845453</v>
+        <v>129845623</v>
       </c>
       <c r="B133" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13715,7 +13715,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406716</v>
+        <v>406310</v>
       </c>
       <c r="R133" t="n">
-        <v>6832970</v>
+        <v>6832901</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13775,22 +13775,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845482</v>
+        <v>129845489</v>
       </c>
       <c r="B134" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13822,10 +13822,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406282</v>
+        <v>406542</v>
       </c>
       <c r="R134" t="n">
-        <v>6832624</v>
+        <v>6832915</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13884,10 +13884,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845489</v>
+        <v>129845658</v>
       </c>
       <c r="B135" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13919,10 +13919,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406542</v>
+        <v>406563</v>
       </c>
       <c r="R135" t="n">
-        <v>6832915</v>
+        <v>6832887</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13969,22 +13969,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845658</v>
+        <v>129845482</v>
       </c>
       <c r="B136" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14016,10 +14016,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406563</v>
+        <v>406282</v>
       </c>
       <c r="R136" t="n">
-        <v>6832887</v>
+        <v>6832624</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14186,7 +14186,7 @@
         <v>129845478</v>
       </c>
       <c r="B138" t="n">
-        <v>90987</v>
+        <v>90988</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>129845497</v>
       </c>
       <c r="B139" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -1758,54 +1758,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845462</v>
+        <v>129845604</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406713</v>
+        <v>406424</v>
       </c>
       <c r="R13" t="n">
-        <v>6832904</v>
+        <v>6832657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,29 +1837,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845610</v>
+        <v>129845467</v>
       </c>
       <c r="B14" t="n">
-        <v>79678</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1876,34 +1866,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406262</v>
+        <v>406359</v>
       </c>
       <c r="R14" t="n">
-        <v>6832854</v>
+        <v>6832764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,63 +1937,73 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845618</v>
+        <v>129845462</v>
       </c>
       <c r="B15" t="n">
-        <v>79678</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406791</v>
+        <v>406713</v>
       </c>
       <c r="R15" t="n">
-        <v>6832845</v>
+        <v>6832904</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,28 +2044,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845429</v>
+        <v>129845655</v>
       </c>
       <c r="B16" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2070,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2094,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406472</v>
+        <v>406473</v>
       </c>
       <c r="R16" t="n">
-        <v>6833103</v>
+        <v>6832798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,19 +2148,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845614</v>
+        <v>129845610</v>
       </c>
       <c r="B17" t="n">
         <v>79678</v>
@@ -2191,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406492</v>
+        <v>406262</v>
       </c>
       <c r="R17" t="n">
-        <v>6832753</v>
+        <v>6832854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,7 +2257,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845613</v>
+        <v>129845614</v>
       </c>
       <c r="B18" t="n">
         <v>79678</v>
@@ -2288,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406388</v>
+        <v>406492</v>
       </c>
       <c r="R18" t="n">
-        <v>6832683</v>
+        <v>6832753</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2350,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845617</v>
+        <v>129845618</v>
       </c>
       <c r="B19" t="n">
         <v>79678</v>
@@ -2385,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406626</v>
+        <v>406791</v>
       </c>
       <c r="R19" t="n">
-        <v>6832781</v>
+        <v>6832845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845655</v>
+        <v>129845429</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2458,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406473</v>
+        <v>406472</v>
       </c>
       <c r="R20" t="n">
-        <v>6832798</v>
+        <v>6833103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,22 +2536,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845604</v>
+        <v>129845613</v>
       </c>
       <c r="B21" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406424</v>
+        <v>406388</v>
       </c>
       <c r="R21" t="n">
-        <v>6832657</v>
+        <v>6832683</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2641,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845467</v>
+        <v>129845617</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,37 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406359</v>
+        <v>406626</v>
       </c>
       <c r="R22" t="n">
-        <v>6832764</v>
+        <v>6832781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,19 +2724,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3528,41 +3528,40 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845463</v>
+        <v>129845636</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3572,10 +3571,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406746</v>
+        <v>406595</v>
       </c>
       <c r="R31" t="n">
-        <v>6832985</v>
+        <v>6833001</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,29 +3615,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845639</v>
+        <v>129845449</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3646,34 +3644,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406276</v>
+        <v>406498</v>
       </c>
       <c r="R32" t="n">
-        <v>6832761</v>
+        <v>6832913</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3720,52 +3726,53 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845636</v>
+        <v>129845463</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3775,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406595</v>
+        <v>406746</v>
       </c>
       <c r="R33" t="n">
-        <v>6833001</v>
+        <v>6832985</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3819,28 +3826,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845449</v>
+        <v>129845639</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3848,42 +3856,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406498</v>
+        <v>406276</v>
       </c>
       <c r="R34" t="n">
-        <v>6832913</v>
+        <v>6832761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3930,12 +3930,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5417,10 +5417,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845638</v>
+        <v>129845624</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>57898</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5428,34 +5428,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406290</v>
+        <v>406494</v>
       </c>
       <c r="R50" t="n">
-        <v>6832900</v>
+        <v>6832766</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5514,10 +5522,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845416</v>
+        <v>129845612</v>
       </c>
       <c r="B51" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,21 +5533,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5549,10 +5557,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406362</v>
+        <v>406379</v>
       </c>
       <c r="R51" t="n">
-        <v>6832766</v>
+        <v>6832756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,19 +5607,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845589</v>
+        <v>129845416</v>
       </c>
       <c r="B52" t="n">
         <v>79707</v>
@@ -5646,10 +5654,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406406</v>
+        <v>406362</v>
       </c>
       <c r="R52" t="n">
-        <v>6833199</v>
+        <v>6832766</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5696,22 +5704,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845624</v>
+        <v>129845589</v>
       </c>
       <c r="B53" t="n">
-        <v>57898</v>
+        <v>79707</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5719,42 +5727,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406494</v>
+        <v>406406</v>
       </c>
       <c r="R53" t="n">
-        <v>6832766</v>
+        <v>6833199</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845612</v>
+        <v>129845638</v>
       </c>
       <c r="B55" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406379</v>
+        <v>406290</v>
       </c>
       <c r="R55" t="n">
-        <v>6832756</v>
+        <v>6832900</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845590</v>
+        <v>129845654</v>
       </c>
       <c r="B66" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406421</v>
+        <v>406460</v>
       </c>
       <c r="R66" t="n">
-        <v>6833142</v>
+        <v>6832823</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845593</v>
+        <v>129845493</v>
       </c>
       <c r="B67" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406451</v>
+        <v>406785</v>
       </c>
       <c r="R67" t="n">
-        <v>6832712</v>
+        <v>6832912</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7211,66 +7211,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845642</v>
+        <v>129845590</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406547</v>
+        <v>406421</v>
       </c>
       <c r="R68" t="n">
-        <v>6832775</v>
+        <v>6833142</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7311,7 +7302,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7330,10 +7320,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845434</v>
+        <v>129845593</v>
       </c>
       <c r="B69" t="n">
-        <v>79678</v>
+        <v>79707</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7341,21 +7331,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7365,10 +7355,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406499</v>
+        <v>406451</v>
       </c>
       <c r="R69" t="n">
-        <v>6833054</v>
+        <v>6832712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7415,22 +7405,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845440</v>
+        <v>129845452</v>
       </c>
       <c r="B70" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7438,34 +7428,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406445</v>
+        <v>406630</v>
       </c>
       <c r="R70" t="n">
-        <v>6832921</v>
+        <v>6832941</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7524,45 +7522,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845605</v>
+        <v>129845642</v>
       </c>
       <c r="B71" t="n">
-        <v>79678</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406440</v>
+        <v>406547</v>
       </c>
       <c r="R71" t="n">
-        <v>6833100</v>
+        <v>6832775</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7603,6 +7610,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7621,7 +7629,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845607</v>
+        <v>129845434</v>
       </c>
       <c r="B72" t="n">
         <v>79678</v>
@@ -7656,10 +7664,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406407</v>
+        <v>406499</v>
       </c>
       <c r="R72" t="n">
-        <v>6833199</v>
+        <v>6833054</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7706,22 +7714,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845654</v>
+        <v>129845440</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7729,21 +7737,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7753,10 +7761,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406460</v>
+        <v>406445</v>
       </c>
       <c r="R73" t="n">
-        <v>6832823</v>
+        <v>6832921</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7803,22 +7811,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845493</v>
+        <v>129845605</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7826,21 +7834,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7850,10 +7858,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406785</v>
+        <v>406440</v>
       </c>
       <c r="R74" t="n">
-        <v>6832912</v>
+        <v>6833100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7900,22 +7908,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845452</v>
+        <v>129845607</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7923,42 +7931,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406630</v>
+        <v>406407</v>
       </c>
       <c r="R75" t="n">
-        <v>6832941</v>
+        <v>6833199</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,12 +8005,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845423</v>
+        <v>129845656</v>
       </c>
       <c r="B86" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9026,21 +9026,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406531</v>
+        <v>406480</v>
       </c>
       <c r="R86" t="n">
-        <v>6832868</v>
+        <v>6832777</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9100,66 +9100,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845641</v>
+        <v>129845653</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406618</v>
+        <v>406430</v>
       </c>
       <c r="R87" t="n">
-        <v>6832813</v>
+        <v>6832777</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9200,7 +9191,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9219,10 +9209,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845437</v>
+        <v>129845423</v>
       </c>
       <c r="B88" t="n">
-        <v>79678</v>
+        <v>79707</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9230,37 +9220,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406331</v>
+        <v>406531</v>
       </c>
       <c r="R88" t="n">
-        <v>6832676</v>
+        <v>6832868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9301,7 +9288,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9320,45 +9306,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845656</v>
+        <v>129845641</v>
       </c>
       <c r="B89" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406480</v>
+        <v>406618</v>
       </c>
       <c r="R89" t="n">
-        <v>6832777</v>
+        <v>6832813</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9399,6 +9394,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9417,10 +9413,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845653</v>
+        <v>129845437</v>
       </c>
       <c r="B90" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9428,34 +9424,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406430</v>
+        <v>406331</v>
       </c>
       <c r="R90" t="n">
-        <v>6832777</v>
+        <v>6832676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9496,28 +9495,29 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845608</v>
+        <v>129845479</v>
       </c>
       <c r="B91" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,21 +9525,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406399</v>
+        <v>406408</v>
       </c>
       <c r="R91" t="n">
-        <v>6833177</v>
+        <v>6832975</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9599,19 +9599,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845479</v>
+        <v>129845480</v>
       </c>
       <c r="B92" t="n">
         <v>79088</v>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406408</v>
+        <v>406277</v>
       </c>
       <c r="R92" t="n">
-        <v>6832975</v>
+        <v>6832823</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,45 +9708,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845480</v>
+        <v>129845464</v>
       </c>
       <c r="B93" t="n">
-        <v>79088</v>
+        <v>58111</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406277</v>
+        <v>406416</v>
       </c>
       <c r="R93" t="n">
-        <v>6832823</v>
+        <v>6832880</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10201,53 +10209,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845464</v>
+        <v>129845608</v>
       </c>
       <c r="B98" t="n">
-        <v>58111</v>
+        <v>79678</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406416</v>
+        <v>406399</v>
       </c>
       <c r="R98" t="n">
-        <v>6832880</v>
+        <v>6833177</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10294,12 +10294,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11997,10 +11997,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845458</v>
+        <v>129845628</v>
       </c>
       <c r="B116" t="n">
-        <v>78846</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,34 +12008,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406531</v>
+        <v>406541</v>
       </c>
       <c r="R116" t="n">
-        <v>6832927</v>
+        <v>6832823</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12082,22 +12090,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845596</v>
+        <v>129845635</v>
       </c>
       <c r="B117" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12105,34 +12113,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406536</v>
+        <v>406677</v>
       </c>
       <c r="R117" t="n">
-        <v>6832770</v>
+        <v>6832986</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12191,10 +12207,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845628</v>
+        <v>129845436</v>
       </c>
       <c r="B118" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12202,42 +12218,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406541</v>
+        <v>406315</v>
       </c>
       <c r="R118" t="n">
-        <v>6832823</v>
+        <v>6832667</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12284,22 +12292,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845635</v>
+        <v>129845458</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12307,42 +12315,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406677</v>
+        <v>406531</v>
       </c>
       <c r="R119" t="n">
-        <v>6832986</v>
+        <v>6832927</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12389,22 +12389,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845436</v>
+        <v>129845596</v>
       </c>
       <c r="B120" t="n">
-        <v>79678</v>
+        <v>79707</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,21 +12412,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406315</v>
+        <v>406536</v>
       </c>
       <c r="R120" t="n">
-        <v>6832667</v>
+        <v>6832770</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,12 +12486,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845414</v>
+        <v>129845453</v>
       </c>
       <c r="B128" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13200,34 +13200,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406313</v>
+        <v>406716</v>
       </c>
       <c r="R128" t="n">
-        <v>6832656</v>
+        <v>6832970</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13286,10 +13294,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845411</v>
+        <v>129845489</v>
       </c>
       <c r="B129" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13297,21 +13305,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13321,10 +13329,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406442</v>
+        <v>406542</v>
       </c>
       <c r="R129" t="n">
-        <v>6833040</v>
+        <v>6832915</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13383,10 +13391,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129845603</v>
+        <v>129845658</v>
       </c>
       <c r="B130" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13394,21 +13402,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13418,10 +13426,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406764</v>
+        <v>406563</v>
       </c>
       <c r="R130" t="n">
-        <v>6832925</v>
+        <v>6832887</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13480,10 +13488,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845424</v>
+        <v>129845482</v>
       </c>
       <c r="B131" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13491,21 +13499,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13515,10 +13523,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406533</v>
+        <v>406282</v>
       </c>
       <c r="R131" t="n">
-        <v>6832861</v>
+        <v>6832624</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13577,10 +13585,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845453</v>
+        <v>129845414</v>
       </c>
       <c r="B132" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13588,42 +13596,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406716</v>
+        <v>406313</v>
       </c>
       <c r="R132" t="n">
-        <v>6832970</v>
+        <v>6832656</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13682,53 +13682,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845623</v>
+        <v>129845411</v>
       </c>
       <c r="B133" t="n">
-        <v>56930</v>
+        <v>79707</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406310</v>
+        <v>406442</v>
       </c>
       <c r="R133" t="n">
-        <v>6832901</v>
+        <v>6833040</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13775,22 +13767,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845489</v>
+        <v>129845603</v>
       </c>
       <c r="B134" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13798,21 +13790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13822,10 +13814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406542</v>
+        <v>406764</v>
       </c>
       <c r="R134" t="n">
-        <v>6832915</v>
+        <v>6832925</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13872,22 +13864,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845658</v>
+        <v>129845424</v>
       </c>
       <c r="B135" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13895,21 +13887,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13919,10 +13911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406563</v>
+        <v>406533</v>
       </c>
       <c r="R135" t="n">
-        <v>6832887</v>
+        <v>6832861</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13969,57 +13961,65 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845482</v>
+        <v>129845623</v>
       </c>
       <c r="B136" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406282</v>
+        <v>406310</v>
       </c>
       <c r="R136" t="n">
-        <v>6832624</v>
+        <v>6832901</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845419</v>
+        <v>129845599</v>
       </c>
       <c r="B2" t="n">
         <v>79707</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406387</v>
+        <v>406635</v>
       </c>
       <c r="R2" t="n">
-        <v>6832850</v>
+        <v>6832779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845599</v>
+        <v>129845598</v>
       </c>
       <c r="B3" t="n">
         <v>79707</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406635</v>
+        <v>406626</v>
       </c>
       <c r="R3" t="n">
-        <v>6832779</v>
+        <v>6832781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845598</v>
+        <v>129845425</v>
       </c>
       <c r="B4" t="n">
         <v>79707</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406626</v>
+        <v>406832</v>
       </c>
       <c r="R4" t="n">
-        <v>6832781</v>
+        <v>6832816</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845425</v>
+        <v>129845419</v>
       </c>
       <c r="B5" t="n">
         <v>79707</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406832</v>
+        <v>406387</v>
       </c>
       <c r="R5" t="n">
-        <v>6832816</v>
+        <v>6832850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1758,45 +1758,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845604</v>
+        <v>129845462</v>
       </c>
       <c r="B13" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406424</v>
+        <v>406713</v>
       </c>
       <c r="R13" t="n">
-        <v>6832657</v>
+        <v>6832904</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,28 +1846,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845467</v>
+        <v>129845610</v>
       </c>
       <c r="B14" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,37 +1876,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406359</v>
+        <v>406262</v>
       </c>
       <c r="R14" t="n">
-        <v>6832764</v>
+        <v>6832854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1937,73 +1944,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845462</v>
+        <v>129845618</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406713</v>
+        <v>406791</v>
       </c>
       <c r="R15" t="n">
-        <v>6832904</v>
+        <v>6832845</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,29 +2041,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845655</v>
+        <v>129845429</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2070,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2094,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406473</v>
+        <v>406472</v>
       </c>
       <c r="R16" t="n">
-        <v>6832798</v>
+        <v>6833103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,19 +2144,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845610</v>
+        <v>129845614</v>
       </c>
       <c r="B17" t="n">
         <v>79678</v>
@@ -2195,10 +2191,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406262</v>
+        <v>406492</v>
       </c>
       <c r="R17" t="n">
-        <v>6832854</v>
+        <v>6832753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,7 +2253,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845614</v>
+        <v>129845613</v>
       </c>
       <c r="B18" t="n">
         <v>79678</v>
@@ -2292,10 +2288,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406492</v>
+        <v>406388</v>
       </c>
       <c r="R18" t="n">
-        <v>6832753</v>
+        <v>6832683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,7 +2350,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845618</v>
+        <v>129845617</v>
       </c>
       <c r="B19" t="n">
         <v>79678</v>
@@ -2389,10 +2385,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406791</v>
+        <v>406626</v>
       </c>
       <c r="R19" t="n">
-        <v>6832845</v>
+        <v>6832781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,10 +2447,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845429</v>
+        <v>129845655</v>
       </c>
       <c r="B20" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,21 +2458,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406472</v>
+        <v>406473</v>
       </c>
       <c r="R20" t="n">
-        <v>6833103</v>
+        <v>6832798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,22 +2532,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845613</v>
+        <v>129845604</v>
       </c>
       <c r="B21" t="n">
-        <v>79678</v>
+        <v>79707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2555,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406388</v>
+        <v>406424</v>
       </c>
       <c r="R21" t="n">
-        <v>6832683</v>
+        <v>6832657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2641,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845617</v>
+        <v>129845467</v>
       </c>
       <c r="B22" t="n">
-        <v>79678</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2652,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406626</v>
+        <v>406359</v>
       </c>
       <c r="R22" t="n">
-        <v>6832781</v>
+        <v>6832764</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2724,18 +2723,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845654</v>
+        <v>129845590</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406460</v>
+        <v>406421</v>
       </c>
       <c r="R66" t="n">
-        <v>6832823</v>
+        <v>6833142</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845493</v>
+        <v>129845593</v>
       </c>
       <c r="B67" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406785</v>
+        <v>406451</v>
       </c>
       <c r="R67" t="n">
-        <v>6832912</v>
+        <v>6832712</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7211,57 +7211,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845590</v>
+        <v>129845642</v>
       </c>
       <c r="B68" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406421</v>
+        <v>406547</v>
       </c>
       <c r="R68" t="n">
-        <v>6833142</v>
+        <v>6832775</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7302,6 +7311,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7320,10 +7330,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845593</v>
+        <v>129845434</v>
       </c>
       <c r="B69" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7331,21 +7341,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7355,10 +7365,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406451</v>
+        <v>406499</v>
       </c>
       <c r="R69" t="n">
-        <v>6832712</v>
+        <v>6833054</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7405,22 +7415,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845452</v>
+        <v>129845440</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7428,42 +7438,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406630</v>
+        <v>406445</v>
       </c>
       <c r="R70" t="n">
-        <v>6832941</v>
+        <v>6832921</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7522,54 +7524,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845642</v>
+        <v>129845605</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>79678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406547</v>
+        <v>406440</v>
       </c>
       <c r="R71" t="n">
-        <v>6832775</v>
+        <v>6833100</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7610,7 +7603,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7629,7 +7621,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845434</v>
+        <v>129845607</v>
       </c>
       <c r="B72" t="n">
         <v>79678</v>
@@ -7664,10 +7656,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406499</v>
+        <v>406407</v>
       </c>
       <c r="R72" t="n">
-        <v>6833054</v>
+        <v>6833199</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7714,22 +7706,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845440</v>
+        <v>129845654</v>
       </c>
       <c r="B73" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,21 +7729,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7761,10 +7753,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406445</v>
+        <v>406460</v>
       </c>
       <c r="R73" t="n">
-        <v>6832921</v>
+        <v>6832823</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7811,22 +7803,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845605</v>
+        <v>129845493</v>
       </c>
       <c r="B74" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,21 +7826,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7858,10 +7850,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406440</v>
+        <v>406785</v>
       </c>
       <c r="R74" t="n">
-        <v>6833100</v>
+        <v>6832912</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7908,22 +7900,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845607</v>
+        <v>129845452</v>
       </c>
       <c r="B75" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,34 +7923,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406407</v>
+        <v>406630</v>
       </c>
       <c r="R75" t="n">
-        <v>6833199</v>
+        <v>6832941</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,12 +8005,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845479</v>
+        <v>129845608</v>
       </c>
       <c r="B91" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,21 +9525,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406408</v>
+        <v>406399</v>
       </c>
       <c r="R91" t="n">
-        <v>6832975</v>
+        <v>6833177</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9599,19 +9599,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845480</v>
+        <v>129845479</v>
       </c>
       <c r="B92" t="n">
         <v>79088</v>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406277</v>
+        <v>406408</v>
       </c>
       <c r="R92" t="n">
-        <v>6832823</v>
+        <v>6832975</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,53 +9708,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845464</v>
+        <v>129845480</v>
       </c>
       <c r="B93" t="n">
-        <v>58111</v>
+        <v>79088</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406416</v>
+        <v>406277</v>
       </c>
       <c r="R93" t="n">
-        <v>6832880</v>
+        <v>6832823</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10209,45 +10201,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845608</v>
+        <v>129845464</v>
       </c>
       <c r="B98" t="n">
-        <v>79678</v>
+        <v>58111</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406399</v>
+        <v>406416</v>
       </c>
       <c r="R98" t="n">
-        <v>6833177</v>
+        <v>6832880</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10294,12 +10294,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10597,10 +10597,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845629</v>
+        <v>129845407</v>
       </c>
       <c r="B102" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,42 +10608,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406618</v>
+        <v>406416</v>
       </c>
       <c r="R102" t="n">
-        <v>6832773</v>
+        <v>6833166</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10690,22 +10682,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845615</v>
+        <v>129845629</v>
       </c>
       <c r="B103" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10713,34 +10705,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406583</v>
+        <v>406618</v>
       </c>
       <c r="R103" t="n">
-        <v>6832911</v>
+        <v>6832773</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10799,10 +10799,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B104" t="n">
-        <v>79707</v>
+        <v>79678</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R104" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,22 +10884,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845597</v>
+        <v>129845485</v>
       </c>
       <c r="B105" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406615</v>
+        <v>406320</v>
       </c>
       <c r="R105" t="n">
-        <v>6832770</v>
+        <v>6832742</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10981,12 +10981,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845485</v>
+        <v>129845597</v>
       </c>
       <c r="B107" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,21 +11101,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11125,10 +11125,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406320</v>
+        <v>406615</v>
       </c>
       <c r="R107" t="n">
-        <v>6832742</v>
+        <v>6832770</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11175,12 +11175,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129845453</v>
+        <v>129845414</v>
       </c>
       <c r="B128" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13200,42 +13200,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406716</v>
+        <v>406313</v>
       </c>
       <c r="R128" t="n">
-        <v>6832970</v>
+        <v>6832656</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13294,10 +13286,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129845489</v>
+        <v>129845411</v>
       </c>
       <c r="B129" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13305,21 +13297,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13329,10 +13321,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406542</v>
+        <v>406442</v>
       </c>
       <c r="R129" t="n">
-        <v>6832915</v>
+        <v>6833040</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13391,10 +13383,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129845658</v>
+        <v>129845603</v>
       </c>
       <c r="B130" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13402,21 +13394,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13426,10 +13418,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406563</v>
+        <v>406764</v>
       </c>
       <c r="R130" t="n">
-        <v>6832887</v>
+        <v>6832925</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13488,10 +13480,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129845482</v>
+        <v>129845424</v>
       </c>
       <c r="B131" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13499,21 +13491,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13523,10 +13515,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406282</v>
+        <v>406533</v>
       </c>
       <c r="R131" t="n">
-        <v>6832624</v>
+        <v>6832861</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13585,10 +13577,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845414</v>
+        <v>129845453</v>
       </c>
       <c r="B132" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13596,34 +13588,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406313</v>
+        <v>406716</v>
       </c>
       <c r="R132" t="n">
-        <v>6832656</v>
+        <v>6832970</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13682,45 +13682,53 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845411</v>
+        <v>129845623</v>
       </c>
       <c r="B133" t="n">
-        <v>79707</v>
+        <v>56930</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406442</v>
+        <v>406310</v>
       </c>
       <c r="R133" t="n">
-        <v>6833040</v>
+        <v>6832901</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13767,22 +13775,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845603</v>
+        <v>129845489</v>
       </c>
       <c r="B134" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13790,21 +13798,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13814,10 +13822,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406764</v>
+        <v>406542</v>
       </c>
       <c r="R134" t="n">
-        <v>6832925</v>
+        <v>6832915</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13864,22 +13872,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845424</v>
+        <v>129845658</v>
       </c>
       <c r="B135" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13887,21 +13895,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13911,10 +13919,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406533</v>
+        <v>406563</v>
       </c>
       <c r="R135" t="n">
-        <v>6832861</v>
+        <v>6832887</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13961,65 +13969,57 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845623</v>
+        <v>129845482</v>
       </c>
       <c r="B136" t="n">
-        <v>56930</v>
+        <v>79088</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406310</v>
+        <v>406282</v>
       </c>
       <c r="R136" t="n">
-        <v>6832901</v>
+        <v>6832624</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129845599</v>
       </c>
       <c r="B2" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129845598</v>
       </c>
       <c r="B3" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129845425</v>
       </c>
       <c r="B4" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129845419</v>
       </c>
       <c r="B5" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129845438</v>
       </c>
       <c r="B6" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129845441</v>
       </c>
       <c r="B7" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845661</v>
+        <v>129845427</v>
       </c>
       <c r="B8" t="n">
-        <v>78754</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406352</v>
+        <v>406794</v>
       </c>
       <c r="R8" t="n">
-        <v>6832709</v>
+        <v>6832934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845427</v>
+        <v>129845417</v>
       </c>
       <c r="B9" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406794</v>
+        <v>406346</v>
       </c>
       <c r="R9" t="n">
-        <v>6832934</v>
+        <v>6832798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845417</v>
+        <v>129845661</v>
       </c>
       <c r="B10" t="n">
-        <v>79707</v>
+        <v>78755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406346</v>
+        <v>406352</v>
       </c>
       <c r="R10" t="n">
-        <v>6832798</v>
+        <v>6832709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
         <v>129845443</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129845610</v>
       </c>
       <c r="B14" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845618</v>
+        <v>129845614</v>
       </c>
       <c r="B15" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406791</v>
+        <v>406492</v>
       </c>
       <c r="R15" t="n">
-        <v>6832845</v>
+        <v>6832753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845429</v>
+        <v>129845618</v>
       </c>
       <c r="B16" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406472</v>
+        <v>406791</v>
       </c>
       <c r="R16" t="n">
-        <v>6833103</v>
+        <v>6832845</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,22 +2144,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845614</v>
+        <v>129845429</v>
       </c>
       <c r="B17" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406492</v>
+        <v>406472</v>
       </c>
       <c r="R17" t="n">
-        <v>6832753</v>
+        <v>6833103</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,12 +2241,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
         <v>129845613</v>
       </c>
       <c r="B18" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>129845617</v>
       </c>
       <c r="B19" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845655</v>
+        <v>129845604</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2458,21 +2458,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406473</v>
+        <v>406424</v>
       </c>
       <c r="R20" t="n">
-        <v>6832798</v>
+        <v>6832657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845604</v>
+        <v>129845467</v>
       </c>
       <c r="B21" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,34 +2555,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406424</v>
+        <v>406359</v>
       </c>
       <c r="R21" t="n">
-        <v>6832657</v>
+        <v>6832764</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2623,28 +2626,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845467</v>
+        <v>129845655</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,37 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406359</v>
+        <v>406473</v>
       </c>
       <c r="R22" t="n">
-        <v>6832764</v>
+        <v>6832798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,29 +2724,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129845488</v>
+        <v>129845422</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2753,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406528</v>
+        <v>406513</v>
       </c>
       <c r="R23" t="n">
-        <v>6832873</v>
+        <v>6832869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129845652</v>
+        <v>129845413</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406408</v>
+        <v>406266</v>
       </c>
       <c r="R24" t="n">
-        <v>6832778</v>
+        <v>6832827</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,22 +2924,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129845659</v>
+        <v>129845488</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406556</v>
+        <v>406528</v>
       </c>
       <c r="R25" t="n">
-        <v>6832846</v>
+        <v>6832873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,22 +3021,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845413</v>
+        <v>129845652</v>
       </c>
       <c r="B26" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406266</v>
+        <v>406408</v>
       </c>
       <c r="R26" t="n">
-        <v>6832827</v>
+        <v>6832778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3118,22 +3118,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845422</v>
+        <v>129845659</v>
       </c>
       <c r="B27" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406513</v>
+        <v>406556</v>
       </c>
       <c r="R27" t="n">
-        <v>6832869</v>
+        <v>6832846</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3215,12 +3215,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
         <v>129845619</v>
       </c>
       <c r="B29" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3431,45 +3431,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845412</v>
+        <v>129845463</v>
       </c>
       <c r="B30" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406426</v>
+        <v>406746</v>
       </c>
       <c r="R30" t="n">
-        <v>6832990</v>
+        <v>6832985</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3510,6 +3519,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3528,10 +3538,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845636</v>
+        <v>129845412</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,42 +3549,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406595</v>
+        <v>406426</v>
       </c>
       <c r="R31" t="n">
-        <v>6833001</v>
+        <v>6832990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3621,19 +3623,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845449</v>
+        <v>129845636</v>
       </c>
       <c r="B32" t="n">
         <v>57737</v>
@@ -3666,7 +3668,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3676,10 +3678,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406498</v>
+        <v>406595</v>
       </c>
       <c r="R32" t="n">
-        <v>6832913</v>
+        <v>6833001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,53 +3728,52 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845463</v>
+        <v>129845449</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3782,10 +3783,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406746</v>
+        <v>406498</v>
       </c>
       <c r="R33" t="n">
-        <v>6832985</v>
+        <v>6832913</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3826,7 +3827,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>129845639</v>
       </c>
       <c r="B34" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845481</v>
+        <v>129845592</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406278</v>
+        <v>406370</v>
       </c>
       <c r="R35" t="n">
-        <v>6832795</v>
+        <v>6832711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,22 +4027,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845483</v>
+        <v>129845657</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406344</v>
+        <v>406495</v>
       </c>
       <c r="R36" t="n">
-        <v>6832706</v>
+        <v>6832766</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4124,22 +4124,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845657</v>
+        <v>129845481</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406495</v>
+        <v>406278</v>
       </c>
       <c r="R37" t="n">
-        <v>6832766</v>
+        <v>6832795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,22 +4221,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845592</v>
+        <v>129845483</v>
       </c>
       <c r="B38" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406370</v>
+        <v>406344</v>
       </c>
       <c r="R38" t="n">
-        <v>6832711</v>
+        <v>6832706</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,12 +4318,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
         <v>129845455</v>
       </c>
       <c r="B39" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845492</v>
+        <v>129845601</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4438,37 +4438,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406591</v>
+        <v>406583</v>
       </c>
       <c r="R40" t="n">
-        <v>6832966</v>
+        <v>6832841</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4509,29 +4506,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845660</v>
+        <v>129845491</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406728</v>
+        <v>406588</v>
       </c>
       <c r="R41" t="n">
-        <v>6832848</v>
+        <v>6832866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4613,22 +4609,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845601</v>
+        <v>129845490</v>
       </c>
       <c r="B42" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4636,21 +4632,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4660,10 +4656,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406583</v>
+        <v>406560</v>
       </c>
       <c r="R42" t="n">
-        <v>6832841</v>
+        <v>6832885</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,12 +4706,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4827,10 +4823,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845456</v>
+        <v>129845492</v>
       </c>
       <c r="B44" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4838,34 +4834,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406442</v>
+        <v>406591</v>
       </c>
       <c r="R44" t="n">
-        <v>6833041</v>
+        <v>6832966</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,6 +4905,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4924,10 +4924,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845490</v>
+        <v>129845660</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406560</v>
+        <v>406728</v>
       </c>
       <c r="R45" t="n">
-        <v>6832885</v>
+        <v>6832848</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,22 +5009,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845491</v>
+        <v>129845611</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406588</v>
+        <v>406276</v>
       </c>
       <c r="R46" t="n">
-        <v>6832866</v>
+        <v>6832761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5106,22 +5106,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845611</v>
+        <v>129845431</v>
       </c>
       <c r="B47" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406276</v>
+        <v>406368</v>
       </c>
       <c r="R47" t="n">
-        <v>6832761</v>
+        <v>6833201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5203,22 +5203,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845431</v>
+        <v>129845456</v>
       </c>
       <c r="B48" t="n">
-        <v>79678</v>
+        <v>78847</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5226,21 +5226,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406368</v>
+        <v>406442</v>
       </c>
       <c r="R48" t="n">
-        <v>6833201</v>
+        <v>6833041</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5312,10 +5312,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845626</v>
+        <v>129845624</v>
       </c>
       <c r="B49" t="n">
-        <v>91627</v>
+        <v>57899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5323,30 +5323,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5354,10 +5355,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406533</v>
+        <v>406494</v>
       </c>
       <c r="R49" t="n">
-        <v>6832761</v>
+        <v>6832766</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5398,7 +5399,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5417,10 +5417,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845624</v>
+        <v>129845638</v>
       </c>
       <c r="B50" t="n">
-        <v>57898</v>
+        <v>78847</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5428,42 +5428,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406494</v>
+        <v>406290</v>
       </c>
       <c r="R50" t="n">
-        <v>6832766</v>
+        <v>6832900</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5525,7 +5517,7 @@
         <v>129845612</v>
       </c>
       <c r="B51" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5619,45 +5611,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845416</v>
+        <v>129845461</v>
       </c>
       <c r="B52" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406362</v>
+        <v>406589</v>
       </c>
       <c r="R52" t="n">
-        <v>6832766</v>
+        <v>6832990</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5698,6 +5699,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5716,10 +5718,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845589</v>
+        <v>129845416</v>
       </c>
       <c r="B53" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5751,10 +5753,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406406</v>
+        <v>406362</v>
       </c>
       <c r="R53" t="n">
-        <v>6833199</v>
+        <v>6832766</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5801,66 +5803,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845461</v>
+        <v>129845589</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>79708</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406589</v>
+        <v>406406</v>
       </c>
       <c r="R54" t="n">
-        <v>6832990</v>
+        <v>6833199</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5901,29 +5894,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845638</v>
+        <v>129845626</v>
       </c>
       <c r="B55" t="n">
-        <v>78846</v>
+        <v>91644</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5931,34 +5923,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406290</v>
+        <v>406533</v>
       </c>
       <c r="R55" t="n">
-        <v>6832900</v>
+        <v>6832761</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5999,6 +5998,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845625</v>
+        <v>129845410</v>
       </c>
       <c r="B56" t="n">
-        <v>91627</v>
+        <v>79708</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,41 +6028,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406472</v>
+        <v>406487</v>
       </c>
       <c r="R56" t="n">
-        <v>6832767</v>
+        <v>6833064</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6103,29 +6096,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845487</v>
+        <v>129845602</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6133,21 +6125,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6157,10 +6149,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406409</v>
+        <v>406791</v>
       </c>
       <c r="R57" t="n">
-        <v>6832824</v>
+        <v>6832844</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6207,66 +6199,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845459</v>
+        <v>129845466</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406331</v>
+        <v>406266</v>
       </c>
       <c r="R58" t="n">
-        <v>6832715</v>
+        <v>6832810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6307,7 +6290,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6326,10 +6308,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845435</v>
+        <v>129845487</v>
       </c>
       <c r="B59" t="n">
-        <v>79678</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6337,21 +6319,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6361,10 +6343,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406455</v>
+        <v>406409</v>
       </c>
       <c r="R59" t="n">
-        <v>6833027</v>
+        <v>6832824</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6423,10 +6405,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845410</v>
+        <v>129845625</v>
       </c>
       <c r="B60" t="n">
-        <v>79707</v>
+        <v>91644</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,34 +6416,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406487</v>
+        <v>406472</v>
       </c>
       <c r="R60" t="n">
-        <v>6833064</v>
+        <v>6832767</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6502,28 +6491,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845602</v>
+        <v>129845632</v>
       </c>
       <c r="B61" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,34 +6521,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406791</v>
+        <v>406667</v>
       </c>
       <c r="R61" t="n">
-        <v>6832844</v>
+        <v>6832849</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6617,10 +6615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845466</v>
+        <v>129845633</v>
       </c>
       <c r="B62" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,34 +6626,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406266</v>
+        <v>406674</v>
       </c>
       <c r="R62" t="n">
-        <v>6832810</v>
+        <v>6832801</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6702,19 +6708,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845632</v>
+        <v>129845627</v>
       </c>
       <c r="B63" t="n">
         <v>57737</v>
@@ -6747,7 +6753,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6757,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406667</v>
+        <v>406539</v>
       </c>
       <c r="R63" t="n">
-        <v>6832849</v>
+        <v>6832767</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6819,40 +6825,41 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845633</v>
+        <v>129845459</v>
       </c>
       <c r="B64" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6862,10 +6869,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406674</v>
+        <v>406331</v>
       </c>
       <c r="R64" t="n">
-        <v>6832801</v>
+        <v>6832715</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,28 +6913,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845627</v>
+        <v>129845435</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>79679</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6935,42 +6943,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406539</v>
+        <v>406455</v>
       </c>
       <c r="R65" t="n">
-        <v>6832767</v>
+        <v>6833027</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7017,12 +7017,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7032,7 +7032,7 @@
         <v>129845590</v>
       </c>
       <c r="B66" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>129845593</v>
       </c>
       <c r="B67" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7223,54 +7223,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845642</v>
+        <v>129845654</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406547</v>
+        <v>406460</v>
       </c>
       <c r="R68" t="n">
-        <v>6832775</v>
+        <v>6832823</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7311,7 +7302,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7330,10 +7320,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845434</v>
+        <v>129845493</v>
       </c>
       <c r="B69" t="n">
-        <v>79678</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7341,21 +7331,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7365,10 +7355,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406499</v>
+        <v>406785</v>
       </c>
       <c r="R69" t="n">
-        <v>6833054</v>
+        <v>6832912</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7427,10 +7417,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129845440</v>
+        <v>129845452</v>
       </c>
       <c r="B70" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7438,34 +7428,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406445</v>
+        <v>406630</v>
       </c>
       <c r="R70" t="n">
-        <v>6832921</v>
+        <v>6832941</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7524,10 +7522,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845605</v>
+        <v>129845434</v>
       </c>
       <c r="B71" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7559,10 +7557,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406440</v>
+        <v>406499</v>
       </c>
       <c r="R71" t="n">
-        <v>6833100</v>
+        <v>6833054</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7609,22 +7607,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845607</v>
+        <v>129845440</v>
       </c>
       <c r="B72" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7656,10 +7654,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406407</v>
+        <v>406445</v>
       </c>
       <c r="R72" t="n">
-        <v>6833199</v>
+        <v>6832921</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7706,22 +7704,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845654</v>
+        <v>129845605</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7729,21 +7727,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7753,10 +7751,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406460</v>
+        <v>406440</v>
       </c>
       <c r="R73" t="n">
-        <v>6832823</v>
+        <v>6833100</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7815,10 +7813,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845493</v>
+        <v>129845607</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7826,21 +7824,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7850,10 +7848,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406785</v>
+        <v>406407</v>
       </c>
       <c r="R74" t="n">
-        <v>6832912</v>
+        <v>6833199</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7900,52 +7898,53 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129845452</v>
+        <v>129845642</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -7955,10 +7954,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406630</v>
+        <v>406547</v>
       </c>
       <c r="R75" t="n">
-        <v>6832941</v>
+        <v>6832775</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7999,28 +7998,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129845486</v>
+        <v>129845420</v>
       </c>
       <c r="B76" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,21 +8028,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406350</v>
+        <v>406424</v>
       </c>
       <c r="R76" t="n">
-        <v>6832772</v>
+        <v>6832865</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845420</v>
+        <v>129845415</v>
       </c>
       <c r="B77" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406424</v>
+        <v>406317</v>
       </c>
       <c r="R77" t="n">
-        <v>6832865</v>
+        <v>6832733</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8211,10 +8211,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845415</v>
+        <v>129845600</v>
       </c>
       <c r="B78" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406317</v>
+        <v>406582</v>
       </c>
       <c r="R78" t="n">
-        <v>6832733</v>
+        <v>6832826</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8296,22 +8296,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845600</v>
+        <v>129845486</v>
       </c>
       <c r="B79" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406582</v>
+        <v>406350</v>
       </c>
       <c r="R79" t="n">
-        <v>6832826</v>
+        <v>6832772</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8393,12 +8393,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8408,7 +8408,7 @@
         <v>129845606</v>
       </c>
       <c r="B80" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845444</v>
+        <v>129845647</v>
       </c>
       <c r="B81" t="n">
-        <v>91627</v>
+        <v>78846</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,37 +8513,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406601</v>
+        <v>406274</v>
       </c>
       <c r="R81" t="n">
-        <v>6832858</v>
+        <v>6832759</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8584,29 +8581,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845454</v>
+        <v>129845444</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>91644</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8614,31 +8610,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8646,10 +8637,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406675</v>
+        <v>406601</v>
       </c>
       <c r="R82" t="n">
-        <v>6832988</v>
+        <v>6832858</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8690,6 +8681,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8708,10 +8700,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845621</v>
+        <v>129845454</v>
       </c>
       <c r="B83" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8719,16 +8711,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8741,7 +8733,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8751,10 +8743,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406672</v>
+        <v>406675</v>
       </c>
       <c r="R83" t="n">
-        <v>6832840</v>
+        <v>6832988</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8801,22 +8793,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845647</v>
+        <v>129845621</v>
       </c>
       <c r="B84" t="n">
-        <v>78845</v>
+        <v>57740</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8824,34 +8816,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406274</v>
+        <v>406672</v>
       </c>
       <c r="R84" t="n">
-        <v>6832759</v>
+        <v>6832840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8913,7 +8913,7 @@
         <v>129845465</v>
       </c>
       <c r="B85" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129845656</v>
+        <v>129845653</v>
       </c>
       <c r="B86" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406480</v>
+        <v>406430</v>
       </c>
       <c r="R86" t="n">
         <v>6832777</v>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129845653</v>
+        <v>129845656</v>
       </c>
       <c r="B87" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406430</v>
+        <v>406480</v>
       </c>
       <c r="R87" t="n">
         <v>6832777</v>
@@ -9209,45 +9209,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845423</v>
+        <v>129845641</v>
       </c>
       <c r="B88" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406531</v>
+        <v>406618</v>
       </c>
       <c r="R88" t="n">
-        <v>6832868</v>
+        <v>6832813</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9288,61 +9297,56 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845641</v>
+        <v>129845437</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>79679</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9350,10 +9354,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406618</v>
+        <v>406331</v>
       </c>
       <c r="R89" t="n">
-        <v>6832813</v>
+        <v>6832676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9401,22 +9405,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845437</v>
+        <v>129845423</v>
       </c>
       <c r="B90" t="n">
-        <v>79678</v>
+        <v>79708</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9424,37 +9428,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406331</v>
+        <v>406531</v>
       </c>
       <c r="R90" t="n">
-        <v>6832676</v>
+        <v>6832868</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9495,7 +9496,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845608</v>
+        <v>129845594</v>
       </c>
       <c r="B91" t="n">
-        <v>79678</v>
+        <v>79708</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,21 +9525,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406399</v>
+        <v>406506</v>
       </c>
       <c r="R91" t="n">
-        <v>6833177</v>
+        <v>6832725</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9611,10 +9611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845479</v>
+        <v>129845418</v>
       </c>
       <c r="B92" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9622,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406408</v>
+        <v>406377</v>
       </c>
       <c r="R92" t="n">
-        <v>6832975</v>
+        <v>6832837</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845480</v>
+        <v>129845408</v>
       </c>
       <c r="B93" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406277</v>
+        <v>406368</v>
       </c>
       <c r="R93" t="n">
-        <v>6832823</v>
+        <v>6833202</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845594</v>
+        <v>129845634</v>
       </c>
       <c r="B94" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9816,34 +9816,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406506</v>
+        <v>406781</v>
       </c>
       <c r="R94" t="n">
-        <v>6832725</v>
+        <v>6832843</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,45 +9910,53 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845418</v>
+        <v>129845464</v>
       </c>
       <c r="B95" t="n">
-        <v>79707</v>
+        <v>58112</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406377</v>
+        <v>406416</v>
       </c>
       <c r="R95" t="n">
-        <v>6832837</v>
+        <v>6832880</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +10015,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845408</v>
+        <v>129845457</v>
       </c>
       <c r="B96" t="n">
-        <v>79707</v>
+        <v>78847</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,21 +10026,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10034,10 +10050,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406368</v>
+        <v>406265</v>
       </c>
       <c r="R96" t="n">
-        <v>6833202</v>
+        <v>6832808</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10096,10 +10112,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845634</v>
+        <v>129845608</v>
       </c>
       <c r="B97" t="n">
-        <v>57737</v>
+        <v>79679</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10107,42 +10123,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406781</v>
+        <v>406399</v>
       </c>
       <c r="R97" t="n">
-        <v>6832843</v>
+        <v>6833177</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,53 +10209,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845464</v>
+        <v>129845479</v>
       </c>
       <c r="B98" t="n">
-        <v>58111</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406416</v>
+        <v>406408</v>
       </c>
       <c r="R98" t="n">
-        <v>6832880</v>
+        <v>6832975</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845457</v>
+        <v>129845480</v>
       </c>
       <c r="B99" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406265</v>
+        <v>406277</v>
       </c>
       <c r="R99" t="n">
-        <v>6832808</v>
+        <v>6832823</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10403,10 +10403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845646</v>
+        <v>129845629</v>
       </c>
       <c r="B100" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,34 +10414,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406290</v>
+        <v>406618</v>
       </c>
       <c r="R100" t="n">
-        <v>6832901</v>
+        <v>6832773</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10500,10 +10508,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845426</v>
+        <v>129845615</v>
       </c>
       <c r="B101" t="n">
-        <v>79707</v>
+        <v>79679</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10511,21 +10519,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10535,10 +10543,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406796</v>
+        <v>406583</v>
       </c>
       <c r="R101" t="n">
-        <v>6832917</v>
+        <v>6832911</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10585,22 +10593,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845407</v>
+        <v>129845646</v>
       </c>
       <c r="B102" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,21 +10616,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10632,10 +10640,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406416</v>
+        <v>406290</v>
       </c>
       <c r="R102" t="n">
-        <v>6833166</v>
+        <v>6832901</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10682,22 +10690,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845629</v>
+        <v>129845426</v>
       </c>
       <c r="B103" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,42 +10713,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406618</v>
+        <v>406796</v>
       </c>
       <c r="R103" t="n">
-        <v>6832773</v>
+        <v>6832917</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10787,22 +10787,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845615</v>
+        <v>129845407</v>
       </c>
       <c r="B104" t="n">
-        <v>79678</v>
+        <v>79708</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406583</v>
+        <v>406416</v>
       </c>
       <c r="R104" t="n">
-        <v>6832911</v>
+        <v>6833166</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,22 +10884,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129845485</v>
+        <v>129845597</v>
       </c>
       <c r="B105" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10907,21 +10907,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406320</v>
+        <v>406615</v>
       </c>
       <c r="R105" t="n">
-        <v>6832742</v>
+        <v>6832770</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10981,22 +10981,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129845439</v>
+        <v>129845595</v>
       </c>
       <c r="B106" t="n">
-        <v>79678</v>
+        <v>79708</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11004,21 +11004,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>406377</v>
+        <v>406455</v>
       </c>
       <c r="R106" t="n">
-        <v>6832840</v>
+        <v>6832823</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11078,22 +11078,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129845597</v>
+        <v>129845485</v>
       </c>
       <c r="B107" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11101,21 +11101,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11125,10 +11125,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406615</v>
+        <v>406320</v>
       </c>
       <c r="R107" t="n">
-        <v>6832770</v>
+        <v>6832742</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11175,22 +11175,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129845595</v>
+        <v>129845450</v>
       </c>
       <c r="B108" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11198,34 +11198,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406455</v>
+        <v>406508</v>
       </c>
       <c r="R108" t="n">
-        <v>6832823</v>
+        <v>6832877</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11272,19 +11280,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129845450</v>
+        <v>129845448</v>
       </c>
       <c r="B109" t="n">
         <v>57737</v>
@@ -11327,10 +11335,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406508</v>
+        <v>406396</v>
       </c>
       <c r="R109" t="n">
-        <v>6832877</v>
+        <v>6832853</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11389,10 +11397,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129845448</v>
+        <v>129845439</v>
       </c>
       <c r="B110" t="n">
-        <v>57737</v>
+        <v>79679</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11400,42 +11408,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406396</v>
+        <v>406377</v>
       </c>
       <c r="R110" t="n">
-        <v>6832853</v>
+        <v>6832840</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11497,7 +11497,7 @@
         <v>129845421</v>
       </c>
       <c r="B111" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11591,45 +11591,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845433</v>
+        <v>129845644</v>
       </c>
       <c r="B112" t="n">
-        <v>79678</v>
+        <v>58112</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406438</v>
+        <v>406457</v>
       </c>
       <c r="R112" t="n">
-        <v>6833114</v>
+        <v>6832809</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11676,57 +11684,66 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845430</v>
+        <v>129845640</v>
       </c>
       <c r="B113" t="n">
-        <v>79678</v>
+        <v>8451</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406465</v>
+        <v>406404</v>
       </c>
       <c r="R113" t="n">
-        <v>6833093</v>
+        <v>6832729</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11767,71 +11784,64 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845644</v>
+        <v>129845433</v>
       </c>
       <c r="B114" t="n">
-        <v>58111</v>
+        <v>79679</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406457</v>
+        <v>406438</v>
       </c>
       <c r="R114" t="n">
-        <v>6832809</v>
+        <v>6833114</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11878,66 +11888,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845640</v>
+        <v>129845430</v>
       </c>
       <c r="B115" t="n">
-        <v>8451</v>
+        <v>79679</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406404</v>
+        <v>406465</v>
       </c>
       <c r="R115" t="n">
-        <v>6832729</v>
+        <v>6833093</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11978,29 +11979,28 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845628</v>
+        <v>129845596</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,42 +12008,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406541</v>
+        <v>406536</v>
       </c>
       <c r="R116" t="n">
-        <v>6832823</v>
+        <v>6832770</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12102,10 +12094,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845635</v>
+        <v>129845458</v>
       </c>
       <c r="B117" t="n">
-        <v>57737</v>
+        <v>78847</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12113,42 +12105,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406677</v>
+        <v>406531</v>
       </c>
       <c r="R117" t="n">
-        <v>6832986</v>
+        <v>6832927</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12195,12 +12179,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12210,7 +12194,7 @@
         <v>129845436</v>
       </c>
       <c r="B118" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12304,10 +12288,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129845458</v>
+        <v>129845628</v>
       </c>
       <c r="B119" t="n">
-        <v>78846</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12315,34 +12299,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406531</v>
+        <v>406541</v>
       </c>
       <c r="R119" t="n">
-        <v>6832927</v>
+        <v>6832823</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12389,22 +12381,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129845596</v>
+        <v>129845635</v>
       </c>
       <c r="B120" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12412,34 +12404,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>406536</v>
+        <v>406677</v>
       </c>
       <c r="R120" t="n">
-        <v>6832770</v>
+        <v>6832986</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12501,7 +12501,7 @@
         <v>129845588</v>
       </c>
       <c r="B121" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>129845591</v>
       </c>
       <c r="B122" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12692,10 +12692,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129845494</v>
+        <v>129845495</v>
       </c>
       <c r="B123" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12727,10 +12727,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406710</v>
+        <v>406668</v>
       </c>
       <c r="R123" t="n">
-        <v>6832990</v>
+        <v>6833007</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12789,10 +12789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845495</v>
+        <v>129845484</v>
       </c>
       <c r="B124" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12818,16 +12818,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406668</v>
+        <v>406310</v>
       </c>
       <c r="R124" t="n">
-        <v>6833007</v>
+        <v>6832729</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12868,6 +12871,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12886,10 +12890,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845484</v>
+        <v>129845494</v>
       </c>
       <c r="B125" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12915,19 +12919,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406310</v>
+        <v>406710</v>
       </c>
       <c r="R125" t="n">
-        <v>6832729</v>
+        <v>6832990</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12968,7 +12969,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12987,10 +12987,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845451</v>
+        <v>129845432</v>
       </c>
       <c r="B126" t="n">
-        <v>57737</v>
+        <v>79679</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12998,42 +12998,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406595</v>
+        <v>406373</v>
       </c>
       <c r="R126" t="n">
-        <v>6832931</v>
+        <v>6833176</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13092,10 +13084,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845432</v>
+        <v>129845451</v>
       </c>
       <c r="B127" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13103,34 +13095,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406373</v>
+        <v>406595</v>
       </c>
       <c r="R127" t="n">
-        <v>6833176</v>
+        <v>6832931</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13192,7 +13192,7 @@
         <v>129845414</v>
       </c>
       <c r="B128" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>129845411</v>
       </c>
       <c r="B129" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>129845603</v>
       </c>
       <c r="B130" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>129845424</v>
       </c>
       <c r="B131" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13577,10 +13577,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129845453</v>
+        <v>129845482</v>
       </c>
       <c r="B132" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13588,42 +13588,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406716</v>
+        <v>406282</v>
       </c>
       <c r="R132" t="n">
-        <v>6832970</v>
+        <v>6832624</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13682,53 +13674,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129845623</v>
+        <v>129845489</v>
       </c>
       <c r="B133" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406310</v>
+        <v>406542</v>
       </c>
       <c r="R133" t="n">
-        <v>6832901</v>
+        <v>6832915</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13775,22 +13759,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129845489</v>
+        <v>129845658</v>
       </c>
       <c r="B134" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13822,10 +13806,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406542</v>
+        <v>406563</v>
       </c>
       <c r="R134" t="n">
-        <v>6832915</v>
+        <v>6832887</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13872,22 +13856,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129845658</v>
+        <v>129845453</v>
       </c>
       <c r="B135" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13895,34 +13879,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406563</v>
+        <v>406716</v>
       </c>
       <c r="R135" t="n">
-        <v>6832887</v>
+        <v>6832970</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13969,57 +13961,65 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129845482</v>
+        <v>129845623</v>
       </c>
       <c r="B136" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406282</v>
+        <v>406310</v>
       </c>
       <c r="R136" t="n">
-        <v>6832624</v>
+        <v>6832901</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14186,7 +14186,7 @@
         <v>129845478</v>
       </c>
       <c r="B138" t="n">
-        <v>90988</v>
+        <v>91005</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>129845497</v>
       </c>
       <c r="B139" t="n">
-        <v>92029</v>
+        <v>92046</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845438</v>
+        <v>129845599</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406361</v>
+        <v>406635</v>
       </c>
       <c r="R2" t="n">
-        <v>6832815</v>
+        <v>6832779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845441</v>
+        <v>129845598</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406638</v>
+        <v>406626</v>
       </c>
       <c r="R3" t="n">
-        <v>6832869</v>
+        <v>6832781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845599</v>
+        <v>129845425</v>
       </c>
       <c r="B4" t="n">
         <v>79714</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406635</v>
+        <v>406832</v>
       </c>
       <c r="R4" t="n">
-        <v>6832779</v>
+        <v>6832816</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845598</v>
+        <v>129845419</v>
       </c>
       <c r="B5" t="n">
         <v>79714</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406626</v>
+        <v>406387</v>
       </c>
       <c r="R5" t="n">
-        <v>6832781</v>
+        <v>6832850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845425</v>
+        <v>129845438</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406832</v>
+        <v>406361</v>
       </c>
       <c r="R6" t="n">
-        <v>6832816</v>
+        <v>6832815</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845419</v>
+        <v>129845441</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406387</v>
+        <v>406638</v>
       </c>
       <c r="R7" t="n">
-        <v>6832850</v>
+        <v>6832869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1758,54 +1758,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129845462</v>
+        <v>129845604</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406713</v>
+        <v>406424</v>
       </c>
       <c r="R13" t="n">
-        <v>6832904</v>
+        <v>6832657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,29 +1837,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129845610</v>
+        <v>129845467</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>78852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1876,34 +1866,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406262</v>
+        <v>406359</v>
       </c>
       <c r="R14" t="n">
-        <v>6832854</v>
+        <v>6832764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,63 +1937,73 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845614</v>
+        <v>129845462</v>
       </c>
       <c r="B15" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406492</v>
+        <v>406713</v>
       </c>
       <c r="R15" t="n">
-        <v>6832753</v>
+        <v>6832904</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,25 +2044,26 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845618</v>
+        <v>129845610</v>
       </c>
       <c r="B16" t="n">
         <v>79685</v>
@@ -2094,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406791</v>
+        <v>406262</v>
       </c>
       <c r="R16" t="n">
-        <v>6832845</v>
+        <v>6832854</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2156,7 +2160,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845429</v>
+        <v>129845614</v>
       </c>
       <c r="B17" t="n">
         <v>79685</v>
@@ -2191,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406472</v>
+        <v>406492</v>
       </c>
       <c r="R17" t="n">
-        <v>6833103</v>
+        <v>6832753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,19 +2245,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845613</v>
+        <v>129845618</v>
       </c>
       <c r="B18" t="n">
         <v>79685</v>
@@ -2288,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406388</v>
+        <v>406791</v>
       </c>
       <c r="R18" t="n">
-        <v>6832683</v>
+        <v>6832845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2350,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845617</v>
+        <v>129845429</v>
       </c>
       <c r="B19" t="n">
         <v>79685</v>
@@ -2385,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406626</v>
+        <v>406472</v>
       </c>
       <c r="R19" t="n">
-        <v>6832781</v>
+        <v>6833103</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,22 +2439,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845655</v>
+        <v>129845613</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2458,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406473</v>
+        <v>406388</v>
       </c>
       <c r="R20" t="n">
-        <v>6832798</v>
+        <v>6832683</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2544,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845604</v>
+        <v>129845617</v>
       </c>
       <c r="B21" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406424</v>
+        <v>406626</v>
       </c>
       <c r="R21" t="n">
-        <v>6832657</v>
+        <v>6832781</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2641,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845467</v>
+        <v>129845655</v>
       </c>
       <c r="B22" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,37 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406359</v>
+        <v>406473</v>
       </c>
       <c r="R22" t="n">
-        <v>6832764</v>
+        <v>6832798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,19 +2724,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3033,54 +3033,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129845460</v>
+        <v>129845422</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406431</v>
+        <v>406513</v>
       </c>
       <c r="R26" t="n">
-        <v>6832825</v>
+        <v>6832869</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,7 +3112,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129845619</v>
+        <v>129845413</v>
       </c>
       <c r="B27" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3175,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406776</v>
+        <v>406266</v>
       </c>
       <c r="R27" t="n">
-        <v>6832860</v>
+        <v>6832827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,57 +3215,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129845422</v>
+        <v>129845460</v>
       </c>
       <c r="B28" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406513</v>
+        <v>406431</v>
       </c>
       <c r="R28" t="n">
-        <v>6832869</v>
+        <v>6832825</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3316,6 +3315,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129845413</v>
+        <v>129845619</v>
       </c>
       <c r="B29" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406266</v>
+        <v>406776</v>
       </c>
       <c r="R29" t="n">
-        <v>6832827</v>
+        <v>6832860</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3419,12 +3419,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3641,54 +3641,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845463</v>
+        <v>129845412</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406746</v>
+        <v>406426</v>
       </c>
       <c r="R32" t="n">
-        <v>6832985</v>
+        <v>6832990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3729,7 +3720,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3748,45 +3738,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845639</v>
+        <v>129845463</v>
       </c>
       <c r="B33" t="n">
-        <v>78853</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406276</v>
+        <v>406746</v>
       </c>
       <c r="R33" t="n">
-        <v>6832761</v>
+        <v>6832985</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3827,28 +3826,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845412</v>
+        <v>129845639</v>
       </c>
       <c r="B34" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406426</v>
+        <v>406276</v>
       </c>
       <c r="R34" t="n">
-        <v>6832990</v>
+        <v>6832761</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3930,19 +3930,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845481</v>
+        <v>129845657</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406278</v>
+        <v>406495</v>
       </c>
       <c r="R35" t="n">
-        <v>6832795</v>
+        <v>6832766</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,22 +4027,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845483</v>
+        <v>129845592</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406344</v>
+        <v>406370</v>
       </c>
       <c r="R36" t="n">
-        <v>6832706</v>
+        <v>6832711</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4124,22 +4124,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845592</v>
+        <v>129845481</v>
       </c>
       <c r="B37" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4147,21 +4147,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406370</v>
+        <v>406278</v>
       </c>
       <c r="R37" t="n">
-        <v>6832711</v>
+        <v>6832795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,19 +4221,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845657</v>
+        <v>129845483</v>
       </c>
       <c r="B38" t="n">
         <v>79095</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406495</v>
+        <v>406344</v>
       </c>
       <c r="R38" t="n">
-        <v>6832766</v>
+        <v>6832706</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,12 +4318,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845490</v>
+        <v>129845601</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4438,21 +4438,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406560</v>
+        <v>406583</v>
       </c>
       <c r="R40" t="n">
-        <v>6832885</v>
+        <v>6832841</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4512,19 +4512,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845491</v>
+        <v>129845490</v>
       </c>
       <c r="B41" t="n">
         <v>79095</v>
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406588</v>
+        <v>406560</v>
       </c>
       <c r="R41" t="n">
-        <v>6832866</v>
+        <v>6832885</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845492</v>
+        <v>129845491</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -4650,19 +4650,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406591</v>
+        <v>406588</v>
       </c>
       <c r="R42" t="n">
-        <v>6832966</v>
+        <v>6832866</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4703,7 +4700,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4722,7 +4718,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845660</v>
+        <v>129845492</v>
       </c>
       <c r="B43" t="n">
         <v>79095</v>
@@ -4751,16 +4747,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406728</v>
+        <v>406591</v>
       </c>
       <c r="R43" t="n">
-        <v>6832848</v>
+        <v>6832966</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4801,28 +4800,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845631</v>
+        <v>129845660</v>
       </c>
       <c r="B44" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,42 +4830,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406698</v>
+        <v>406728</v>
       </c>
       <c r="R44" t="n">
-        <v>6832875</v>
+        <v>6832848</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4924,10 +4916,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845601</v>
+        <v>129845611</v>
       </c>
       <c r="B45" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4935,21 +4927,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4959,10 +4951,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406583</v>
+        <v>406276</v>
       </c>
       <c r="R45" t="n">
-        <v>6832841</v>
+        <v>6832761</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5021,7 +5013,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845611</v>
+        <v>129845431</v>
       </c>
       <c r="B46" t="n">
         <v>79685</v>
@@ -5056,10 +5048,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406276</v>
+        <v>406368</v>
       </c>
       <c r="R46" t="n">
-        <v>6832761</v>
+        <v>6833201</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5106,22 +5098,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845431</v>
+        <v>129845456</v>
       </c>
       <c r="B47" t="n">
-        <v>79685</v>
+        <v>78853</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5129,21 +5121,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5153,10 +5145,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406368</v>
+        <v>406442</v>
       </c>
       <c r="R47" t="n">
-        <v>6833201</v>
+        <v>6833041</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5215,10 +5207,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845456</v>
+        <v>129845631</v>
       </c>
       <c r="B48" t="n">
-        <v>78853</v>
+        <v>57738</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5226,34 +5218,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406442</v>
+        <v>406698</v>
       </c>
       <c r="R48" t="n">
-        <v>6833041</v>
+        <v>6832875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5300,12 +5300,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -8017,10 +8017,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129845420</v>
+        <v>129845486</v>
       </c>
       <c r="B76" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,21 +8028,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406424</v>
+        <v>406350</v>
       </c>
       <c r="R76" t="n">
-        <v>6832865</v>
+        <v>6832772</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129845415</v>
+        <v>129845420</v>
       </c>
       <c r="B77" t="n">
         <v>79714</v>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406317</v>
+        <v>406424</v>
       </c>
       <c r="R77" t="n">
-        <v>6832733</v>
+        <v>6832865</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8211,7 +8211,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129845600</v>
+        <v>129845415</v>
       </c>
       <c r="B78" t="n">
         <v>79714</v>
@@ -8246,10 +8246,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406582</v>
+        <v>406317</v>
       </c>
       <c r="R78" t="n">
-        <v>6832826</v>
+        <v>6832733</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8296,22 +8296,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129845606</v>
+        <v>129845600</v>
       </c>
       <c r="B79" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406394</v>
+        <v>406582</v>
       </c>
       <c r="R79" t="n">
-        <v>6833197</v>
+        <v>6832826</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129845486</v>
+        <v>129845606</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406350</v>
+        <v>406394</v>
       </c>
       <c r="R80" t="n">
-        <v>6832772</v>
+        <v>6833197</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8490,22 +8490,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845647</v>
+        <v>129845454</v>
       </c>
       <c r="B81" t="n">
-        <v>78852</v>
+        <v>57738</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,34 +8513,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406274</v>
+        <v>406675</v>
       </c>
       <c r="R81" t="n">
-        <v>6832759</v>
+        <v>6832988</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8587,22 +8595,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845444</v>
+        <v>129845621</v>
       </c>
       <c r="B82" t="n">
-        <v>91660</v>
+        <v>57741</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8610,26 +8618,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8637,10 +8650,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406601</v>
+        <v>406672</v>
       </c>
       <c r="R82" t="n">
-        <v>6832858</v>
+        <v>6832840</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8681,29 +8694,28 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845454</v>
+        <v>129845444</v>
       </c>
       <c r="B83" t="n">
-        <v>57738</v>
+        <v>91660</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8711,31 +8723,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8743,10 +8750,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406675</v>
+        <v>406601</v>
       </c>
       <c r="R83" t="n">
-        <v>6832988</v>
+        <v>6832858</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8787,6 +8794,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8805,10 +8813,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845621</v>
+        <v>129845647</v>
       </c>
       <c r="B84" t="n">
-        <v>57741</v>
+        <v>78852</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8816,42 +8824,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406672</v>
+        <v>406274</v>
       </c>
       <c r="R84" t="n">
-        <v>6832840</v>
+        <v>6832759</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9209,54 +9209,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845641</v>
+        <v>129845423</v>
       </c>
       <c r="B88" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406618</v>
+        <v>406531</v>
       </c>
       <c r="R88" t="n">
-        <v>6832813</v>
+        <v>6832868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9297,56 +9288,61 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845437</v>
+        <v>129845641</v>
       </c>
       <c r="B89" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9354,10 +9350,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406331</v>
+        <v>406618</v>
       </c>
       <c r="R89" t="n">
-        <v>6832676</v>
+        <v>6832813</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9405,22 +9401,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845423</v>
+        <v>129845437</v>
       </c>
       <c r="B90" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9428,34 +9424,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406531</v>
+        <v>406331</v>
       </c>
       <c r="R90" t="n">
-        <v>6832868</v>
+        <v>6832676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9496,6 +9495,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845479</v>
+        <v>129845634</v>
       </c>
       <c r="B91" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,34 +9525,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406408</v>
+        <v>406781</v>
       </c>
       <c r="R91" t="n">
-        <v>6832975</v>
+        <v>6832843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9599,22 +9607,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845480</v>
+        <v>129845457</v>
       </c>
       <c r="B92" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9622,21 +9630,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406277</v>
+        <v>406265</v>
       </c>
       <c r="R92" t="n">
-        <v>6832823</v>
+        <v>6832808</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9708,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845594</v>
+        <v>129845608</v>
       </c>
       <c r="B93" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9743,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406506</v>
+        <v>406399</v>
       </c>
       <c r="R93" t="n">
-        <v>6832725</v>
+        <v>6833177</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9805,45 +9813,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845418</v>
+        <v>129845464</v>
       </c>
       <c r="B94" t="n">
-        <v>79714</v>
+        <v>58113</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406377</v>
+        <v>406416</v>
       </c>
       <c r="R94" t="n">
-        <v>6832837</v>
+        <v>6832880</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9902,10 +9918,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845408</v>
+        <v>129845479</v>
       </c>
       <c r="B95" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9913,21 +9929,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9937,10 +9953,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406368</v>
+        <v>406408</v>
       </c>
       <c r="R95" t="n">
-        <v>6833202</v>
+        <v>6832975</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9999,10 +10015,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845634</v>
+        <v>129845480</v>
       </c>
       <c r="B96" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10010,42 +10026,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406781</v>
+        <v>406277</v>
       </c>
       <c r="R96" t="n">
-        <v>6832843</v>
+        <v>6832823</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10092,65 +10100,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845464</v>
+        <v>129845594</v>
       </c>
       <c r="B97" t="n">
-        <v>58113</v>
+        <v>79714</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406416</v>
+        <v>406506</v>
       </c>
       <c r="R97" t="n">
-        <v>6832880</v>
+        <v>6832725</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10197,22 +10197,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845457</v>
+        <v>129845418</v>
       </c>
       <c r="B98" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10220,21 +10220,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406265</v>
+        <v>406377</v>
       </c>
       <c r="R98" t="n">
-        <v>6832808</v>
+        <v>6832837</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845608</v>
+        <v>129845408</v>
       </c>
       <c r="B99" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406399</v>
+        <v>406368</v>
       </c>
       <c r="R99" t="n">
-        <v>6833177</v>
+        <v>6833202</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10391,12 +10391,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -11599,45 +11599,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129845433</v>
+        <v>129845640</v>
       </c>
       <c r="B112" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406438</v>
+        <v>406404</v>
       </c>
       <c r="R112" t="n">
-        <v>6833114</v>
+        <v>6832729</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11678,25 +11687,26 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129845430</v>
+        <v>129845433</v>
       </c>
       <c r="B113" t="n">
         <v>79685</v>
@@ -11731,10 +11741,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406465</v>
+        <v>406438</v>
       </c>
       <c r="R113" t="n">
-        <v>6833093</v>
+        <v>6833114</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11793,10 +11803,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129845421</v>
+        <v>129845430</v>
       </c>
       <c r="B114" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11804,21 +11814,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11828,10 +11838,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406500</v>
+        <v>406465</v>
       </c>
       <c r="R114" t="n">
-        <v>6832933</v>
+        <v>6833093</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11890,54 +11900,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129845640</v>
+        <v>129845421</v>
       </c>
       <c r="B115" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406404</v>
+        <v>406500</v>
       </c>
       <c r="R115" t="n">
-        <v>6832729</v>
+        <v>6832933</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11978,29 +11979,28 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845596</v>
+        <v>129845628</v>
       </c>
       <c r="B116" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,34 +12008,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406536</v>
+        <v>406541</v>
       </c>
       <c r="R116" t="n">
-        <v>6832770</v>
+        <v>6832823</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12094,7 +12102,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845628</v>
+        <v>129845635</v>
       </c>
       <c r="B117" t="n">
         <v>57738</v>
@@ -12127,7 +12135,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12137,10 +12145,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406541</v>
+        <v>406677</v>
       </c>
       <c r="R117" t="n">
-        <v>6832823</v>
+        <v>6832986</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12199,10 +12207,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845635</v>
+        <v>129845596</v>
       </c>
       <c r="B118" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12210,42 +12218,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406677</v>
+        <v>406536</v>
       </c>
       <c r="R118" t="n">
-        <v>6832986</v>
+        <v>6832770</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12789,10 +12789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129845494</v>
+        <v>129845451</v>
       </c>
       <c r="B124" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12800,34 +12800,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406710</v>
+        <v>406595</v>
       </c>
       <c r="R124" t="n">
-        <v>6832990</v>
+        <v>6832931</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12886,7 +12894,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129845495</v>
+        <v>129845494</v>
       </c>
       <c r="B125" t="n">
         <v>79095</v>
@@ -12921,10 +12929,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406668</v>
+        <v>406710</v>
       </c>
       <c r="R125" t="n">
-        <v>6833007</v>
+        <v>6832990</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12983,7 +12991,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129845484</v>
+        <v>129845495</v>
       </c>
       <c r="B126" t="n">
         <v>79095</v>
@@ -13012,19 +13020,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406310</v>
+        <v>406668</v>
       </c>
       <c r="R126" t="n">
-        <v>6832729</v>
+        <v>6833007</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13065,7 +13070,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13084,10 +13088,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129845451</v>
+        <v>129845484</v>
       </c>
       <c r="B127" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13095,31 +13099,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13127,10 +13126,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406595</v>
+        <v>406310</v>
       </c>
       <c r="R127" t="n">
-        <v>6832931</v>
+        <v>6832729</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13171,6 +13170,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129845599</v>
+        <v>129845438</v>
       </c>
       <c r="B2" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406635</v>
+        <v>406361</v>
       </c>
       <c r="R2" t="n">
-        <v>6832779</v>
+        <v>6832815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129845598</v>
+        <v>129845441</v>
       </c>
       <c r="B3" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406626</v>
+        <v>406638</v>
       </c>
       <c r="R3" t="n">
-        <v>6832781</v>
+        <v>6832869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129845425</v>
+        <v>129845599</v>
       </c>
       <c r="B4" t="n">
         <v>79714</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406832</v>
+        <v>406635</v>
       </c>
       <c r="R4" t="n">
-        <v>6832816</v>
+        <v>6832779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129845419</v>
+        <v>129845598</v>
       </c>
       <c r="B5" t="n">
         <v>79714</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406387</v>
+        <v>406626</v>
       </c>
       <c r="R5" t="n">
-        <v>6832850</v>
+        <v>6832781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129845438</v>
+        <v>129845425</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406361</v>
+        <v>406832</v>
       </c>
       <c r="R6" t="n">
-        <v>6832815</v>
+        <v>6832816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129845441</v>
+        <v>129845419</v>
       </c>
       <c r="B7" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406638</v>
+        <v>406387</v>
       </c>
       <c r="R7" t="n">
-        <v>6832869</v>
+        <v>6832850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3641,45 +3641,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129845412</v>
+        <v>129845463</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406426</v>
+        <v>406746</v>
       </c>
       <c r="R32" t="n">
-        <v>6832990</v>
+        <v>6832985</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3720,6 +3729,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3738,54 +3748,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129845463</v>
+        <v>129845639</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>78853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406746</v>
+        <v>406276</v>
       </c>
       <c r="R33" t="n">
-        <v>6832985</v>
+        <v>6832761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3826,29 +3827,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129845639</v>
+        <v>129845412</v>
       </c>
       <c r="B34" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406276</v>
+        <v>406426</v>
       </c>
       <c r="R34" t="n">
-        <v>6832761</v>
+        <v>6832990</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3930,19 +3930,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129845657</v>
+        <v>129845481</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406495</v>
+        <v>406278</v>
       </c>
       <c r="R35" t="n">
-        <v>6832766</v>
+        <v>6832795</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,22 +4027,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129845592</v>
+        <v>129845483</v>
       </c>
       <c r="B36" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406370</v>
+        <v>406344</v>
       </c>
       <c r="R36" t="n">
-        <v>6832711</v>
+        <v>6832706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4124,22 +4124,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129845481</v>
+        <v>129845592</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4147,21 +4147,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406278</v>
+        <v>406370</v>
       </c>
       <c r="R37" t="n">
-        <v>6832795</v>
+        <v>6832711</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,19 +4221,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129845483</v>
+        <v>129845657</v>
       </c>
       <c r="B38" t="n">
         <v>79095</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406344</v>
+        <v>406495</v>
       </c>
       <c r="R38" t="n">
-        <v>6832706</v>
+        <v>6832766</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4318,12 +4318,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129845601</v>
+        <v>129845490</v>
       </c>
       <c r="B40" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4438,21 +4438,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406583</v>
+        <v>406560</v>
       </c>
       <c r="R40" t="n">
-        <v>6832841</v>
+        <v>6832885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4512,19 +4512,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129845490</v>
+        <v>129845491</v>
       </c>
       <c r="B41" t="n">
         <v>79095</v>
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406560</v>
+        <v>406588</v>
       </c>
       <c r="R41" t="n">
-        <v>6832885</v>
+        <v>6832866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129845491</v>
+        <v>129845492</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -4650,16 +4650,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406588</v>
+        <v>406591</v>
       </c>
       <c r="R42" t="n">
-        <v>6832866</v>
+        <v>6832966</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4700,6 +4703,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4718,7 +4722,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129845492</v>
+        <v>129845660</v>
       </c>
       <c r="B43" t="n">
         <v>79095</v>
@@ -4747,19 +4751,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406591</v>
+        <v>406728</v>
       </c>
       <c r="R43" t="n">
-        <v>6832966</v>
+        <v>6832848</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4800,29 +4801,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129845660</v>
+        <v>129845631</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4830,34 +4830,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406728</v>
+        <v>406698</v>
       </c>
       <c r="R44" t="n">
-        <v>6832848</v>
+        <v>6832875</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4916,10 +4924,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129845611</v>
+        <v>129845601</v>
       </c>
       <c r="B45" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4927,21 +4935,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4951,10 +4959,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406276</v>
+        <v>406583</v>
       </c>
       <c r="R45" t="n">
-        <v>6832761</v>
+        <v>6832841</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5013,7 +5021,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129845431</v>
+        <v>129845611</v>
       </c>
       <c r="B46" t="n">
         <v>79685</v>
@@ -5048,10 +5056,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406368</v>
+        <v>406276</v>
       </c>
       <c r="R46" t="n">
-        <v>6833201</v>
+        <v>6832761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,22 +5106,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129845456</v>
+        <v>129845431</v>
       </c>
       <c r="B47" t="n">
-        <v>78853</v>
+        <v>79685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5121,21 +5129,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5145,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406442</v>
+        <v>406368</v>
       </c>
       <c r="R47" t="n">
-        <v>6833041</v>
+        <v>6833201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5207,10 +5215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129845631</v>
+        <v>129845456</v>
       </c>
       <c r="B48" t="n">
-        <v>57738</v>
+        <v>78853</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5218,42 +5226,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406698</v>
+        <v>406442</v>
       </c>
       <c r="R48" t="n">
-        <v>6832875</v>
+        <v>6833041</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5300,22 +5300,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129845638</v>
+        <v>129845416</v>
       </c>
       <c r="B49" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5323,21 +5323,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406290</v>
+        <v>406362</v>
       </c>
       <c r="R49" t="n">
-        <v>6832900</v>
+        <v>6832766</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5397,22 +5397,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129845612</v>
+        <v>129845589</v>
       </c>
       <c r="B50" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5420,21 +5420,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406379</v>
+        <v>406406</v>
       </c>
       <c r="R50" t="n">
-        <v>6832756</v>
+        <v>6833199</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5506,10 +5506,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129845624</v>
+        <v>129845626</v>
       </c>
       <c r="B51" t="n">
-        <v>57900</v>
+        <v>91660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5517,31 +5517,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5549,10 +5548,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406494</v>
+        <v>406533</v>
       </c>
       <c r="R51" t="n">
-        <v>6832766</v>
+        <v>6832761</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5593,6 +5592,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5611,41 +5611,40 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129845461</v>
+        <v>129845624</v>
       </c>
       <c r="B52" t="n">
-        <v>8451</v>
+        <v>57900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5655,10 +5654,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406589</v>
+        <v>406494</v>
       </c>
       <c r="R52" t="n">
-        <v>6832990</v>
+        <v>6832766</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5699,60 +5698,61 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129845626</v>
+        <v>129845461</v>
       </c>
       <c r="B53" t="n">
-        <v>91660</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406533</v>
+        <v>406589</v>
       </c>
       <c r="R53" t="n">
-        <v>6832761</v>
+        <v>6832990</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5811,22 +5811,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129845416</v>
+        <v>129845638</v>
       </c>
       <c r="B54" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406362</v>
+        <v>406290</v>
       </c>
       <c r="R54" t="n">
-        <v>6832766</v>
+        <v>6832900</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5908,22 +5908,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129845589</v>
+        <v>129845612</v>
       </c>
       <c r="B55" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406406</v>
+        <v>406379</v>
       </c>
       <c r="R55" t="n">
-        <v>6833199</v>
+        <v>6832756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6017,43 +6017,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129845459</v>
+        <v>129845625</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>91660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6061,10 +6059,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406331</v>
+        <v>406472</v>
       </c>
       <c r="R56" t="n">
-        <v>6832715</v>
+        <v>6832767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6112,22 +6110,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129845435</v>
+        <v>129845487</v>
       </c>
       <c r="B57" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6135,21 +6133,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6159,10 +6157,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406455</v>
+        <v>406409</v>
       </c>
       <c r="R57" t="n">
-        <v>6833027</v>
+        <v>6832824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6221,10 +6219,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129845625</v>
+        <v>129845410</v>
       </c>
       <c r="B58" t="n">
-        <v>91660</v>
+        <v>79714</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6232,41 +6230,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406472</v>
+        <v>406487</v>
       </c>
       <c r="R58" t="n">
-        <v>6832767</v>
+        <v>6833064</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6307,29 +6298,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129845487</v>
+        <v>129845602</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6337,21 +6327,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6361,10 +6351,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406409</v>
+        <v>406791</v>
       </c>
       <c r="R59" t="n">
-        <v>6832824</v>
+        <v>6832844</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,22 +6401,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129845410</v>
+        <v>129845466</v>
       </c>
       <c r="B60" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6424,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6448,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406487</v>
+        <v>406266</v>
       </c>
       <c r="R60" t="n">
-        <v>6833064</v>
+        <v>6832810</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6520,10 +6510,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129845602</v>
+        <v>129845632</v>
       </c>
       <c r="B61" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,34 +6521,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406791</v>
+        <v>406667</v>
       </c>
       <c r="R61" t="n">
-        <v>6832844</v>
+        <v>6832849</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6617,10 +6615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129845466</v>
+        <v>129845633</v>
       </c>
       <c r="B62" t="n">
-        <v>78852</v>
+        <v>57738</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,34 +6626,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406266</v>
+        <v>406674</v>
       </c>
       <c r="R62" t="n">
-        <v>6832810</v>
+        <v>6832801</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6702,19 +6708,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129845632</v>
+        <v>129845627</v>
       </c>
       <c r="B63" t="n">
         <v>57738</v>
@@ -6747,7 +6753,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6757,10 +6763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406667</v>
+        <v>406539</v>
       </c>
       <c r="R63" t="n">
-        <v>6832849</v>
+        <v>6832767</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6819,40 +6825,41 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129845633</v>
+        <v>129845459</v>
       </c>
       <c r="B64" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6862,10 +6869,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406674</v>
+        <v>406331</v>
       </c>
       <c r="R64" t="n">
-        <v>6832801</v>
+        <v>6832715</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,28 +6913,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129845627</v>
+        <v>129845435</v>
       </c>
       <c r="B65" t="n">
-        <v>57738</v>
+        <v>79685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6935,42 +6943,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406539</v>
+        <v>406455</v>
       </c>
       <c r="R65" t="n">
-        <v>6832767</v>
+        <v>6833027</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7017,22 +7017,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129845493</v>
+        <v>129845434</v>
       </c>
       <c r="B66" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406785</v>
+        <v>406499</v>
       </c>
       <c r="R66" t="n">
-        <v>6832912</v>
+        <v>6833054</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129845590</v>
+        <v>129845440</v>
       </c>
       <c r="B67" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406421</v>
+        <v>406445</v>
       </c>
       <c r="R67" t="n">
-        <v>6833142</v>
+        <v>6832921</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7211,22 +7211,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129845593</v>
+        <v>129845605</v>
       </c>
       <c r="B68" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7234,21 +7234,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406451</v>
+        <v>406440</v>
       </c>
       <c r="R68" t="n">
-        <v>6832712</v>
+        <v>6833100</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7320,10 +7320,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129845452</v>
+        <v>129845607</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>79685</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7331,42 +7331,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406630</v>
+        <v>406407</v>
       </c>
       <c r="R69" t="n">
-        <v>6832941</v>
+        <v>6833199</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7413,12 +7405,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7522,10 +7514,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129845434</v>
+        <v>129845493</v>
       </c>
       <c r="B71" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,21 +7525,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7557,10 +7549,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406499</v>
+        <v>406785</v>
       </c>
       <c r="R71" t="n">
-        <v>6833054</v>
+        <v>6832912</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7619,10 +7611,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129845440</v>
+        <v>129845590</v>
       </c>
       <c r="B72" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7630,21 +7622,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7654,10 +7646,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406445</v>
+        <v>406421</v>
       </c>
       <c r="R72" t="n">
-        <v>6832921</v>
+        <v>6833142</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7704,22 +7696,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129845605</v>
+        <v>129845593</v>
       </c>
       <c r="B73" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7727,21 +7719,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7751,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406440</v>
+        <v>406451</v>
       </c>
       <c r="R73" t="n">
-        <v>6833100</v>
+        <v>6832712</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7813,10 +7805,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129845607</v>
+        <v>129845452</v>
       </c>
       <c r="B74" t="n">
-        <v>79685</v>
+        <v>57738</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7824,34 +7816,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406407</v>
+        <v>406630</v>
       </c>
       <c r="R74" t="n">
-        <v>6833199</v>
+        <v>6832941</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7898,12 +7898,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129845454</v>
+        <v>129845647</v>
       </c>
       <c r="B81" t="n">
-        <v>57738</v>
+        <v>78852</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,42 +8513,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406675</v>
+        <v>406274</v>
       </c>
       <c r="R81" t="n">
-        <v>6832988</v>
+        <v>6832759</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8595,22 +8587,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129845621</v>
+        <v>129845444</v>
       </c>
       <c r="B82" t="n">
-        <v>57741</v>
+        <v>91660</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8618,31 +8610,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8650,10 +8637,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406672</v>
+        <v>406601</v>
       </c>
       <c r="R82" t="n">
-        <v>6832840</v>
+        <v>6832858</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8694,28 +8681,29 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129845444</v>
+        <v>129845454</v>
       </c>
       <c r="B83" t="n">
-        <v>91660</v>
+        <v>57738</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8723,26 +8711,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8750,10 +8743,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406601</v>
+        <v>406675</v>
       </c>
       <c r="R83" t="n">
-        <v>6832858</v>
+        <v>6832988</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8794,7 +8787,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8813,10 +8805,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129845647</v>
+        <v>129845621</v>
       </c>
       <c r="B84" t="n">
-        <v>78852</v>
+        <v>57741</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8824,34 +8816,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406274</v>
+        <v>406672</v>
       </c>
       <c r="R84" t="n">
-        <v>6832759</v>
+        <v>6832840</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9209,45 +9209,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129845423</v>
+        <v>129845641</v>
       </c>
       <c r="B88" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406531</v>
+        <v>406618</v>
       </c>
       <c r="R88" t="n">
-        <v>6832868</v>
+        <v>6832813</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9288,61 +9297,56 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129845641</v>
+        <v>129845437</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9350,10 +9354,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406618</v>
+        <v>406331</v>
       </c>
       <c r="R89" t="n">
-        <v>6832813</v>
+        <v>6832676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9401,22 +9405,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129845437</v>
+        <v>129845423</v>
       </c>
       <c r="B90" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9424,37 +9428,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406331</v>
+        <v>406531</v>
       </c>
       <c r="R90" t="n">
-        <v>6832676</v>
+        <v>6832868</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9495,7 +9496,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129845634</v>
+        <v>129845457</v>
       </c>
       <c r="B91" t="n">
-        <v>57738</v>
+        <v>78853</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9525,42 +9525,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406781</v>
+        <v>406265</v>
       </c>
       <c r="R91" t="n">
-        <v>6832843</v>
+        <v>6832808</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9607,22 +9599,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129845457</v>
+        <v>129845608</v>
       </c>
       <c r="B92" t="n">
-        <v>78853</v>
+        <v>79685</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9630,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9654,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406265</v>
+        <v>406399</v>
       </c>
       <c r="R92" t="n">
-        <v>6832808</v>
+        <v>6833177</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9704,22 +9696,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129845608</v>
+        <v>129845479</v>
       </c>
       <c r="B93" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9719,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9743,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406399</v>
+        <v>406408</v>
       </c>
       <c r="R93" t="n">
-        <v>6833177</v>
+        <v>6832975</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9801,65 +9793,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129845464</v>
+        <v>129845480</v>
       </c>
       <c r="B94" t="n">
-        <v>58113</v>
+        <v>79095</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406416</v>
+        <v>406277</v>
       </c>
       <c r="R94" t="n">
-        <v>6832880</v>
+        <v>6832823</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9918,10 +9902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129845479</v>
+        <v>129845594</v>
       </c>
       <c r="B95" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9929,21 +9913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9953,10 +9937,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406408</v>
+        <v>406506</v>
       </c>
       <c r="R95" t="n">
-        <v>6832975</v>
+        <v>6832725</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10003,22 +9987,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129845480</v>
+        <v>129845418</v>
       </c>
       <c r="B96" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10026,21 +10010,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10050,10 +10034,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406277</v>
+        <v>406377</v>
       </c>
       <c r="R96" t="n">
-        <v>6832823</v>
+        <v>6832837</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10112,7 +10096,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129845594</v>
+        <v>129845408</v>
       </c>
       <c r="B97" t="n">
         <v>79714</v>
@@ -10147,10 +10131,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406506</v>
+        <v>406368</v>
       </c>
       <c r="R97" t="n">
-        <v>6832725</v>
+        <v>6833202</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10197,22 +10181,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129845418</v>
+        <v>129845634</v>
       </c>
       <c r="B98" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10220,34 +10204,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406377</v>
+        <v>406781</v>
       </c>
       <c r="R98" t="n">
-        <v>6832837</v>
+        <v>6832843</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10294,57 +10286,65 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129845408</v>
+        <v>129845464</v>
       </c>
       <c r="B99" t="n">
-        <v>79714</v>
+        <v>58113</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406368</v>
+        <v>406416</v>
       </c>
       <c r="R99" t="n">
-        <v>6833202</v>
+        <v>6832880</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10403,10 +10403,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129845646</v>
+        <v>129845629</v>
       </c>
       <c r="B100" t="n">
-        <v>78852</v>
+        <v>57738</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10414,34 +10414,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406290</v>
+        <v>406618</v>
       </c>
       <c r="R100" t="n">
-        <v>6832901</v>
+        <v>6832773</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10500,10 +10508,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129845426</v>
+        <v>129845646</v>
       </c>
       <c r="B101" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10511,21 +10519,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10535,10 +10543,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406796</v>
+        <v>406290</v>
       </c>
       <c r="R101" t="n">
-        <v>6832917</v>
+        <v>6832901</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10585,22 +10593,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129845407</v>
+        <v>129845615</v>
       </c>
       <c r="B102" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10608,21 +10616,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10632,10 +10640,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406416</v>
+        <v>406583</v>
       </c>
       <c r="R102" t="n">
-        <v>6833166</v>
+        <v>6832911</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10682,22 +10690,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129845629</v>
+        <v>129845426</v>
       </c>
       <c r="B103" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,42 +10713,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406618</v>
+        <v>406796</v>
       </c>
       <c r="R103" t="n">
-        <v>6832773</v>
+        <v>6832917</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10787,22 +10787,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129845615</v>
+        <v>129845407</v>
       </c>
       <c r="B104" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10810,21 +10810,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406583</v>
+        <v>406416</v>
       </c>
       <c r="R104" t="n">
-        <v>6832911</v>
+        <v>6833166</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10884,12 +10884,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11997,10 +11997,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129845628</v>
+        <v>129845596</v>
       </c>
       <c r="B116" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,42 +12008,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406541</v>
+        <v>406536</v>
       </c>
       <c r="R116" t="n">
-        <v>6832823</v>
+        <v>6832770</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12102,7 +12094,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129845635</v>
+        <v>129845628</v>
       </c>
       <c r="B117" t="n">
         <v>57738</v>
@@ -12135,7 +12127,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -12145,10 +12137,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406677</v>
+        <v>406541</v>
       </c>
       <c r="R117" t="n">
-        <v>6832986</v>
+        <v>6832823</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12207,10 +12199,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129845596</v>
+        <v>129845635</v>
       </c>
       <c r="B118" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12218,34 +12210,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406536</v>
+        <v>406677</v>
       </c>
       <c r="R118" t="n">
-        <v>6832770</v>
+        <v>6832986</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 20146-2025 artfynd.xlsx
+++ b/artfynd/A 20146-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129845661</v>
+        <v>129845630</v>
       </c>
       <c r="B8" t="n">
-        <v>78761</v>
+        <v>57738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406352</v>
+        <v>406631</v>
       </c>
       <c r="R8" t="n">
-        <v>6832709</v>
+        <v>6832822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129845630</v>
+        <v>129845443</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1387,7 +1395,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1397,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406631</v>
+        <v>406333</v>
       </c>
       <c r="R9" t="n">
-        <v>6832822</v>
+        <v>6832733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,19 +1455,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129845427</v>
+        <v>129845417</v>
       </c>
       <c r="B10" t="n">
         <v>79714</v>
@@ -1494,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406794</v>
+        <v>406346</v>
       </c>
       <c r="R10" t="n">
-        <v>6832934</v>
+        <v>6832798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129845417</v>
+        <v>129845661</v>
       </c>
       <c r="B11" t="n">
-        <v>79714</v>
+        <v>78761</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406346</v>
+        <v>406352</v>
       </c>
       <c r="R11" t="n">
-        <v>6832798</v>
+        <v>6832709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,22 +1649,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129845443</v>
+        <v>129845427</v>
       </c>
       <c r="B12" t="n">
-        <v>57900</v>
+        <v>79714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,42 +1672,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406333</v>
+        <v>406794</v>
       </c>
       <c r="R12" t="n">
-        <v>6832733</v>
+        <v>6832934</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1956,54 +1956,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129845462</v>
+        <v>129845655</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406713</v>
+        <v>406473</v>
       </c>
       <c r="R15" t="n">
-        <v>6832904</v>
+        <v>6832798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,64 +2035,72 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129845610</v>
+        <v>129845462</v>
       </c>
       <c r="B16" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406262</v>
+        <v>406713</v>
       </c>
       <c r="R16" t="n">
-        <v>6832854</v>
+        <v>6832904</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2142,25 +2141,26 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129845614</v>
+        <v>129845610</v>
       </c>
       <c r="B17" t="n">
         <v>79685</v>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406492</v>
+        <v>406262</v>
       </c>
       <c r="R17" t="n">
-        <v>6832753</v>
+        <v>6832854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,7 +2257,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129845618</v>
+        <v>129845614</v>
       </c>
       <c r="B18" t="n">
         <v>79685</v>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406791</v>
+        <v>406492</v>
       </c>
       <c r="R18" t="n">
-        <v>6832845</v>
+        <v>6832753</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129845429</v>
+        <v>129845618</v>
       </c>
       <c r="B19" t="n">
         <v>79685</v>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406472</v>
+        <v>406791</v>
       </c>
       <c r="R19" t="n">
-        <v>6833103</v>
+        <v>6832845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,19 +2439,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129845613</v>
+        <v>129845429</v>
       </c>
       <c r="B20" t="n">
         <v>79685</v>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406388</v>
+        <v>406472</v>
       </c>
       <c r="R20" t="n">
-        <v>6832683</v>
+        <v>6833103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,19 +2536,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129845617</v>
+        <v>129845613</v>
       </c>
       <c r="B21" t="n">
         <v>79685</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406626</v>
+        <v>406388</v>
       </c>
       <c r="R21" t="n">
-        <v>6832781</v>
+        <v>6832683</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129845655</v>
+        <v>129845617</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406473</v>
+        <v>406626</v>
       </c>
       <c r="R22" t="n">
-        <v>6832798</v>
+        <v>6832781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129845636</v>
+        <v>129845412</v>
       </c>
       <c r="B30" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,42 +3442,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valkesmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406595</v>
+        <v>406426</v>
       </c>
       <c r="R30" t="n">
-        <v>6833001</v>
+        <v>6832990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3524,22 +3516,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129845449</v>
+        <v>129845639</v>
       </c>
       <c r="B31" t="n">
-        <v>57738</v>
+        <v>78853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3547,42 +3539,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="in